--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>445.0</v>
+        <v>446.0</v>
       </c>
       <c r="D3" t="n">
         <v>63.0</v>
@@ -863,7 +863,7 @@
         <v>145.0</v>
       </c>
       <c r="D30" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="31">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="D40" t="n">
-        <v>839.0</v>
+        <v>840.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>171.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2086.0</v>
+        <v>2091.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>376.0</v>
+        <v>384.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3945.0</v>
+        <v>3946.0</v>
       </c>
     </row>
     <row r="44">
@@ -1129,7 +1129,7 @@
         <v>22.0</v>
       </c>
       <c r="D49" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="50">
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>572.0</v>
+        <v>574.0</v>
       </c>
       <c r="D50" t="n">
         <v>71.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>704.0</v>
+        <v>708.0</v>
       </c>
       <c r="D56" t="n">
         <v>431.0</v>
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="D57" t="n">
         <v>153.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>645.0</v>
+        <v>648.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1283,7 +1283,7 @@
         <v>718.0</v>
       </c>
       <c r="D60" t="n">
-        <v>817.0</v>
+        <v>819.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1965.0</v>
+        <v>1966.0</v>
       </c>
       <c r="D61" t="n">
-        <v>11850.0</v>
+        <v>11874.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1783.0</v>
+        <v>1795.0</v>
       </c>
       <c r="D62" t="n">
         <v>325.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1254.0</v>
+        <v>1265.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2409.0</v>
+        <v>2413.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1267.0</v>
+        <v>1279.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1034.0</v>
+        <v>1036.0</v>
       </c>
     </row>
     <row r="66">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
       <c r="D100" t="n">
         <v>143.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>377.0</v>
+        <v>467.0</v>
       </c>
       <c r="D18" t="n">
         <v>239.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>388.0</v>
+        <v>392.0</v>
       </c>
       <c r="D21" t="n">
         <v>523.0</v>
@@ -835,7 +835,7 @@
         <v>233.0</v>
       </c>
       <c r="D28" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="29">
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
       <c r="D30" t="n">
         <v>143.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>648.0</v>
+        <v>649.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1294,7 +1294,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1966.0</v>
+        <v>1969.0</v>
       </c>
       <c r="D61" t="n">
         <v>11874.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1265.0</v>
+        <v>1269.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2413.0</v>
+        <v>2417.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>502.0</v>
+        <v>503.0</v>
       </c>
     </row>
     <row r="67">
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="100">
@@ -1896,10 +1896,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>295.0</v>
+        <v>296.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>931.0</v>
+        <v>934.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1072.0</v>
+        <v>1078.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2127.0</v>
+        <v>2129.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1060.0</v>
+        <v>1065.0</v>
       </c>
     </row>
     <row r="8">
@@ -622,10 +622,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>796.0</v>
+        <v>818.0</v>
       </c>
       <c r="D13" t="n">
-        <v>301.0</v>
+        <v>313.0</v>
       </c>
     </row>
     <row r="14">
@@ -636,10 +636,10 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>518.0</v>
+        <v>532.0</v>
       </c>
       <c r="D14" t="n">
-        <v>103.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="15">
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>597.0</v>
+        <v>611.0</v>
       </c>
       <c r="D15" t="n">
-        <v>164.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="16">
@@ -664,7 +664,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
       <c r="D16" t="n">
         <v>83.0</v>
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9172.0</v>
+        <v>9205.0</v>
       </c>
       <c r="D17" t="n">
-        <v>862.0</v>
+        <v>884.0</v>
       </c>
     </row>
     <row r="18">
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>467.0</v>
+        <v>473.0</v>
       </c>
       <c r="D18" t="n">
-        <v>239.0</v>
+        <v>241.0</v>
       </c>
     </row>
     <row r="19">
@@ -720,7 +720,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="D20" t="n">
         <v>306.0</v>
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>392.0</v>
+        <v>464.0</v>
       </c>
       <c r="D21" t="n">
-        <v>523.0</v>
+        <v>527.0</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +751,7 @@
         <v>18.0</v>
       </c>
       <c r="D22" t="n">
-        <v>287.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="23">
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="D23" t="n">
-        <v>217.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="24">
@@ -790,10 +790,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>749.0</v>
+        <v>759.0</v>
       </c>
       <c r="D25" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
     </row>
     <row r="26">
@@ -807,7 +807,7 @@
         <v>25.0</v>
       </c>
       <c r="D26" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="27">
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="D27" t="n">
         <v>12.0</v>
@@ -863,7 +863,7 @@
         <v>146.0</v>
       </c>
       <c r="D30" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="31">
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>1010.0</v>
+        <v>1023.0</v>
       </c>
       <c r="D39" t="n">
         <v>14.0</v>
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="D40" t="n">
-        <v>840.0</v>
+        <v>848.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>171.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2091.0</v>
+        <v>2099.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>384.0</v>
+        <v>389.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>96.0</v>
+        <v>98.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3946.0</v>
+        <v>3948.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>2801.0</v>
+        <v>2802.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>8.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1401.0</v>
+        <v>1402.0</v>
       </c>
     </row>
     <row r="47">
@@ -1140,10 +1140,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>574.0</v>
+        <v>576.0</v>
       </c>
       <c r="D50" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>351.0</v>
+        <v>352.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1168,10 +1168,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>227.0</v>
+        <v>228.0</v>
       </c>
       <c r="D52" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="53">
@@ -1182,10 +1182,10 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
       <c r="D53" t="n">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="54">
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>457.0</v>
+        <v>467.0</v>
       </c>
       <c r="D54" t="n">
         <v>128.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>407.0</v>
+        <v>408.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>708.0</v>
+        <v>711.0</v>
       </c>
       <c r="D56" t="n">
-        <v>431.0</v>
+        <v>433.0</v>
       </c>
     </row>
     <row r="57">
@@ -1241,7 +1241,7 @@
         <v>159.0</v>
       </c>
       <c r="D57" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="58">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="D58" t="n">
         <v>1.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>649.0</v>
+        <v>678.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1283,7 +1283,7 @@
         <v>718.0</v>
       </c>
       <c r="D60" t="n">
-        <v>819.0</v>
+        <v>826.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1969.0</v>
+        <v>1991.0</v>
       </c>
       <c r="D61" t="n">
-        <v>11874.0</v>
+        <v>11955.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1795.0</v>
+        <v>1855.0</v>
       </c>
       <c r="D62" t="n">
-        <v>325.0</v>
+        <v>327.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1269.0</v>
+        <v>1286.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2417.0</v>
+        <v>2429.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1279.0</v>
+        <v>1293.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1036.0</v>
+        <v>1041.0</v>
       </c>
     </row>
     <row r="66">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>503.0</v>
+        <v>506.0</v>
       </c>
     </row>
     <row r="67">
@@ -1392,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>194.0</v>
+        <v>198.0</v>
       </c>
       <c r="D68" t="n">
         <v>184.0</v>
@@ -1409,7 +1409,7 @@
         <v>83.0</v>
       </c>
       <c r="D69" t="n">
-        <v>92.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="70">
@@ -1434,7 +1434,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="D71" t="n">
         <v>0.0</v>
@@ -1462,7 +1462,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>283.0</v>
+        <v>285.0</v>
       </c>
       <c r="D73" t="n">
         <v>40.0</v>
@@ -1658,10 +1658,10 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
       <c r="D87" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
     </row>
     <row r="88">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>422.0</v>
+        <v>424.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="D89" t="n">
         <v>104.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>764.0</v>
+        <v>765.0</v>
       </c>
       <c r="D91" t="n">
         <v>18.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>195.0</v>
+        <v>204.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1164.0</v>
+        <v>1189.0</v>
       </c>
       <c r="D93" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>64.0</v>
+        <v>70.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>779.0</v>
+        <v>783.0</v>
       </c>
       <c r="D96" t="n">
-        <v>420.0</v>
+        <v>422.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>559.0</v>
+        <v>561.0</v>
       </c>
       <c r="D97" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="98">
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
       <c r="D100" t="n">
         <v>143.0</v>
@@ -1899,7 +1899,7 @@
         <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -863,7 +863,7 @@
         <v>146.0</v>
       </c>
       <c r="D30" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="31">
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>1023.0</v>
+        <v>1025.0</v>
       </c>
       <c r="D39" t="n">
         <v>14.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>352.0</v>
+        <v>353.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>467.0</v>
+        <v>468.0</v>
       </c>
       <c r="D54" t="n">
         <v>128.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>408.0</v>
+        <v>409.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>678.0</v>
+        <v>679.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1297,7 +1297,7 @@
         <v>1991.0</v>
       </c>
       <c r="D61" t="n">
-        <v>11955.0</v>
+        <v>11978.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1855.0</v>
+        <v>1901.0</v>
       </c>
       <c r="D62" t="n">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1286.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2429.0</v>
+        <v>2430.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1293.0</v>
+        <v>1301.0</v>
       </c>
       <c r="D65" t="n">
         <v>1041.0</v>
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
     </row>
     <row r="67">
@@ -1493,7 +1493,7 @@
         <v>654.0</v>
       </c>
       <c r="D75" t="n">
-        <v>424.0</v>
+        <v>423.0</v>
       </c>
     </row>
     <row r="76">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>424.0</v>
+        <v>426.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>204.0</v>
+        <v>205.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1189.0</v>
+        <v>1193.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>783.0</v>
+        <v>786.0</v>
       </c>
       <c r="D96" t="n">
-        <v>422.0</v>
+        <v>423.0</v>
       </c>
     </row>
     <row r="97">
@@ -1812,7 +1812,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="D98" t="n">
         <v>42.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>185.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="100">
@@ -1899,7 +1899,7 @@
         <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -667,7 +667,7 @@
         <v>41.0</v>
       </c>
       <c r="D16" t="n">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="17">
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9205.0</v>
+        <v>9206.0</v>
       </c>
       <c r="D17" t="n">
-        <v>884.0</v>
+        <v>887.0</v>
       </c>
     </row>
     <row r="18">
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>389.0</v>
+        <v>395.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,7 +1042,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
       <c r="D43" t="n">
         <v>3948.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>679.0</v>
+        <v>682.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1280,10 +1280,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>718.0</v>
+        <v>719.0</v>
       </c>
       <c r="D60" t="n">
-        <v>826.0</v>
+        <v>831.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1991.0</v>
+        <v>1997.0</v>
       </c>
       <c r="D61" t="n">
-        <v>11978.0</v>
+        <v>11989.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1901.0</v>
+        <v>1915.0</v>
       </c>
       <c r="D62" t="n">
         <v>329.0</v>
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1286.0</v>
+        <v>1289.0</v>
       </c>
       <c r="D63" t="n">
         <v>2430.0</v>
@@ -1353,7 +1353,7 @@
         <v>1301.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1041.0</v>
+        <v>1046.0</v>
       </c>
     </row>
     <row r="66">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -653,7 +653,7 @@
         <v>611.0</v>
       </c>
       <c r="D15" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
     </row>
     <row r="16">
@@ -681,7 +681,7 @@
         <v>9206.0</v>
       </c>
       <c r="D17" t="n">
-        <v>887.0</v>
+        <v>891.0</v>
       </c>
     </row>
     <row r="18">
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>473.0</v>
+        <v>479.0</v>
       </c>
       <c r="D18" t="n">
         <v>241.0</v>
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>73.0</v>
       </c>
       <c r="D20" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>464.0</v>
+        <v>467.0</v>
       </c>
       <c r="D21" t="n">
         <v>527.0</v>
@@ -751,7 +751,7 @@
         <v>18.0</v>
       </c>
       <c r="D22" t="n">
-        <v>289.0</v>
+        <v>291.0</v>
       </c>
     </row>
     <row r="23">
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="D23" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
     </row>
     <row r="24">
@@ -779,7 +779,7 @@
         <v>74.0</v>
       </c>
       <c r="D24" t="n">
-        <v>367.0</v>
+        <v>369.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>759.0</v>
+        <v>765.0</v>
       </c>
       <c r="D25" t="n">
         <v>311.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1078.0</v>
+        <v>1086.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,7 +538,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2129.0</v>
+        <v>2131.0</v>
       </c>
       <c r="D7" t="n">
         <v>1065.0</v>
@@ -1283,7 +1283,7 @@
         <v>719.0</v>
       </c>
       <c r="D60" t="n">
-        <v>831.0</v>
+        <v>832.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1997.0</v>
+        <v>2003.0</v>
       </c>
       <c r="D61" t="n">
-        <v>11989.0</v>
+        <v>12019.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1915.0</v>
+        <v>1937.0</v>
       </c>
       <c r="D62" t="n">
-        <v>329.0</v>
+        <v>330.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1289.0</v>
+        <v>1292.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2430.0</v>
+        <v>2432.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1301.0</v>
+        <v>1307.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1046.0</v>
+        <v>1047.0</v>
       </c>
     </row>
     <row r="66">
@@ -1392,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>198.0</v>
+        <v>202.0</v>
       </c>
       <c r="D68" t="n">
         <v>184.0</v>
@@ -1406,7 +1406,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="D69" t="n">
         <v>94.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>934.0</v>
+        <v>938.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -485,7 +485,7 @@
         <v>446.0</v>
       </c>
       <c r="D3" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         <v>179.0</v>
       </c>
       <c r="D4" t="n">
-        <v>330.0</v>
+        <v>331.0</v>
       </c>
     </row>
     <row r="5">
@@ -667,7 +667,7 @@
         <v>41.0</v>
       </c>
       <c r="D16" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="17">
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D36" t="n">
         <v>0.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>353.0</v>
+        <v>354.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="D54" t="n">
         <v>128.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>409.0</v>
+        <v>411.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>711.0</v>
+        <v>717.0</v>
       </c>
       <c r="D56" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
     </row>
     <row r="57">
@@ -1238,10 +1238,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="D57" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="58">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>682.0</v>
+        <v>688.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1937.0</v>
+        <v>1939.0</v>
       </c>
       <c r="D62" t="n">
-        <v>330.0</v>
+        <v>332.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1292.0</v>
+        <v>1305.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2432.0</v>
+        <v>2435.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1307.0</v>
+        <v>1314.0</v>
       </c>
       <c r="D65" t="n">
         <v>1047.0</v>
@@ -1479,7 +1479,7 @@
         <v>48.0</v>
       </c>
       <c r="D74" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="75">
@@ -1490,10 +1490,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>654.0</v>
+        <v>659.0</v>
       </c>
       <c r="D75" t="n">
-        <v>423.0</v>
+        <v>425.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>429.0</v>
+        <v>441.0</v>
       </c>
       <c r="D76" t="n">
-        <v>416.0</v>
+        <v>424.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>1651.0</v>
+        <v>1676.0</v>
       </c>
       <c r="D77" t="n">
-        <v>500.0</v>
+        <v>509.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,10 +1532,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>305.0</v>
+        <v>309.0</v>
       </c>
       <c r="D78" t="n">
-        <v>467.0</v>
+        <v>479.0</v>
       </c>
     </row>
     <row r="79">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>205.0</v>
+        <v>212.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1193.0</v>
+        <v>1194.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1787,7 +1787,7 @@
         <v>786.0</v>
       </c>
       <c r="D96" t="n">
-        <v>423.0</v>
+        <v>425.0</v>
       </c>
     </row>
     <row r="97">
@@ -1801,7 +1801,7 @@
         <v>561.0</v>
       </c>
       <c r="D97" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="98">
@@ -1899,7 +1899,7 @@
         <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>298.0</v>
+        <v>302.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>520.0</v>
+        <v>525.0</v>
       </c>
       <c r="D8" t="n">
         <v>157.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>260.0</v>
+        <v>265.0</v>
       </c>
       <c r="D9" t="n">
-        <v>551.0</v>
+        <v>559.0</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>211.0</v>
+        <v>214.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -625,7 +625,7 @@
         <v>818.0</v>
       </c>
       <c r="D13" t="n">
-        <v>313.0</v>
+        <v>315.0</v>
       </c>
     </row>
     <row r="14">
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="D23" t="n">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
     </row>
     <row r="24">
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="D30" t="n">
         <v>146.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>688.0</v>
+        <v>692.0</v>
       </c>
       <c r="D59" t="n">
         <v>131.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2003.0</v>
+        <v>2005.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12019.0</v>
+        <v>12042.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1939.0</v>
+        <v>1941.0</v>
       </c>
       <c r="D62" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1305.0</v>
+        <v>1309.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2435.0</v>
+        <v>2438.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
     </row>
     <row r="67">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="D87" t="n">
         <v>265.0</v>
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="D89" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="90">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1194.0</v>
+        <v>1198.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
       <c r="D100" t="n">
         <v>143.0</v>
@@ -1868,7 +1868,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="D102" t="n">
         <v>194.0</v>
@@ -1899,7 +1899,7 @@
         <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>938.0</v>
+        <v>939.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -485,7 +485,7 @@
         <v>446.0</v>
       </c>
       <c r="D3" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="D5" t="n">
         <v>114.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,7 +1042,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>100.0</v>
+        <v>106.0</v>
       </c>
       <c r="D43" t="n">
         <v>3948.0</v>
@@ -1269,7 +1269,7 @@
         <v>692.0</v>
       </c>
       <c r="D59" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,10 +1280,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>719.0</v>
+        <v>720.0</v>
       </c>
       <c r="D60" t="n">
-        <v>832.0</v>
+        <v>833.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2005.0</v>
+        <v>2007.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12042.0</v>
+        <v>12061.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1941.0</v>
+        <v>1952.0</v>
       </c>
       <c r="D62" t="n">
         <v>333.0</v>
@@ -1325,7 +1325,7 @@
         <v>1309.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2438.0</v>
+        <v>2439.0</v>
       </c>
     </row>
     <row r="64">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="D87" t="n">
         <v>265.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>213.0</v>
+        <v>216.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1198.0</v>
+        <v>1201.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -695,7 +695,7 @@
         <v>479.0</v>
       </c>
       <c r="D18" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
     </row>
     <row r="19">
@@ -720,10 +720,10 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="D20" t="n">
-        <v>307.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="21">
@@ -737,7 +737,7 @@
         <v>467.0</v>
       </c>
       <c r="D21" t="n">
-        <v>527.0</v>
+        <v>529.0</v>
       </c>
     </row>
     <row r="22">
@@ -776,10 +776,10 @@
         <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="D24" t="n">
-        <v>369.0</v>
+        <v>370.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>765.0</v>
       </c>
       <c r="D25" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="26">
@@ -1003,7 +1003,7 @@
         <v>123.0</v>
       </c>
       <c r="D40" t="n">
-        <v>848.0</v>
+        <v>849.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>171.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2099.0</v>
+        <v>2106.0</v>
       </c>
     </row>
     <row r="42">
@@ -1045,7 +1045,7 @@
         <v>106.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3948.0</v>
+        <v>3953.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>2802.0</v>
+        <v>2803.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>8.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1402.0</v>
+        <v>1410.0</v>
       </c>
     </row>
     <row r="47">
@@ -1143,7 +1143,7 @@
         <v>576.0</v>
       </c>
       <c r="D50" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="51">
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>228.0</v>
+        <v>229.0</v>
       </c>
       <c r="D52" t="n">
         <v>56.0</v>
@@ -1269,7 +1269,7 @@
         <v>692.0</v>
       </c>
       <c r="D59" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="60">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2007.0</v>
+        <v>2014.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12061.0</v>
+        <v>12077.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1952.0</v>
+        <v>1984.0</v>
       </c>
       <c r="D62" t="n">
         <v>333.0</v>
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1309.0</v>
+        <v>1311.0</v>
       </c>
       <c r="D63" t="n">
         <v>2439.0</v>
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1314.0</v>
+        <v>1315.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1047.0</v>
+        <v>1048.0</v>
       </c>
     </row>
     <row r="66">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>434.0</v>
+        <v>435.0</v>
       </c>
       <c r="D87" t="n">
         <v>265.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>253.0</v>
+        <v>254.0</v>
       </c>
       <c r="D89" t="n">
         <v>105.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>786.0</v>
+        <v>787.0</v>
       </c>
       <c r="D96" t="n">
-        <v>425.0</v>
+        <v>426.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>479.0</v>
+        <v>504.0</v>
       </c>
       <c r="D18" t="n">
         <v>242.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>467.0</v>
+        <v>491.0</v>
       </c>
       <c r="D21" t="n">
         <v>529.0</v>
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>765.0</v>
+        <v>769.0</v>
       </c>
       <c r="D25" t="n">
         <v>312.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="D89" t="n">
         <v>105.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>216.0</v>
+        <v>222.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1201.0</v>
+        <v>1202.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1773,7 +1773,7 @@
         <v>146.0</v>
       </c>
       <c r="D95" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>939.0</v>
+        <v>941.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="D5" t="n">
         <v>114.0</v>
@@ -835,7 +835,7 @@
         <v>233.0</v>
       </c>
       <c r="D28" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="29">
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="D30" t="n">
         <v>146.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>717.0</v>
+        <v>719.0</v>
       </c>
       <c r="D56" t="n">
         <v>434.0</v>
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D57" t="n">
         <v>156.0</v>
@@ -1283,7 +1283,7 @@
         <v>720.0</v>
       </c>
       <c r="D60" t="n">
-        <v>833.0</v>
+        <v>834.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2014.0</v>
+        <v>2015.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12077.0</v>
+        <v>12097.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1984.0</v>
+        <v>1990.0</v>
       </c>
       <c r="D62" t="n">
         <v>333.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1311.0</v>
+        <v>1314.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2439.0</v>
+        <v>2440.0</v>
       </c>
     </row>
     <row r="64">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
       <c r="D100" t="n">
         <v>143.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>822.0</v>
+        <v>836.0</v>
       </c>
       <c r="D31" t="n">
         <v>55.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>287.0</v>
+        <v>292.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,10 +902,10 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>304.0</v>
+        <v>308.0</v>
       </c>
       <c r="D33" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="34">
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5307.0</v>
+        <v>5355.0</v>
       </c>
       <c r="D34" t="n">
-        <v>203.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="35">
@@ -930,10 +930,10 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>838.0</v>
+        <v>861.0</v>
       </c>
       <c r="D35" t="n">
-        <v>82.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="36">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="D40" t="n">
-        <v>849.0</v>
+        <v>851.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>171.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2106.0</v>
+        <v>2108.0</v>
       </c>
     </row>
     <row r="42">
@@ -1031,7 +1031,7 @@
         <v>397.0</v>
       </c>
       <c r="D42" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="43">
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3953.0</v>
+        <v>3955.0</v>
       </c>
     </row>
     <row r="44">
@@ -1087,7 +1087,7 @@
         <v>8.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1410.0</v>
+        <v>1413.0</v>
       </c>
     </row>
     <row r="47">
@@ -1143,7 +1143,7 @@
         <v>576.0</v>
       </c>
       <c r="D50" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="51">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="D58" t="n">
         <v>1.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>692.0</v>
+        <v>693.0</v>
       </c>
       <c r="D59" t="n">
         <v>133.0</v>
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1990.0</v>
+        <v>1996.0</v>
       </c>
       <c r="D62" t="n">
         <v>333.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1314.0</v>
+        <v>1317.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2440.0</v>
+        <v>2441.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1315.0</v>
+        <v>1320.0</v>
       </c>
       <c r="D65" t="n">
         <v>1048.0</v>
@@ -1899,7 +1899,7 @@
         <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>303.0</v>
+        <v>304.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="D22" t="n">
         <v>291.0</v>
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="D23" t="n">
-        <v>223.0</v>
+        <v>225.0</v>
       </c>
     </row>
     <row r="24">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>397.0</v>
+        <v>398.0</v>
       </c>
       <c r="D42" t="n">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="43">
@@ -1140,10 +1140,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="D50" t="n">
-        <v>74.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="51">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2015.0</v>
+        <v>2019.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12097.0</v>
+        <v>12116.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1317.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2441.0</v>
+        <v>2442.0</v>
       </c>
     </row>
     <row r="64">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>428.0</v>
+        <v>430.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>765.0</v>
+        <v>766.0</v>
       </c>
       <c r="D91" t="n">
         <v>18.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1202.0</v>
+        <v>1203.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>189.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="D100" t="n">
         <v>143.0</v>
@@ -1899,7 +1899,7 @@
         <v>118.0</v>
       </c>
       <c r="D104" t="n">
-        <v>304.0</v>
+        <v>305.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>941.0</v>
+        <v>943.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -499,7 +499,7 @@
         <v>179.0</v>
       </c>
       <c r="D4" t="n">
-        <v>331.0</v>
+        <v>332.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="D5" t="n">
         <v>114.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>354.0</v>
+        <v>356.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1185,7 +1185,7 @@
         <v>99.0</v>
       </c>
       <c r="D53" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="54">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>411.0</v>
+        <v>412.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>719.0</v>
+        <v>721.0</v>
       </c>
       <c r="D56" t="n">
         <v>434.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>32.0</v>
+        <v>34.0</v>
       </c>
       <c r="D58" t="n">
         <v>1.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>693.0</v>
+        <v>697.0</v>
       </c>
       <c r="D59" t="n">
         <v>133.0</v>
@@ -1283,7 +1283,7 @@
         <v>720.0</v>
       </c>
       <c r="D60" t="n">
-        <v>834.0</v>
+        <v>836.0</v>
       </c>
     </row>
     <row r="61">
@@ -1297,7 +1297,7 @@
         <v>2019.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12116.0</v>
+        <v>12136.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1996.0</v>
+        <v>2028.0</v>
       </c>
       <c r="D62" t="n">
         <v>333.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1317.0</v>
+        <v>1319.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2442.0</v>
+        <v>2447.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="D64" t="n">
         <v>23.0</v>
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1320.0</v>
+        <v>1321.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1048.0</v>
+        <v>1054.0</v>
       </c>
     </row>
     <row r="66">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>435.0</v>
+        <v>437.0</v>
       </c>
       <c r="D87" t="n">
         <v>265.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1203.0</v>
+        <v>1205.0</v>
       </c>
       <c r="D93" t="n">
         <v>39.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>787.0</v>
+        <v>790.0</v>
       </c>
       <c r="D96" t="n">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>504.0</v>
+        <v>555.0</v>
       </c>
       <c r="D18" t="n">
-        <v>242.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         <v>74.0</v>
       </c>
       <c r="D20" t="n">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>491.0</v>
+        <v>513.0</v>
       </c>
       <c r="D21" t="n">
-        <v>529.0</v>
+        <v>531.0</v>
       </c>
     </row>
     <row r="22">
@@ -765,7 +765,7 @@
         <v>3.0</v>
       </c>
       <c r="D23" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
     </row>
     <row r="24">
@@ -779,7 +779,7 @@
         <v>75.0</v>
       </c>
       <c r="D24" t="n">
-        <v>370.0</v>
+        <v>372.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>769.0</v>
+        <v>774.0</v>
       </c>
       <c r="D25" t="n">
         <v>312.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1283,7 +1283,7 @@
         <v>720.0</v>
       </c>
       <c r="D60" t="n">
-        <v>836.0</v>
+        <v>837.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2019.0</v>
+        <v>2020.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12136.0</v>
+        <v>12154.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1319.0</v>
+        <v>1331.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2447.0</v>
+        <v>2448.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1321.0</v>
+        <v>1322.0</v>
       </c>
       <c r="D65" t="n">
         <v>1054.0</v>
@@ -1644,7 +1644,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D86" t="n">
         <v>0.0</v>
@@ -1745,7 +1745,7 @@
         <v>1205.0</v>
       </c>
       <c r="D93" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="94">
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>790.0</v>
+        <v>791.0</v>
       </c>
       <c r="D96" t="n">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>561.0</v>
+        <v>562.0</v>
       </c>
       <c r="D97" t="n">
         <v>134.0</v>
@@ -1843,7 +1843,7 @@
         <v>200.0</v>
       </c>
       <c r="D100" t="n">
-        <v>143.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="101">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1086.0</v>
+        <v>1092.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2131.0</v>
+        <v>2142.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1065.0</v>
+        <v>1066.0</v>
       </c>
     </row>
     <row r="8">
@@ -1392,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
       <c r="D68" t="n">
         <v>184.0</v>
@@ -1406,10 +1406,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="D69" t="n">
-        <v>94.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="70">
@@ -1462,10 +1462,10 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>285.0</v>
+        <v>289.0</v>
       </c>
       <c r="D73" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="74">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>437.0</v>
+        <v>438.0</v>
       </c>
       <c r="D87" t="n">
         <v>265.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>223.0</v>
+        <v>227.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1205.0</v>
+        <v>1207.0</v>
       </c>
       <c r="D93" t="n">
         <v>40.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="D95" t="n">
         <v>209.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -152,9 +152,6 @@
     <t>Parma</t>
   </si>
   <si>
-    <t>Piacenza</t>
-  </si>
-  <si>
     <t>Ravenna</t>
   </si>
   <si>
@@ -228,6 +225,9 @@
   </si>
   <si>
     <t>Monza e della brianza</t>
+  </si>
+  <si>
+    <t>Pavia</t>
   </si>
   <si>
     <t>Sondrio</t>
@@ -681,7 +681,7 @@
         <v>9206.0</v>
       </c>
       <c r="D17" t="n">
-        <v>891.0</v>
+        <v>894.0</v>
       </c>
     </row>
     <row r="18">
@@ -720,7 +720,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="D20" t="n">
         <v>310.0</v>
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>513.0</v>
+        <v>272.0</v>
       </c>
       <c r="D21" t="n">
-        <v>531.0</v>
+        <v>503.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="D22" t="n">
-        <v>291.0</v>
+        <v>254.0</v>
       </c>
     </row>
     <row r="23">
@@ -762,10 +762,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="n">
-        <v>3.0</v>
+        <v>75.0</v>
       </c>
       <c r="D23" t="n">
-        <v>226.0</v>
+        <v>372.0</v>
       </c>
     </row>
     <row r="24">
@@ -776,10 +776,10 @@
         <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>75.0</v>
+        <v>119.0</v>
       </c>
       <c r="D24" t="n">
-        <v>372.0</v>
+        <v>276.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,24 +790,24 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>774.0</v>
+        <v>25.0</v>
       </c>
       <c r="D25" t="n">
-        <v>312.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>25.0</v>
+        <v>147.0</v>
       </c>
       <c r="D26" t="n">
-        <v>78.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="27">
@@ -818,10 +818,10 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>147.0</v>
+        <v>233.0</v>
       </c>
       <c r="D27" t="n">
-        <v>12.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="28">
@@ -832,10 +832,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>233.0</v>
+        <v>150.0</v>
       </c>
       <c r="D28" t="n">
-        <v>145.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="29">
@@ -846,24 +846,24 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>150.0</v>
+        <v>148.0</v>
       </c>
       <c r="D29" t="n">
-        <v>6.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>148.0</v>
+        <v>836.0</v>
       </c>
       <c r="D30" t="n">
-        <v>146.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="31">
@@ -874,10 +874,10 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>836.0</v>
+        <v>292.0</v>
       </c>
       <c r="D31" t="n">
-        <v>55.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="32">
@@ -888,10 +888,10 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>292.0</v>
+        <v>308.0</v>
       </c>
       <c r="D32" t="n">
-        <v>9.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="33">
@@ -902,10 +902,10 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>308.0</v>
+        <v>5355.0</v>
       </c>
       <c r="D33" t="n">
-        <v>49.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="34">
@@ -916,24 +916,24 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5355.0</v>
+        <v>861.0</v>
       </c>
       <c r="D34" t="n">
-        <v>209.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>861.0</v>
+        <v>14.0</v>
       </c>
       <c r="D35" t="n">
-        <v>85.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -944,10 +944,10 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>14.0</v>
+        <v>239.0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="37">
@@ -958,10 +958,10 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>239.0</v>
+        <v>4.0</v>
       </c>
       <c r="D37" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -972,24 +972,24 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>4.0</v>
+        <v>1025.0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>1025.0</v>
+        <v>124.0</v>
       </c>
       <c r="D39" t="n">
-        <v>14.0</v>
+        <v>851.0</v>
       </c>
     </row>
     <row r="40">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>124.0</v>
+        <v>171.0</v>
       </c>
       <c r="D40" t="n">
-        <v>851.0</v>
+        <v>2108.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>171.0</v>
+        <v>402.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2108.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>400.0</v>
+        <v>109.0</v>
       </c>
       <c r="D42" t="n">
-        <v>38.0</v>
+        <v>3955.0</v>
       </c>
     </row>
     <row r="43">
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>109.0</v>
+        <v>29.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3955.0</v>
+        <v>32.0</v>
       </c>
     </row>
     <row r="44">
@@ -1056,10 +1056,10 @@
         <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>29.0</v>
+        <v>50.0</v>
       </c>
       <c r="D44" t="n">
-        <v>32.0</v>
+        <v>24279.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>2803.0</v>
+        <v>1413.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>8.0</v>
+        <v>681.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1413.0</v>
+        <v>1873.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,10 +1098,10 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="D47" t="n">
-        <v>77.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="48">
@@ -1112,10 +1112,10 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1.0</v>
+        <v>1254.0</v>
       </c>
       <c r="D48" t="n">
-        <v>11.0</v>
+        <v>3866.0</v>
       </c>
     </row>
     <row r="49">
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>577.0</v>
+        <v>738.0</v>
       </c>
       <c r="D50" t="n">
         <v>73.0</v>
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>34.0</v>
+        <v>587.0</v>
       </c>
       <c r="D58" t="n">
-        <v>1.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>697.0</v>
+        <v>715.0</v>
       </c>
       <c r="D59" t="n">
         <v>133.0</v>
@@ -1283,7 +1283,7 @@
         <v>720.0</v>
       </c>
       <c r="D60" t="n">
-        <v>837.0</v>
+        <v>839.0</v>
       </c>
     </row>
     <row r="61">
@@ -1297,7 +1297,7 @@
         <v>2020.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12154.0</v>
+        <v>12184.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2028.0</v>
+        <v>2851.0</v>
       </c>
       <c r="D62" t="n">
-        <v>333.0</v>
+        <v>633.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1331.0</v>
+        <v>1332.0</v>
       </c>
       <c r="D63" t="n">
         <v>2448.0</v>
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1322.0</v>
+        <v>1474.0</v>
       </c>
       <c r="D65" t="n">
         <v>1054.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>943.0</v>
+        <v>944.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -989,7 +989,7 @@
         <v>124.0</v>
       </c>
       <c r="D39" t="n">
-        <v>851.0</v>
+        <v>854.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>171.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2108.0</v>
+        <v>2111.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>402.0</v>
+        <v>409.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>109.0</v>
+        <v>113.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3955.0</v>
+        <v>3957.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>50.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24279.0</v>
+        <v>24304.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1413.0</v>
+        <v>1418.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>681.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1873.0</v>
+        <v>1875.0</v>
       </c>
     </row>
     <row r="47">
@@ -1112,10 +1112,10 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1254.0</v>
+        <v>1262.0</v>
       </c>
       <c r="D48" t="n">
-        <v>3866.0</v>
+        <v>3884.0</v>
       </c>
     </row>
     <row r="49">
@@ -1129,7 +1129,7 @@
         <v>22.0</v>
       </c>
       <c r="D49" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="50">
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>721.0</v>
+        <v>727.0</v>
       </c>
       <c r="D56" t="n">
         <v>434.0</v>
@@ -1241,7 +1241,7 @@
         <v>162.0</v>
       </c>
       <c r="D57" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="58">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2851.0</v>
+        <v>2855.0</v>
       </c>
       <c r="D62" t="n">
         <v>633.0</v>
@@ -1325,7 +1325,7 @@
         <v>1332.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2448.0</v>
+        <v>2450.0</v>
       </c>
     </row>
     <row r="64">
@@ -1689,7 +1689,7 @@
         <v>255.0</v>
       </c>
       <c r="D89" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="90">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>227.0</v>
+        <v>231.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>944.0</v>
+        <v>945.0</v>
       </c>
       <c r="D2" t="n">
         <v>79.0</v>
@@ -499,7 +499,7 @@
         <v>179.0</v>
       </c>
       <c r="D4" t="n">
-        <v>332.0</v>
+        <v>334.0</v>
       </c>
     </row>
     <row r="5">
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>525.0</v>
+        <v>532.0</v>
       </c>
       <c r="D8" t="n">
         <v>157.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>265.0</v>
+        <v>268.0</v>
       </c>
       <c r="D9" t="n">
-        <v>559.0</v>
+        <v>564.0</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>469.0</v>
+        <v>470.0</v>
       </c>
       <c r="D54" t="n">
         <v>128.0</v>
@@ -1227,7 +1227,7 @@
         <v>727.0</v>
       </c>
       <c r="D56" t="n">
-        <v>434.0</v>
+        <v>435.0</v>
       </c>
     </row>
     <row r="57">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>715.0</v>
+        <v>716.0</v>
       </c>
       <c r="D59" t="n">
         <v>133.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2020.0</v>
+        <v>2023.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12184.0</v>
+        <v>12202.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2855.0</v>
       </c>
       <c r="D62" t="n">
-        <v>633.0</v>
+        <v>634.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1332.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2450.0</v>
+        <v>2452.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1474.0</v>
+        <v>1483.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1054.0</v>
+        <v>1056.0</v>
       </c>
     </row>
     <row r="66">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="D89" t="n">
         <v>106.0</v>
@@ -1714,10 +1714,10 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>766.0</v>
+        <v>767.0</v>
       </c>
       <c r="D91" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="92">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1207.0</v>
+        <v>1210.0</v>
       </c>
       <c r="D93" t="n">
         <v>40.0</v>
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>562.0</v>
+        <v>565.0</v>
       </c>
       <c r="D97" t="n">
-        <v>134.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="98">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
       <c r="D100" t="n">
         <v>146.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -723,7 +723,7 @@
         <v>75.0</v>
       </c>
       <c r="D20" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
     </row>
     <row r="21">
@@ -765,7 +765,7 @@
         <v>75.0</v>
       </c>
       <c r="D23" t="n">
-        <v>372.0</v>
+        <v>373.0</v>
       </c>
     </row>
     <row r="24">
@@ -793,7 +793,7 @@
         <v>25.0</v>
       </c>
       <c r="D25" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="26">
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="D39" t="n">
         <v>854.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>356.0</v>
+        <v>357.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>229.0</v>
+        <v>231.0</v>
       </c>
       <c r="D52" t="n">
         <v>56.0</v>
@@ -1196,10 +1196,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>470.0</v>
+        <v>471.0</v>
       </c>
       <c r="D54" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="55">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>716.0</v>
+        <v>719.0</v>
       </c>
       <c r="D59" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>720.0</v>
+        <v>722.0</v>
       </c>
       <c r="D60" t="n">
         <v>839.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2023.0</v>
+        <v>2024.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12202.0</v>
+        <v>12217.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2855.0</v>
+        <v>2857.0</v>
       </c>
       <c r="D62" t="n">
-        <v>634.0</v>
+        <v>635.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1332.0</v>
+        <v>1334.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2452.0</v>
+        <v>2454.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1483.0</v>
+        <v>1486.0</v>
       </c>
       <c r="D65" t="n">
         <v>1056.0</v>
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
       <c r="D87" t="n">
         <v>265.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>430.0</v>
+        <v>431.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>767.0</v>
+        <v>768.0</v>
       </c>
       <c r="D91" t="n">
         <v>19.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>232.0</v>
+        <v>237.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1210.0</v>
+        <v>1213.0</v>
       </c>
       <c r="D93" t="n">
         <v>40.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>73.0</v>
+        <v>75.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1773,7 +1773,7 @@
         <v>147.0</v>
       </c>
       <c r="D95" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
     </row>
     <row r="96">
@@ -1787,7 +1787,7 @@
         <v>791.0</v>
       </c>
       <c r="D96" t="n">
-        <v>428.0</v>
+        <v>429.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>565.0</v>
+        <v>567.0</v>
       </c>
       <c r="D97" t="n">
         <v>136.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -471,7 +471,7 @@
         <v>945.0</v>
       </c>
       <c r="D2" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1092.0</v>
+        <v>1098.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2142.0</v>
+        <v>2147.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1066.0</v>
+        <v>1068.0</v>
       </c>
     </row>
     <row r="8">
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="D28" t="n">
         <v>6.0</v>
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>410.0</v>
+        <v>412.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="D42" t="n">
         <v>3957.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>727.0</v>
+        <v>729.0</v>
       </c>
       <c r="D56" t="n">
-        <v>435.0</v>
+        <v>436.0</v>
       </c>
     </row>
     <row r="57">
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="D58" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>719.0</v>
+        <v>722.0</v>
       </c>
       <c r="D59" t="n">
         <v>135.0</v>
@@ -1283,7 +1283,7 @@
         <v>722.0</v>
       </c>
       <c r="D60" t="n">
-        <v>839.0</v>
+        <v>843.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2025.0</v>
+        <v>2027.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12234.0</v>
+        <v>12263.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2873.0</v>
+        <v>2875.0</v>
       </c>
       <c r="D62" t="n">
-        <v>636.0</v>
+        <v>637.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1336.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2454.0</v>
+        <v>2455.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1486.0</v>
+        <v>1493.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1056.0</v>
+        <v>1060.0</v>
       </c>
     </row>
     <row r="66">
@@ -1395,7 +1395,7 @@
         <v>203.0</v>
       </c>
       <c r="D68" t="n">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="69">
@@ -1409,7 +1409,7 @@
         <v>85.0</v>
       </c>
       <c r="D69" t="n">
-        <v>97.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="70">
@@ -1434,7 +1434,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="D71" t="n">
         <v>0.0</v>
@@ -1462,7 +1462,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
       <c r="D73" t="n">
         <v>41.0</v>
@@ -1812,7 +1812,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="D98" t="n">
         <v>42.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>205.0</v>
+        <v>206.0</v>
       </c>
       <c r="D100" t="n">
         <v>146.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>555.0</v>
+        <v>562.0</v>
       </c>
       <c r="D18" t="n">
         <v>245.0</v>
@@ -723,7 +723,7 @@
         <v>76.0</v>
       </c>
       <c r="D20" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>273.0</v>
+        <v>276.0</v>
       </c>
       <c r="D21" t="n">
         <v>503.0</v>
@@ -1185,7 +1185,7 @@
         <v>99.0</v>
       </c>
       <c r="D53" t="n">
-        <v>162.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="54">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>722.0</v>
+        <v>732.0</v>
       </c>
       <c r="D59" t="n">
         <v>135.0</v>
@@ -1297,7 +1297,7 @@
         <v>2027.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12263.0</v>
+        <v>12264.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1336.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2455.0</v>
+        <v>2457.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>511.0</v>
+        <v>512.0</v>
       </c>
     </row>
     <row r="67">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1787,7 +1787,7 @@
         <v>791.0</v>
       </c>
       <c r="D96" t="n">
-        <v>429.0</v>
+        <v>431.0</v>
       </c>
     </row>
     <row r="97">
@@ -1896,7 +1896,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="D104" t="n">
         <v>305.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>945.0</v>
+        <v>948.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>446.0</v>
+        <v>447.0</v>
       </c>
       <c r="D3" t="n">
         <v>65.0</v>
@@ -499,7 +499,7 @@
         <v>179.0</v>
       </c>
       <c r="D4" t="n">
-        <v>334.0</v>
+        <v>336.0</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1098.0</v>
+        <v>1100.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2147.0</v>
+        <v>2149.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1068.0</v>
+        <v>1069.0</v>
       </c>
     </row>
     <row r="8">
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>562.0</v>
+        <v>577.0</v>
       </c>
       <c r="D18" t="n">
         <v>245.0</v>
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>276.0</v>
+        <v>288.0</v>
       </c>
       <c r="D21" t="n">
-        <v>503.0</v>
+        <v>506.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="D22" t="n">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
     </row>
     <row r="23">
@@ -776,7 +776,7 @@
         <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="D24" t="n">
         <v>276.0</v>
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="D26" t="n">
         <v>12.0</v>
@@ -849,7 +849,7 @@
         <v>150.0</v>
       </c>
       <c r="D29" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="30">
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -975,7 +975,7 @@
         <v>1025.0</v>
       </c>
       <c r="D38" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="39">
@@ -986,10 +986,10 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="D39" t="n">
-        <v>854.0</v>
+        <v>856.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>171.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2111.0</v>
+        <v>2115.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>412.0</v>
+        <v>417.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3957.0</v>
+        <v>3963.0</v>
       </c>
     </row>
     <row r="43">
@@ -1045,7 +1045,7 @@
         <v>29.0</v>
       </c>
       <c r="D43" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="44">
@@ -1059,7 +1059,7 @@
         <v>50.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24304.0</v>
+        <v>24309.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1418.0</v>
+        <v>1424.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>681.0</v>
+        <v>683.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1875.0</v>
+        <v>1878.0</v>
       </c>
     </row>
     <row r="47">
@@ -1112,7 +1112,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1262.0</v>
+        <v>1269.0</v>
       </c>
       <c r="D48" t="n">
         <v>3884.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1171,7 +1171,7 @@
         <v>231.0</v>
       </c>
       <c r="D52" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="53">
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>471.0</v>
+        <v>473.0</v>
       </c>
       <c r="D54" t="n">
         <v>130.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>412.0</v>
+        <v>413.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>729.0</v>
+        <v>730.0</v>
       </c>
       <c r="D56" t="n">
         <v>436.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>588.0</v>
+        <v>591.0</v>
       </c>
       <c r="D58" t="n">
         <v>131.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>732.0</v>
+        <v>735.0</v>
       </c>
       <c r="D59" t="n">
-        <v>135.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>722.0</v>
       </c>
       <c r="D60" t="n">
-        <v>843.0</v>
+        <v>844.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2027.0</v>
+        <v>2036.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12264.0</v>
+        <v>12331.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2875.0</v>
+        <v>2880.0</v>
       </c>
       <c r="D62" t="n">
-        <v>637.0</v>
+        <v>643.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1336.0</v>
+        <v>1341.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2457.0</v>
+        <v>2465.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1493.0</v>
+        <v>1503.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1060.0</v>
+        <v>1065.0</v>
       </c>
     </row>
     <row r="66">
@@ -1395,7 +1395,7 @@
         <v>203.0</v>
       </c>
       <c r="D68" t="n">
-        <v>186.0</v>
+        <v>190.0</v>
       </c>
     </row>
     <row r="69">
@@ -1462,7 +1462,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>290.0</v>
+        <v>292.0</v>
       </c>
       <c r="D73" t="n">
         <v>41.0</v>
@@ -1479,7 +1479,7 @@
         <v>48.0</v>
       </c>
       <c r="D74" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="75">
@@ -1490,10 +1490,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>659.0</v>
+        <v>669.0</v>
       </c>
       <c r="D75" t="n">
-        <v>425.0</v>
+        <v>428.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>441.0</v>
+        <v>449.0</v>
       </c>
       <c r="D76" t="n">
-        <v>424.0</v>
+        <v>433.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>1676.0</v>
+        <v>1711.0</v>
       </c>
       <c r="D77" t="n">
-        <v>509.0</v>
+        <v>519.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,10 +1532,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>309.0</v>
+        <v>315.0</v>
       </c>
       <c r="D78" t="n">
-        <v>479.0</v>
+        <v>485.0</v>
       </c>
     </row>
     <row r="79">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>440.0</v>
+        <v>443.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="D89" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="90">
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="D90" t="n">
         <v>58.0</v>
@@ -1714,10 +1714,10 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>768.0</v>
+        <v>775.0</v>
       </c>
       <c r="D91" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="92">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>242.0</v>
+        <v>247.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1214.0</v>
+        <v>1222.0</v>
       </c>
       <c r="D93" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="D95" t="n">
         <v>210.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>791.0</v>
+        <v>794.0</v>
       </c>
       <c r="D96" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>567.0</v>
+        <v>569.0</v>
       </c>
       <c r="D97" t="n">
         <v>136.0</v>
@@ -1899,7 +1899,7 @@
         <v>119.0</v>
       </c>
       <c r="D104" t="n">
-        <v>305.0</v>
+        <v>306.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -821,7 +821,7 @@
         <v>233.0</v>
       </c>
       <c r="D27" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="28">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>591.0</v>
+        <v>592.0</v>
       </c>
       <c r="D58" t="n">
         <v>131.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2036.0</v>
+        <v>2037.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12331.0</v>
+        <v>12350.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1341.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2465.0</v>
+        <v>2467.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>512.0</v>
+        <v>513.0</v>
       </c>
     </row>
     <row r="67">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>775.0</v>
+        <v>776.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>76.0</v>
+        <v>78.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>194.0</v>
+        <v>195.0</v>
       </c>
     </row>
     <row r="100">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>948.0</v>
+        <v>949.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="D3" t="n">
         <v>65.0</v>
@@ -499,7 +499,7 @@
         <v>179.0</v>
       </c>
       <c r="D4" t="n">
-        <v>336.0</v>
+        <v>338.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="D5" t="n">
         <v>114.0</v>
@@ -695,7 +695,7 @@
         <v>577.0</v>
       </c>
       <c r="D18" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
     </row>
     <row r="19">
@@ -737,7 +737,7 @@
         <v>288.0</v>
       </c>
       <c r="D21" t="n">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
     </row>
     <row r="22">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>358.0</v>
+        <v>361.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>231.0</v>
+        <v>234.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>473.0</v>
+        <v>475.0</v>
       </c>
       <c r="D54" t="n">
         <v>130.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>413.0</v>
+        <v>415.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>730.0</v>
+        <v>736.0</v>
       </c>
       <c r="D56" t="n">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
     </row>
     <row r="57">
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="D57" t="n">
         <v>157.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>735.0</v>
+        <v>736.0</v>
       </c>
       <c r="D59" t="n">
-        <v>137.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="60">
@@ -1297,7 +1297,7 @@
         <v>2037.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12350.0</v>
+        <v>12363.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2880.0</v>
+        <v>2882.0</v>
       </c>
       <c r="D62" t="n">
-        <v>643.0</v>
+        <v>644.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1341.0</v>
+        <v>1342.0</v>
       </c>
       <c r="D63" t="n">
         <v>2467.0</v>
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1503.0</v>
+        <v>1514.0</v>
       </c>
       <c r="D65" t="n">
         <v>1065.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>248.0</v>
+        <v>252.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>794.0</v>
+        <v>797.0</v>
       </c>
       <c r="D96" t="n">
         <v>432.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>569.0</v>
+        <v>570.0</v>
       </c>
       <c r="D97" t="n">
         <v>136.0</v>
@@ -1812,7 +1812,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="D98" t="n">
         <v>42.0</v>
@@ -1899,7 +1899,7 @@
         <v>119.0</v>
       </c>
       <c r="D104" t="n">
-        <v>306.0</v>
+        <v>307.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>288.0</v>
+        <v>297.0</v>
       </c>
       <c r="D21" t="n">
         <v>508.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1222.0</v>
+        <v>1224.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -622,10 +622,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>818.0</v>
+        <v>846.0</v>
       </c>
       <c r="D13" t="n">
-        <v>315.0</v>
+        <v>321.0</v>
       </c>
     </row>
     <row r="14">
@@ -636,10 +636,10 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>532.0</v>
+        <v>557.0</v>
       </c>
       <c r="D14" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="15">
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>611.0</v>
+        <v>639.0</v>
       </c>
       <c r="D15" t="n">
-        <v>170.0</v>
+        <v>173.0</v>
       </c>
     </row>
     <row r="16">
@@ -664,10 +664,10 @@
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="D16" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="17">
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9206.0</v>
+        <v>9232.0</v>
       </c>
       <c r="D17" t="n">
-        <v>894.0</v>
+        <v>902.0</v>
       </c>
     </row>
     <row r="18">
@@ -989,7 +989,7 @@
         <v>126.0</v>
       </c>
       <c r="D39" t="n">
-        <v>856.0</v>
+        <v>859.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>171.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2115.0</v>
+        <v>2118.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>417.0</v>
+        <v>421.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1031,7 +1031,7 @@
         <v>115.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3963.0</v>
+        <v>3965.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>50.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24309.0</v>
+        <v>24310.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1424.0</v>
+        <v>1429.0</v>
       </c>
     </row>
     <row r="46">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>592.0</v>
+        <v>598.0</v>
       </c>
       <c r="D58" t="n">
         <v>131.0</v>
@@ -1283,7 +1283,7 @@
         <v>722.0</v>
       </c>
       <c r="D60" t="n">
-        <v>844.0</v>
+        <v>845.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2037.0</v>
+        <v>2043.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12363.0</v>
+        <v>12389.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1342.0</v>
+        <v>1345.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2467.0</v>
+        <v>2470.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1514.0</v>
+        <v>1523.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1065.0</v>
+        <v>1069.0</v>
       </c>
     </row>
     <row r="66">
@@ -1899,7 +1899,7 @@
         <v>119.0</v>
       </c>
       <c r="D104" t="n">
-        <v>307.0</v>
+        <v>308.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>421.0</v>
+        <v>427.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
       <c r="D42" t="n">
         <v>3965.0</v>
@@ -1056,7 +1056,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="D44" t="n">
         <v>24310.0</v>
@@ -1084,7 +1084,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>683.0</v>
+        <v>690.0</v>
       </c>
       <c r="D46" t="n">
         <v>1878.0</v>
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>738.0</v>
+        <v>739.0</v>
       </c>
       <c r="D50" t="n">
         <v>73.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>475.0</v>
+        <v>476.0</v>
       </c>
       <c r="D54" t="n">
         <v>130.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>598.0</v>
+        <v>601.0</v>
       </c>
       <c r="D58" t="n">
         <v>131.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>736.0</v>
+        <v>739.0</v>
       </c>
       <c r="D59" t="n">
         <v>139.0</v>
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2882.0</v>
+        <v>2883.0</v>
       </c>
       <c r="D62" t="n">
         <v>644.0</v>
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1345.0</v>
+        <v>1346.0</v>
       </c>
       <c r="D63" t="n">
         <v>2470.0</v>
@@ -1787,7 +1787,7 @@
         <v>797.0</v>
       </c>
       <c r="D96" t="n">
-        <v>432.0</v>
+        <v>434.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>570.0</v>
+        <v>573.0</v>
       </c>
       <c r="D97" t="n">
         <v>136.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -821,7 +821,7 @@
         <v>233.0</v>
       </c>
       <c r="D27" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="28">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>739.0</v>
+        <v>740.0</v>
       </c>
       <c r="D59" t="n">
         <v>139.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2043.0</v>
+        <v>2047.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12389.0</v>
+        <v>12403.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1346.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2470.0</v>
+        <v>2475.0</v>
       </c>
     </row>
     <row r="64">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>444.0</v>
+        <v>445.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="D88" t="n">
         <v>113.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>776.0</v>
+        <v>778.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>252.0</v>
+        <v>255.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1899,7 +1899,7 @@
         <v>119.0</v>
       </c>
       <c r="D104" t="n">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="D26" t="n">
         <v>12.0</v>
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>601.0</v>
+        <v>603.0</v>
       </c>
       <c r="D58" t="n">
         <v>131.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>740.0</v>
+        <v>744.0</v>
       </c>
       <c r="D59" t="n">
         <v>139.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2047.0</v>
+        <v>2049.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12403.0</v>
+        <v>12421.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2883.0</v>
       </c>
       <c r="D62" t="n">
-        <v>644.0</v>
+        <v>647.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1346.0</v>
+        <v>1360.0</v>
       </c>
       <c r="D63" t="n">
         <v>2475.0</v>
@@ -1353,7 +1353,7 @@
         <v>1523.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1069.0</v>
+        <v>1072.0</v>
       </c>
     </row>
     <row r="66">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>513.0</v>
+        <v>516.0</v>
       </c>
     </row>
     <row r="67">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>445.0</v>
+        <v>447.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>433.0</v>
+        <v>434.0</v>
       </c>
       <c r="D88" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="89">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>778.0</v>
+        <v>779.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1224.0</v>
+        <v>1225.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="D95" t="n">
         <v>210.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>195.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="100">
@@ -1896,10 +1896,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
       <c r="D104" t="n">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -723,7 +723,7 @@
         <v>76.0</v>
       </c>
       <c r="D20" t="n">
-        <v>312.0</v>
+        <v>316.0</v>
       </c>
     </row>
     <row r="21">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>361.0</v>
+        <v>362.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>234.0</v>
+        <v>235.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>476.0</v>
+        <v>478.0</v>
       </c>
       <c r="D54" t="n">
         <v>130.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>415.0</v>
+        <v>417.0</v>
       </c>
       <c r="D55" t="n">
         <v>142.0</v>
@@ -1280,10 +1280,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>722.0</v>
+        <v>723.0</v>
       </c>
       <c r="D60" t="n">
-        <v>845.0</v>
+        <v>846.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2049.0</v>
+        <v>2050.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12421.0</v>
+        <v>12433.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2883.0</v>
       </c>
       <c r="D62" t="n">
-        <v>647.0</v>
+        <v>649.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1360.0</v>
+        <v>1362.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2475.0</v>
+        <v>2477.0</v>
       </c>
     </row>
     <row r="64">
@@ -1353,7 +1353,7 @@
         <v>1523.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1072.0</v>
+        <v>1073.0</v>
       </c>
     </row>
     <row r="66">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>779.0</v>
+        <v>780.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>257.0</v>
+        <v>262.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1225.0</v>
+        <v>1227.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>797.0</v>
+        <v>799.0</v>
       </c>
       <c r="D96" t="n">
-        <v>434.0</v>
+        <v>436.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>434.0</v>
+        <v>435.0</v>
       </c>
       <c r="D88" t="n">
         <v>115.0</v>
@@ -1703,7 +1703,7 @@
         <v>163.0</v>
       </c>
       <c r="D90" t="n">
-        <v>58.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="91">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>780.0</v>
+        <v>781.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1227.0</v>
+        <v>1230.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1100.0</v>
+        <v>1108.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2149.0</v>
+        <v>2151.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1069.0</v>
+        <v>1070.0</v>
       </c>
     </row>
     <row r="8">
@@ -625,7 +625,7 @@
         <v>846.0</v>
       </c>
       <c r="D13" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
     </row>
     <row r="14">
@@ -639,7 +639,7 @@
         <v>557.0</v>
       </c>
       <c r="D14" t="n">
-        <v>107.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="15">
@@ -972,7 +972,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>1025.0</v>
+        <v>1027.0</v>
       </c>
       <c r="D38" t="n">
         <v>15.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>362.0</v>
+        <v>363.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="D53" t="n">
         <v>164.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>478.0</v>
+        <v>480.0</v>
       </c>
       <c r="D54" t="n">
         <v>130.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>603.0</v>
+        <v>606.0</v>
       </c>
       <c r="D58" t="n">
         <v>131.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>744.0</v>
+        <v>745.0</v>
       </c>
       <c r="D59" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>723.0</v>
       </c>
       <c r="D60" t="n">
-        <v>846.0</v>
+        <v>847.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2050.0</v>
+        <v>2051.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12433.0</v>
+        <v>12460.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2883.0</v>
+        <v>2884.0</v>
       </c>
       <c r="D62" t="n">
         <v>649.0</v>
@@ -1325,7 +1325,7 @@
         <v>1362.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2477.0</v>
+        <v>2479.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1523.0</v>
+        <v>1529.0</v>
       </c>
       <c r="D65" t="n">
         <v>1073.0</v>
@@ -1392,10 +1392,10 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>203.0</v>
+        <v>207.0</v>
       </c>
       <c r="D68" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="69">
@@ -1409,7 +1409,7 @@
         <v>85.0</v>
       </c>
       <c r="D69" t="n">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="70">
@@ -1434,7 +1434,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="D71" t="n">
         <v>0.0</v>
@@ -1465,7 +1465,7 @@
         <v>292.0</v>
       </c>
       <c r="D73" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="74">
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>573.0</v>
+        <v>574.0</v>
       </c>
       <c r="D97" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -681,7 +681,7 @@
         <v>9232.0</v>
       </c>
       <c r="D17" t="n">
-        <v>902.0</v>
+        <v>903.0</v>
       </c>
     </row>
     <row r="18">
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>577.0</v>
+        <v>602.0</v>
       </c>
       <c r="D18" t="n">
         <v>246.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>297.0</v>
+        <v>315.0</v>
       </c>
       <c r="D21" t="n">
         <v>508.0</v>
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="D22" t="n">
         <v>256.0</v>
@@ -818,10 +818,10 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="28">
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>150.0</v>
+        <v>153.0</v>
       </c>
       <c r="D29" t="n">
         <v>148.0</v>
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -986,10 +986,10 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="D39" t="n">
-        <v>859.0</v>
+        <v>874.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>171.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2118.0</v>
+        <v>2128.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>427.0</v>
       </c>
       <c r="D41" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>116.0</v>
+        <v>119.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3965.0</v>
+        <v>3968.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>51.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24310.0</v>
+        <v>24315.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1429.0</v>
+        <v>1432.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>690.0</v>
+        <v>698.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1878.0</v>
+        <v>1879.0</v>
       </c>
     </row>
     <row r="47">
@@ -1129,7 +1129,7 @@
         <v>22.0</v>
       </c>
       <c r="D49" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="50">
@@ -1255,7 +1255,7 @@
         <v>606.0</v>
       </c>
       <c r="D58" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="59">
@@ -1269,7 +1269,7 @@
         <v>745.0</v>
       </c>
       <c r="D59" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="60">
@@ -1325,7 +1325,7 @@
         <v>1362.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2479.0</v>
+        <v>2483.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>516.0</v>
+        <v>517.0</v>
       </c>
     </row>
     <row r="67">
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>799.0</v>
+        <v>800.0</v>
       </c>
       <c r="D96" t="n">
         <v>436.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>206.0</v>
+        <v>207.0</v>
       </c>
       <c r="D100" t="n">
         <v>146.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>602.0</v>
+        <v>605.0</v>
       </c>
       <c r="D18" t="n">
-        <v>246.0</v>
+        <v>249.0</v>
       </c>
     </row>
     <row r="19">
@@ -779,7 +779,7 @@
         <v>121.0</v>
       </c>
       <c r="D24" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
     </row>
     <row r="25">
@@ -1210,10 +1210,10 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>417.0</v>
+        <v>418.0</v>
       </c>
       <c r="D55" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="56">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>606.0</v>
+        <v>608.0</v>
       </c>
       <c r="D58" t="n">
         <v>132.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>745.0</v>
+        <v>746.0</v>
       </c>
       <c r="D59" t="n">
         <v>141.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2051.0</v>
+        <v>2056.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12460.0</v>
+        <v>12481.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2884.0</v>
       </c>
       <c r="D62" t="n">
-        <v>649.0</v>
+        <v>652.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1362.0</v>
+        <v>1364.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2483.0</v>
+        <v>2489.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>60.0</v>
       </c>
       <c r="D64" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="65">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>435.0</v>
+        <v>436.0</v>
       </c>
       <c r="D88" t="n">
         <v>115.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>781.0</v>
+        <v>782.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>263.0</v>
+        <v>266.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>800.0</v>
+        <v>802.0</v>
       </c>
       <c r="D96" t="n">
         <v>436.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>574.0</v>
+        <v>575.0</v>
       </c>
       <c r="D97" t="n">
         <v>138.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>608.0</v>
+        <v>612.0</v>
       </c>
       <c r="D58" t="n">
         <v>132.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>723.0</v>
+        <v>724.0</v>
       </c>
       <c r="D60" t="n">
         <v>847.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2056.0</v>
+        <v>2057.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12481.0</v>
+        <v>12502.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1364.0</v>
+        <v>1365.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2489.0</v>
+        <v>2490.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1529.0</v>
+        <v>1531.0</v>
       </c>
       <c r="D65" t="n">
         <v>1073.0</v>
@@ -1630,7 +1630,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="D85" t="n">
         <v>9.0</v>
@@ -1675,7 +1675,7 @@
         <v>436.0</v>
       </c>
       <c r="D88" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1230.0</v>
+        <v>1234.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>782.0</v>
+        <v>783.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>266.0</v>
+        <v>268.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>949.0</v>
+        <v>955.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>448.0</v>
+        <v>449.0</v>
       </c>
       <c r="D3" t="n">
         <v>65.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>179.0</v>
+        <v>183.0</v>
       </c>
       <c r="D4" t="n">
-        <v>338.0</v>
+        <v>340.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,10 +510,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>216.0</v>
+        <v>219.0</v>
       </c>
       <c r="D5" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="6">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>315.0</v>
+        <v>316.0</v>
       </c>
       <c r="D21" t="n">
         <v>508.0</v>
@@ -765,7 +765,7 @@
         <v>75.0</v>
       </c>
       <c r="D23" t="n">
-        <v>373.0</v>
+        <v>375.0</v>
       </c>
     </row>
     <row r="24">
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1185,7 +1185,7 @@
         <v>100.0</v>
       </c>
       <c r="D53" t="n">
-        <v>164.0</v>
+        <v>166.0</v>
       </c>
     </row>
     <row r="54">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>418.0</v>
+        <v>419.0</v>
       </c>
       <c r="D55" t="n">
         <v>143.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>736.0</v>
+        <v>743.0</v>
       </c>
       <c r="D56" t="n">
-        <v>437.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="57">
@@ -1238,10 +1238,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="D57" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="58">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>612.0</v>
+        <v>615.0</v>
       </c>
       <c r="D58" t="n">
         <v>132.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2057.0</v>
+        <v>2062.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12502.0</v>
+        <v>12527.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2884.0</v>
       </c>
       <c r="D62" t="n">
-        <v>652.0</v>
+        <v>653.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1365.0</v>
+        <v>1366.0</v>
       </c>
       <c r="D63" t="n">
         <v>2490.0</v>
@@ -1353,7 +1353,7 @@
         <v>1531.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1073.0</v>
+        <v>1075.0</v>
       </c>
     </row>
     <row r="66">
@@ -1787,7 +1787,7 @@
         <v>802.0</v>
       </c>
       <c r="D96" t="n">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>575.0</v>
+        <v>576.0</v>
       </c>
       <c r="D97" t="n">
         <v>138.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="D28" t="n">
         <v>6.0</v>
@@ -849,7 +849,7 @@
         <v>153.0</v>
       </c>
       <c r="D29" t="n">
-        <v>148.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="30">
@@ -986,10 +986,10 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="D39" t="n">
-        <v>874.0</v>
+        <v>879.0</v>
       </c>
     </row>
     <row r="40">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2128.0</v>
+        <v>2131.0</v>
       </c>
     </row>
     <row r="41">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>119.0</v>
+        <v>123.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3968.0</v>
+        <v>3973.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>51.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24315.0</v>
+        <v>24316.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1432.0</v>
+        <v>1435.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>698.0</v>
+        <v>702.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1879.0</v>
+        <v>1881.0</v>
       </c>
     </row>
     <row r="47">
@@ -1143,7 +1143,7 @@
         <v>739.0</v>
       </c>
       <c r="D50" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>363.0</v>
+        <v>364.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1196,10 +1196,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>480.0</v>
+        <v>481.0</v>
       </c>
       <c r="D54" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="55">
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>615.0</v>
+        <v>616.0</v>
       </c>
       <c r="D58" t="n">
         <v>132.0</v>
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1366.0</v>
+        <v>1386.0</v>
       </c>
       <c r="D63" t="n">
         <v>2490.0</v>
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="D64" t="n">
         <v>24.0</v>
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1531.0</v>
+        <v>1532.0</v>
       </c>
       <c r="D65" t="n">
         <v>1075.0</v>
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>517.0</v>
+        <v>519.0</v>
       </c>
     </row>
     <row r="67">
@@ -1787,7 +1787,7 @@
         <v>802.0</v>
       </c>
       <c r="D96" t="n">
-        <v>437.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="97">
@@ -1801,7 +1801,7 @@
         <v>576.0</v>
       </c>
       <c r="D97" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="98">
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="D100" t="n">
         <v>146.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>605.0</v>
+        <v>607.0</v>
       </c>
       <c r="D18" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
     </row>
     <row r="19">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="D21" t="n">
         <v>508.0</v>
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>18.0</v>
+        <v>21.0</v>
       </c>
       <c r="D22" t="n">
         <v>256.0</v>
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>616.0</v>
+        <v>620.0</v>
       </c>
       <c r="D58" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="59">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2062.0</v>
+        <v>2070.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12527.0</v>
+        <v>12542.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1386.0</v>
+        <v>1387.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2490.0</v>
+        <v>2495.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1532.0</v>
+        <v>1533.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1075.0</v>
+        <v>1077.0</v>
       </c>
     </row>
     <row r="66">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>448.0</v>
+        <v>450.0</v>
       </c>
       <c r="D87" t="n">
         <v>266.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>783.0</v>
+        <v>785.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>268.0</v>
+        <v>273.0</v>
       </c>
       <c r="D92" t="n">
         <v>49.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1234.0</v>
+        <v>1237.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>620.0</v>
+        <v>621.0</v>
       </c>
       <c r="D58" t="n">
         <v>133.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>746.0</v>
+        <v>748.0</v>
       </c>
       <c r="D59" t="n">
         <v>141.0</v>
@@ -1280,10 +1280,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>724.0</v>
+        <v>725.0</v>
       </c>
       <c r="D60" t="n">
-        <v>847.0</v>
+        <v>849.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2070.0</v>
+        <v>2075.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12542.0</v>
+        <v>12558.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2884.0</v>
       </c>
       <c r="D62" t="n">
-        <v>653.0</v>
+        <v>654.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1387.0</v>
+        <v>1389.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2495.0</v>
+        <v>2497.0</v>
       </c>
     </row>
     <row r="64">
@@ -1353,7 +1353,7 @@
         <v>1533.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1077.0</v>
+        <v>1078.0</v>
       </c>
     </row>
     <row r="66">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1237.0</v>
+        <v>1247.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="D95" t="n">
         <v>210.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>607.0</v>
+        <v>610.0</v>
       </c>
       <c r="D18" t="n">
         <v>250.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D53" t="n">
         <v>166.0</v>
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="D54" t="n">
         <v>132.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>419.0</v>
+        <v>421.0</v>
       </c>
       <c r="D55" t="n">
         <v>143.0</v>
@@ -1297,7 +1297,7 @@
         <v>2075.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12558.0</v>
+        <v>12572.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2884.0</v>
       </c>
       <c r="D62" t="n">
-        <v>654.0</v>
+        <v>656.0</v>
       </c>
     </row>
     <row r="63">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1533.0</v>
+        <v>1534.0</v>
       </c>
       <c r="D65" t="n">
         <v>1078.0</v>
@@ -1661,7 +1661,7 @@
         <v>450.0</v>
       </c>
       <c r="D87" t="n">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
     </row>
     <row r="88">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>785.0</v>
+        <v>786.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,10 +1728,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>273.0</v>
+        <v>277.0</v>
       </c>
       <c r="D92" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="93">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1247.0</v>
+        <v>1248.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1787,7 +1787,7 @@
         <v>802.0</v>
       </c>
       <c r="D96" t="n">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
     </row>
     <row r="97">
@@ -1801,7 +1801,7 @@
         <v>576.0</v>
       </c>
       <c r="D97" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1108.0</v>
+        <v>1110.0</v>
       </c>
       <c r="D6" t="n">
         <v>340.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2151.0</v>
+        <v>2153.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1070.0</v>
+        <v>1071.0</v>
       </c>
     </row>
     <row r="8">
@@ -1392,10 +1392,10 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="D68" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
     </row>
     <row r="69">
@@ -1423,7 +1423,7 @@
         <v>3.0</v>
       </c>
       <c r="D70" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="71">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>610.0</v>
+        <v>616.0</v>
       </c>
       <c r="D18" t="n">
         <v>250.0</v>
@@ -720,7 +720,7 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="D20" t="n">
         <v>316.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>317.0</v>
+        <v>338.0</v>
       </c>
       <c r="D21" t="n">
         <v>508.0</v>
@@ -751,7 +751,7 @@
         <v>21.0</v>
       </c>
       <c r="D22" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
     </row>
     <row r="23">
@@ -849,7 +849,7 @@
         <v>153.0</v>
       </c>
       <c r="D29" t="n">
-        <v>151.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="30">
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -989,7 +989,7 @@
         <v>128.0</v>
       </c>
       <c r="D39" t="n">
-        <v>879.0</v>
+        <v>886.0</v>
       </c>
     </row>
     <row r="40">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>172.0</v>
+        <v>174.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2131.0</v>
+        <v>2137.0</v>
       </c>
     </row>
     <row r="41">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3973.0</v>
+        <v>3977.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>51.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24316.0</v>
+        <v>24317.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1435.0</v>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="46">
@@ -1112,7 +1112,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1269.0</v>
+        <v>1274.0</v>
       </c>
       <c r="D48" t="n">
         <v>3884.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>365.0</v>
+        <v>366.0</v>
       </c>
       <c r="D51" t="n">
         <v>93.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1182,10 +1182,10 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="D53" t="n">
-        <v>166.0</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="54">
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>482.0</v>
+        <v>485.0</v>
       </c>
       <c r="D54" t="n">
         <v>132.0</v>
@@ -1213,7 +1213,7 @@
         <v>421.0</v>
       </c>
       <c r="D55" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="56">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>748.0</v>
+        <v>749.0</v>
       </c>
       <c r="D59" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>725.0</v>
       </c>
       <c r="D60" t="n">
-        <v>849.0</v>
+        <v>852.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2075.0</v>
+        <v>2078.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12572.0</v>
+        <v>12606.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1389.0</v>
+        <v>1392.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2497.0</v>
+        <v>2502.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1534.0</v>
+        <v>1541.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1078.0</v>
+        <v>1082.0</v>
       </c>
     </row>
     <row r="66">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>519.0</v>
+        <v>522.0</v>
       </c>
     </row>
     <row r="67">
@@ -1479,7 +1479,7 @@
         <v>48.0</v>
       </c>
       <c r="D74" t="n">
-        <v>67.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="75">
@@ -1490,10 +1490,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>669.0</v>
+        <v>675.0</v>
       </c>
       <c r="D75" t="n">
-        <v>428.0</v>
+        <v>430.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>449.0</v>
+        <v>462.0</v>
       </c>
       <c r="D76" t="n">
-        <v>433.0</v>
+        <v>439.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>1711.0</v>
+        <v>1744.0</v>
       </c>
       <c r="D77" t="n">
-        <v>519.0</v>
+        <v>528.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,10 +1532,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>315.0</v>
+        <v>323.0</v>
       </c>
       <c r="D78" t="n">
-        <v>485.0</v>
+        <v>492.0</v>
       </c>
     </row>
     <row r="79">
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>802.0</v>
+        <v>804.0</v>
       </c>
       <c r="D96" t="n">
         <v>439.0</v>
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>576.0</v>
+        <v>577.0</v>
       </c>
       <c r="D97" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="98">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="D100" t="n">
         <v>146.0</v>
@@ -1871,7 +1871,7 @@
         <v>102.0</v>
       </c>
       <c r="D102" t="n">
-        <v>194.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="103">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>955.0</v>
+        <v>961.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>449.0</v>
+        <v>453.0</v>
       </c>
       <c r="D3" t="n">
         <v>65.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
       <c r="D4" t="n">
-        <v>340.0</v>
+        <v>344.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>219.0</v>
+        <v>221.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>616.0</v>
+        <v>620.0</v>
       </c>
       <c r="D18" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
     </row>
     <row r="19">
@@ -737,7 +737,7 @@
         <v>338.0</v>
       </c>
       <c r="D21" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
       <c r="D22" t="n">
         <v>257.0</v>
@@ -972,7 +972,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>1027.0</v>
+        <v>1029.0</v>
       </c>
       <c r="D38" t="n">
         <v>15.0</v>
@@ -1000,7 +1000,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>174.0</v>
+        <v>175.0</v>
       </c>
       <c r="D40" t="n">
         <v>2137.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>743.0</v>
+        <v>748.0</v>
       </c>
       <c r="D56" t="n">
         <v>440.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>621.0</v>
+        <v>623.0</v>
       </c>
       <c r="D58" t="n">
         <v>133.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>749.0</v>
+        <v>750.0</v>
       </c>
       <c r="D59" t="n">
         <v>142.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2078.0</v>
+        <v>2079.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12606.0</v>
+        <v>12620.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1392.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2502.0</v>
+        <v>2505.0</v>
       </c>
     </row>
     <row r="64">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>450.0</v>
+        <v>453.0</v>
       </c>
       <c r="D87" t="n">
         <v>267.0</v>
@@ -1675,7 +1675,7 @@
         <v>436.0</v>
       </c>
       <c r="D88" t="n">
-        <v>116.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="89">
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="D90" t="n">
         <v>61.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>786.0</v>
+        <v>791.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>277.0</v>
+        <v>281.0</v>
       </c>
       <c r="D92" t="n">
         <v>50.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1248.0</v>
+        <v>1251.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1773,7 +1773,7 @@
         <v>150.0</v>
       </c>
       <c r="D95" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
     </row>
     <row r="96">
@@ -1899,7 +1899,7 @@
         <v>120.0</v>
       </c>
       <c r="D104" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="D35" t="n">
         <v>0.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>623.0</v>
+        <v>624.0</v>
       </c>
       <c r="D58" t="n">
         <v>133.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>750.0</v>
+        <v>752.0</v>
       </c>
       <c r="D59" t="n">
         <v>142.0</v>
@@ -1283,7 +1283,7 @@
         <v>725.0</v>
       </c>
       <c r="D60" t="n">
-        <v>852.0</v>
+        <v>854.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2079.0</v>
+        <v>2084.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12620.0</v>
+        <v>12639.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2884.0</v>
+        <v>2885.0</v>
       </c>
       <c r="D62" t="n">
-        <v>656.0</v>
+        <v>657.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1392.0</v>
+        <v>1393.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2505.0</v>
+        <v>2507.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1541.0</v>
+        <v>1542.0</v>
       </c>
       <c r="D65" t="n">
         <v>1082.0</v>
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>436.0</v>
+        <v>443.0</v>
       </c>
       <c r="D88" t="n">
-        <v>119.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="89">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>791.0</v>
+        <v>792.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1251.0</v>
+        <v>1255.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1773,7 +1773,7 @@
         <v>150.0</v>
       </c>
       <c r="D95" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>532.0</v>
+        <v>541.0</v>
       </c>
       <c r="D8" t="n">
         <v>157.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>268.0</v>
+        <v>277.0</v>
       </c>
       <c r="D9" t="n">
-        <v>564.0</v>
+        <v>576.0</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>215.0</v>
+        <v>222.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>624.0</v>
+        <v>625.0</v>
       </c>
       <c r="D58" t="n">
         <v>133.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2084.0</v>
+        <v>2086.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12639.0</v>
+        <v>12651.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2885.0</v>
+        <v>2886.0</v>
       </c>
       <c r="D62" t="n">
         <v>657.0</v>
@@ -1325,7 +1325,7 @@
         <v>1393.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2507.0</v>
+        <v>2508.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1542.0</v>
+        <v>1548.0</v>
       </c>
       <c r="D65" t="n">
         <v>1082.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>281.0</v>
+        <v>287.0</v>
       </c>
       <c r="D92" t="n">
         <v>50.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1255.0</v>
+        <v>1256.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="D95" t="n">
         <v>212.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1731,7 +1731,7 @@
         <v>287.0</v>
       </c>
       <c r="D92" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="93">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1256.0</v>
+        <v>1258.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>86.0</v>
+        <v>94.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="D95" t="n">
         <v>212.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -496,7 +496,7 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="D4" t="n">
         <v>344.0</v>
@@ -524,10 +524,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1110.0</v>
+        <v>1120.0</v>
       </c>
       <c r="D6" t="n">
-        <v>340.0</v>
+        <v>342.0</v>
       </c>
     </row>
     <row r="7">
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2153.0</v>
+        <v>2163.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1071.0</v>
+        <v>1074.0</v>
       </c>
     </row>
     <row r="8">
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="D26" t="n">
         <v>12.0</v>
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>153.0</v>
+        <v>155.0</v>
       </c>
       <c r="D29" t="n">
         <v>153.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2086.0</v>
+        <v>2087.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12651.0</v>
+        <v>12677.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>657.0</v>
+        <v>658.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1393.0</v>
+        <v>1397.0</v>
       </c>
       <c r="D63" t="n">
         <v>2508.0</v>
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1548.0</v>
+        <v>1550.0</v>
       </c>
       <c r="D65" t="n">
         <v>1082.0</v>
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>522.0</v>
+        <v>524.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>37.0</v>
       </c>
       <c r="D67" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="68">
@@ -1392,10 +1392,10 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>208.0</v>
+        <v>210.0</v>
       </c>
       <c r="D68" t="n">
-        <v>193.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="69">
@@ -1409,7 +1409,7 @@
         <v>85.0</v>
       </c>
       <c r="D69" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="70">
@@ -1434,7 +1434,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="D71" t="n">
         <v>0.0</v>
@@ -1448,7 +1448,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
       <c r="D72" t="n">
         <v>16.0</v>
@@ -1462,7 +1462,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>292.0</v>
+        <v>297.0</v>
       </c>
       <c r="D73" t="n">
         <v>42.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>804.0</v>
+        <v>806.0</v>
       </c>
       <c r="D96" t="n">
-        <v>439.0</v>
+        <v>440.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>577.0</v>
+        <v>578.0</v>
       </c>
       <c r="D97" t="n">
         <v>141.0</v>
@@ -1843,7 +1843,7 @@
         <v>209.0</v>
       </c>
       <c r="D100" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="101">
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="104">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -989,7 +989,7 @@
         <v>128.0</v>
       </c>
       <c r="D39" t="n">
-        <v>886.0</v>
+        <v>888.0</v>
       </c>
     </row>
     <row r="40">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2137.0</v>
+        <v>2139.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>427.0</v>
+        <v>428.0</v>
       </c>
       <c r="D41" t="n">
         <v>39.0</v>
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>126.0</v>
+        <v>129.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3977.0</v>
+        <v>3978.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>51.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24317.0</v>
+        <v>24319.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1440.0</v>
+        <v>1442.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>702.0</v>
+        <v>707.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1881.0</v>
+        <v>1882.0</v>
       </c>
     </row>
     <row r="47">
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>739.0</v>
+        <v>742.0</v>
       </c>
       <c r="D50" t="n">
         <v>74.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>625.0</v>
+        <v>627.0</v>
       </c>
       <c r="D58" t="n">
         <v>133.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>752.0</v>
+        <v>753.0</v>
       </c>
       <c r="D59" t="n">
         <v>142.0</v>
@@ -1283,7 +1283,7 @@
         <v>725.0</v>
       </c>
       <c r="D60" t="n">
-        <v>854.0</v>
+        <v>855.0</v>
       </c>
     </row>
     <row r="61">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1397.0</v>
+        <v>1400.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2508.0</v>
+        <v>2514.0</v>
       </c>
     </row>
     <row r="64">
@@ -1353,7 +1353,7 @@
         <v>1550.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1082.0</v>
+        <v>1086.0</v>
       </c>
     </row>
     <row r="66">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>620.0</v>
+        <v>624.0</v>
       </c>
       <c r="D18" t="n">
         <v>251.0</v>
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="20">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>338.0</v>
+        <v>341.0</v>
       </c>
       <c r="D21" t="n">
         <v>509.0</v>
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="D22" t="n">
-        <v>257.0</v>
+        <v>262.0</v>
       </c>
     </row>
     <row r="23">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>753.0</v>
+        <v>761.0</v>
       </c>
       <c r="D59" t="n">
         <v>142.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2087.0</v>
+        <v>2093.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12677.0</v>
+        <v>12695.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1400.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2514.0</v>
+        <v>2515.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1550.0</v>
+        <v>1552.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1086.0</v>
+        <v>1087.0</v>
       </c>
     </row>
     <row r="66">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>260.0</v>
+        <v>262.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="D90" t="n">
         <v>61.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>792.0</v>
+        <v>793.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>287.0</v>
+        <v>289.0</v>
       </c>
       <c r="D92" t="n">
         <v>51.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1258.0</v>
+        <v>1259.0</v>
       </c>
       <c r="D93" t="n">
         <v>41.0</v>
@@ -1773,7 +1773,7 @@
         <v>152.0</v>
       </c>
       <c r="D95" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -776,10 +776,10 @@
         <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>121.0</v>
+        <v>107.0</v>
       </c>
       <c r="D24" t="n">
-        <v>277.0</v>
+        <v>272.0</v>
       </c>
     </row>
     <row r="25">
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>235.0</v>
+        <v>238.0</v>
       </c>
       <c r="D27" t="n">
         <v>148.0</v>
@@ -972,10 +972,10 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>1029.0</v>
+        <v>641.0</v>
       </c>
       <c r="D38" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="39">
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>128.0</v>
+        <v>130.0</v>
       </c>
       <c r="D39" t="n">
         <v>888.0</v>
@@ -1084,7 +1084,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>707.0</v>
+        <v>708.0</v>
       </c>
       <c r="D46" t="n">
         <v>1882.0</v>
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>742.0</v>
+        <v>744.0</v>
       </c>
       <c r="D50" t="n">
         <v>74.0</v>
@@ -1185,7 +1185,7 @@
         <v>103.0</v>
       </c>
       <c r="D53" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
     </row>
     <row r="54">
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>627.0</v>
+        <v>630.0</v>
       </c>
       <c r="D58" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>761.0</v>
+        <v>764.0</v>
       </c>
       <c r="D59" t="n">
         <v>142.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>2093.0</v>
+        <v>1543.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12695.0</v>
+        <v>12709.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>659.0</v>
+        <v>661.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1400.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2515.0</v>
+        <v>2518.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1552.0</v>
+        <v>1553.0</v>
       </c>
       <c r="D65" t="n">
         <v>1087.0</v>
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>524.0</v>
+        <v>527.0</v>
       </c>
     </row>
     <row r="67">
@@ -1675,7 +1675,7 @@
         <v>443.0</v>
       </c>
       <c r="D88" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="89">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>793.0</v>
+        <v>794.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>806.0</v>
+        <v>808.0</v>
       </c>
       <c r="D96" t="n">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>578.0</v>
+        <v>580.0</v>
       </c>
       <c r="D97" t="n">
         <v>141.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>198.0</v>
+        <v>204.0</v>
       </c>
     </row>
     <row r="100">
@@ -1871,7 +1871,7 @@
         <v>102.0</v>
       </c>
       <c r="D102" t="n">
-        <v>196.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="103">
@@ -1899,7 +1899,7 @@
         <v>120.0</v>
       </c>
       <c r="D104" t="n">
-        <v>311.0</v>
+        <v>313.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>485.0</v>
+        <v>486.0</v>
       </c>
       <c r="D54" t="n">
         <v>132.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>421.0</v>
+        <v>422.0</v>
       </c>
       <c r="D55" t="n">
         <v>144.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>630.0</v>
+        <v>631.0</v>
       </c>
       <c r="D58" t="n">
         <v>134.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1543.0</v>
+        <v>1546.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12709.0</v>
+        <v>12719.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1400.0</v>
+        <v>1402.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2518.0</v>
+        <v>2528.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1553.0</v>
+        <v>1554.0</v>
       </c>
       <c r="D65" t="n">
         <v>1087.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>794.0</v>
+        <v>797.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>289.0</v>
+        <v>294.0</v>
       </c>
       <c r="D92" t="n">
         <v>51.0</v>
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1259.0</v>
+        <v>1260.0</v>
       </c>
       <c r="D93" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="94">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>797.0</v>
+        <v>798.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>294.0</v>
+        <v>296.0</v>
       </c>
       <c r="D92" t="n">
         <v>51.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1260.0</v>
+        <v>1262.0</v>
       </c>
       <c r="D93" t="n">
         <v>42.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1773,7 +1773,7 @@
         <v>152.0</v>
       </c>
       <c r="D95" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>961.0</v>
+        <v>964.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>453.0</v>
+        <v>456.0</v>
       </c>
       <c r="D3" t="n">
         <v>65.0</v>
@@ -499,7 +499,7 @@
         <v>185.0</v>
       </c>
       <c r="D4" t="n">
-        <v>344.0</v>
+        <v>348.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>238.0</v>
+        <v>239.0</v>
       </c>
       <c r="D27" t="n">
         <v>148.0</v>
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
       <c r="D29" t="n">
         <v>153.0</v>
@@ -989,7 +989,7 @@
         <v>130.0</v>
       </c>
       <c r="D39" t="n">
-        <v>888.0</v>
+        <v>889.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>176.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2139.0</v>
+        <v>2144.0</v>
       </c>
     </row>
     <row r="41">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3978.0</v>
+        <v>3979.0</v>
       </c>
     </row>
     <row r="43">
@@ -1059,7 +1059,7 @@
         <v>51.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24319.0</v>
+        <v>24323.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1442.0</v>
+        <v>1446.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,7 +1084,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>708.0</v>
+        <v>725.0</v>
       </c>
       <c r="D46" t="n">
         <v>1882.0</v>
@@ -1140,10 +1140,10 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>744.0</v>
+        <v>745.0</v>
       </c>
       <c r="D50" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,10 +1154,10 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
       <c r="D51" t="n">
-        <v>93.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="52">
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="D53" t="n">
         <v>169.0</v>
@@ -1199,7 +1199,7 @@
         <v>486.0</v>
       </c>
       <c r="D54" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>422.0</v>
+        <v>423.0</v>
       </c>
       <c r="D55" t="n">
         <v>144.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>748.0</v>
+        <v>751.0</v>
       </c>
       <c r="D56" t="n">
         <v>440.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>631.0</v>
+        <v>632.0</v>
       </c>
       <c r="D58" t="n">
         <v>134.0</v>
@@ -1283,7 +1283,7 @@
         <v>725.0</v>
       </c>
       <c r="D60" t="n">
-        <v>855.0</v>
+        <v>857.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1546.0</v>
+        <v>1552.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12719.0</v>
+        <v>12765.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>661.0</v>
+        <v>665.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1402.0</v>
+        <v>1407.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2528.0</v>
+        <v>2535.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>527.0</v>
+        <v>530.0</v>
       </c>
     </row>
     <row r="67">
@@ -1574,10 +1574,10 @@
         <v>104</v>
       </c>
       <c r="C81" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D81" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="82">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>798.0</v>
+        <v>800.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>296.0</v>
+        <v>297.0</v>
       </c>
       <c r="D92" t="n">
         <v>51.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1262.0</v>
+        <v>1263.0</v>
       </c>
       <c r="D93" t="n">
         <v>42.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1787,7 +1787,7 @@
         <v>808.0</v>
       </c>
       <c r="D96" t="n">
-        <v>441.0</v>
+        <v>442.0</v>
       </c>
     </row>
     <row r="97">
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>204.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="104">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>632.0</v>
+        <v>634.0</v>
       </c>
       <c r="D58" t="n">
         <v>134.0</v>
@@ -1297,7 +1297,7 @@
         <v>1552.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12765.0</v>
+        <v>12780.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>665.0</v>
+        <v>669.0</v>
       </c>
     </row>
     <row r="63">
@@ -1353,7 +1353,7 @@
         <v>1554.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1087.0</v>
+        <v>1088.0</v>
       </c>
     </row>
     <row r="66">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>443.0</v>
+        <v>444.0</v>
       </c>
       <c r="D88" t="n">
         <v>121.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>800.0</v>
+        <v>801.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1263.0</v>
+        <v>1265.0</v>
       </c>
       <c r="D93" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>123.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="104">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>624.0</v>
+        <v>635.0</v>
       </c>
       <c r="D18" t="n">
         <v>251.0</v>
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="20">
@@ -720,10 +720,10 @@
         <v>43</v>
       </c>
       <c r="C20" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>341.0</v>
+        <v>350.0</v>
       </c>
       <c r="D21" t="n">
         <v>509.0</v>
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>29.0</v>
+        <v>31.0</v>
       </c>
       <c r="D22" t="n">
         <v>262.0</v>
@@ -765,7 +765,7 @@
         <v>75.0</v>
       </c>
       <c r="D23" t="n">
-        <v>375.0</v>
+        <v>377.0</v>
       </c>
     </row>
     <row r="24">
@@ -793,7 +793,7 @@
         <v>25.0</v>
       </c>
       <c r="D25" t="n">
-        <v>79.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="26">
@@ -972,7 +972,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>641.0</v>
+        <v>642.0</v>
       </c>
       <c r="D38" t="n">
         <v>14.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>367.0</v>
+        <v>368.0</v>
       </c>
       <c r="D51" t="n">
         <v>96.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="D52" t="n">
         <v>57.0</v>
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>634.0</v>
+        <v>635.0</v>
       </c>
       <c r="D58" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="59">
@@ -1297,7 +1297,7 @@
         <v>1552.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12780.0</v>
+        <v>12803.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1407.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2535.0</v>
+        <v>2539.0</v>
       </c>
     </row>
     <row r="64">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1728,10 +1728,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>297.0</v>
+        <v>303.0</v>
       </c>
       <c r="D92" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="93">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1265.0</v>
+        <v>1269.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>808.0</v>
+        <v>809.0</v>
       </c>
       <c r="D96" t="n">
         <v>442.0</v>
@@ -1801,7 +1801,7 @@
         <v>580.0</v>
       </c>
       <c r="D97" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1120.0</v>
+        <v>1123.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2163.0</v>
+        <v>2166.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1074.0</v>
+        <v>1080.0</v>
       </c>
     </row>
     <row r="8">
@@ -1392,10 +1392,10 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>210.0</v>
+        <v>213.0</v>
       </c>
       <c r="D68" t="n">
-        <v>196.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="69">
@@ -1409,7 +1409,7 @@
         <v>85.0</v>
       </c>
       <c r="D69" t="n">
-        <v>105.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="70">
@@ -1434,7 +1434,7 @@
         <v>94</v>
       </c>
       <c r="C71" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="D71" t="n">
         <v>0.0</v>
@@ -1658,10 +1658,10 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="D87" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
     </row>
     <row r="88">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>801.0</v>
+        <v>802.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1269.0</v>
+        <v>1270.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>964.0</v>
+        <v>967.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -485,7 +485,7 @@
         <v>456.0</v>
       </c>
       <c r="D3" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="4">
@@ -499,7 +499,7 @@
         <v>185.0</v>
       </c>
       <c r="D4" t="n">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>223.0</v>
+        <v>224.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -821,7 +821,7 @@
         <v>239.0</v>
       </c>
       <c r="D27" t="n">
-        <v>148.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="28">
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="D28" t="n">
         <v>6.0</v>
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="D29" t="n">
         <v>153.0</v>
@@ -989,7 +989,7 @@
         <v>130.0</v>
       </c>
       <c r="D39" t="n">
-        <v>889.0</v>
+        <v>885.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>176.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2144.0</v>
+        <v>2151.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>428.0</v>
+        <v>431.0</v>
       </c>
       <c r="D41" t="n">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3979.0</v>
+        <v>3980.0</v>
       </c>
     </row>
     <row r="43">
@@ -1056,10 +1056,10 @@
         <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24323.0</v>
+        <v>24325.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1446.0</v>
+        <v>1447.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>725.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1882.0</v>
+        <v>1881.0</v>
       </c>
     </row>
     <row r="47">
@@ -1112,10 +1112,10 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1274.0</v>
+        <v>1276.0</v>
       </c>
       <c r="D48" t="n">
-        <v>3884.0</v>
+        <v>3885.0</v>
       </c>
     </row>
     <row r="49">
@@ -1129,7 +1129,7 @@
         <v>22.0</v>
       </c>
       <c r="D49" t="n">
-        <v>57.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="50">
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>745.0</v>
+        <v>746.0</v>
       </c>
       <c r="D50" t="n">
         <v>75.0</v>
@@ -1227,7 +1227,7 @@
         <v>751.0</v>
       </c>
       <c r="D56" t="n">
-        <v>440.0</v>
+        <v>442.0</v>
       </c>
     </row>
     <row r="57">
@@ -1241,7 +1241,7 @@
         <v>164.0</v>
       </c>
       <c r="D57" t="n">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="58">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>725.0</v>
+        <v>726.0</v>
       </c>
       <c r="D60" t="n">
         <v>857.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1552.0</v>
+        <v>1553.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12803.0</v>
+        <v>12821.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1407.0</v>
+        <v>1410.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2539.0</v>
+        <v>2541.0</v>
       </c>
     </row>
     <row r="64">
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="100">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1703,7 +1703,7 @@
         <v>166.0</v>
       </c>
       <c r="D90" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="91">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>303.0</v>
+        <v>306.0</v>
       </c>
       <c r="D92" t="n">
         <v>52.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>635.0</v>
+        <v>638.0</v>
       </c>
       <c r="D18" t="n">
         <v>251.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>350.0</v>
+        <v>357.0</v>
       </c>
       <c r="D21" t="n">
         <v>509.0</v>
@@ -1210,10 +1210,10 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>423.0</v>
+        <v>424.0</v>
       </c>
       <c r="D55" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="56">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>669.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="63">
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>809.0</v>
+        <v>811.0</v>
       </c>
       <c r="D96" t="n">
-        <v>442.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>580.0</v>
+        <v>584.0</v>
       </c>
       <c r="D97" t="n">
         <v>142.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>246.0</v>
+        <v>247.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>726.0</v>
+        <v>727.0</v>
       </c>
       <c r="D60" t="n">
         <v>857.0</v>
@@ -1297,7 +1297,7 @@
         <v>1553.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12821.0</v>
+        <v>12829.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2886.0</v>
       </c>
       <c r="D62" t="n">
-        <v>670.0</v>
+        <v>671.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1410.0</v>
+        <v>1411.0</v>
       </c>
       <c r="D63" t="n">
         <v>2541.0</v>
@@ -1353,7 +1353,7 @@
         <v>1554.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1088.0</v>
+        <v>1093.0</v>
       </c>
     </row>
     <row r="66">
@@ -1661,7 +1661,7 @@
         <v>454.0</v>
       </c>
       <c r="D87" t="n">
-        <v>268.0</v>
+        <v>271.0</v>
       </c>
     </row>
     <row r="88">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>263.0</v>
+        <v>264.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1270.0</v>
+        <v>1272.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="D95" t="n">
         <v>214.0</v>
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -972,7 +972,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>642.0</v>
+        <v>643.0</v>
       </c>
       <c r="D38" t="n">
         <v>14.0</v>
@@ -1185,7 +1185,7 @@
         <v>104.0</v>
       </c>
       <c r="D53" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
     </row>
     <row r="54">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1553.0</v>
+        <v>1555.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12829.0</v>
+        <v>12850.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1411.0</v>
+        <v>1412.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2541.0</v>
+        <v>2544.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1554.0</v>
+        <v>1555.0</v>
       </c>
       <c r="D65" t="n">
         <v>1093.0</v>
@@ -1507,7 +1507,7 @@
         <v>462.0</v>
       </c>
       <c r="D76" t="n">
-        <v>439.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="77">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>264.0</v>
+        <v>265.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>802.0</v>
+        <v>804.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>306.0</v>
+        <v>315.0</v>
       </c>
       <c r="D92" t="n">
         <v>52.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1272.0</v>
+        <v>1274.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>811.0</v>
+        <v>813.0</v>
       </c>
       <c r="D96" t="n">
-        <v>443.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>584.0</v>
+        <v>585.0</v>
       </c>
       <c r="D97" t="n">
         <v>142.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1507,7 +1507,7 @@
         <v>462.0</v>
       </c>
       <c r="D76" t="n">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
     </row>
     <row r="77">
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>444.0</v>
+        <v>447.0</v>
       </c>
       <c r="D88" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="89">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>315.0</v>
+        <v>319.0</v>
       </c>
       <c r="D92" t="n">
         <v>52.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1274.0</v>
+        <v>1276.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1123.0</v>
+        <v>1126.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,7 +538,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2166.0</v>
+        <v>2170.0</v>
       </c>
       <c r="D7" t="n">
         <v>1080.0</v>
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="D27" t="n">
         <v>151.0</v>
@@ -849,7 +849,7 @@
         <v>157.0</v>
       </c>
       <c r="D29" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="30">
@@ -1269,7 +1269,7 @@
         <v>764.0</v>
       </c>
       <c r="D59" t="n">
-        <v>142.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="60">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1555.0</v>
+        <v>1556.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12850.0</v>
+        <v>12884.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2886.0</v>
+        <v>2887.0</v>
       </c>
       <c r="D62" t="n">
         <v>671.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1412.0</v>
+        <v>1413.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2544.0</v>
+        <v>2546.0</v>
       </c>
     </row>
     <row r="64">
@@ -1392,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="D68" t="n">
         <v>198.0</v>
@@ -1812,7 +1812,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="D98" t="n">
         <v>42.0</v>
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>210.0</v>
+        <v>211.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>125.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="104">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -972,7 +972,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>643.0</v>
+        <v>644.0</v>
       </c>
       <c r="D38" t="n">
         <v>14.0</v>
@@ -989,7 +989,7 @@
         <v>130.0</v>
       </c>
       <c r="D39" t="n">
-        <v>885.0</v>
+        <v>887.0</v>
       </c>
     </row>
     <row r="40">
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2151.0</v>
+        <v>2154.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1031,7 +1031,7 @@
         <v>132.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3980.0</v>
+        <v>3981.0</v>
       </c>
     </row>
     <row r="43">
@@ -1056,10 +1056,10 @@
         <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24325.0</v>
+        <v>24328.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1447.0</v>
+        <v>1449.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>725.0</v>
+        <v>726.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1881.0</v>
+        <v>1883.0</v>
       </c>
     </row>
     <row r="47">
@@ -1112,7 +1112,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1276.0</v>
+        <v>1282.0</v>
       </c>
       <c r="D48" t="n">
         <v>3885.0</v>
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="D49" t="n">
         <v>56.0</v>
@@ -1140,7 +1140,7 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>746.0</v>
+        <v>747.0</v>
       </c>
       <c r="D50" t="n">
         <v>75.0</v>
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="D53" t="n">
         <v>170.0</v>
@@ -1269,7 +1269,7 @@
         <v>764.0</v>
       </c>
       <c r="D59" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="60">
@@ -1311,7 +1311,7 @@
         <v>2887.0</v>
       </c>
       <c r="D62" t="n">
-        <v>671.0</v>
+        <v>673.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1413.0</v>
+        <v>1414.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2546.0</v>
+        <v>2548.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="D64" t="n">
         <v>24.0</v>
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>530.0</v>
+        <v>531.0</v>
       </c>
     </row>
     <row r="67">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>454.0</v>
+        <v>455.0</v>
       </c>
       <c r="D87" t="n">
         <v>271.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>804.0</v>
+        <v>809.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1787,7 +1787,7 @@
         <v>813.0</v>
       </c>
       <c r="D96" t="n">
-        <v>447.0</v>
+        <v>450.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>585.0</v>
+        <v>586.0</v>
       </c>
       <c r="D97" t="n">
         <v>142.0</v>
@@ -1899,7 +1899,7 @@
         <v>120.0</v>
       </c>
       <c r="D104" t="n">
-        <v>313.0</v>
+        <v>314.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>967.0</v>
+        <v>971.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,10 +482,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>456.0</v>
+        <v>458.0</v>
       </c>
       <c r="D3" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="4">
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="D4" t="n">
-        <v>349.0</v>
+        <v>352.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>224.0</v>
+        <v>226.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>751.0</v>
+        <v>754.0</v>
       </c>
       <c r="D56" t="n">
-        <v>442.0</v>
+        <v>444.0</v>
       </c>
     </row>
     <row r="57">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1556.0</v>
+        <v>1557.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12884.0</v>
+        <v>12911.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1414.0</v>
+        <v>1425.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2548.0</v>
+        <v>2549.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1555.0</v>
+        <v>1557.0</v>
       </c>
       <c r="D65" t="n">
         <v>1093.0</v>
@@ -1661,7 +1661,7 @@
         <v>455.0</v>
       </c>
       <c r="D87" t="n">
-        <v>271.0</v>
+        <v>276.0</v>
       </c>
     </row>
     <row r="88">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>447.0</v>
+        <v>448.0</v>
       </c>
       <c r="D88" t="n">
         <v>123.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>265.0</v>
+        <v>268.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="D90" t="n">
         <v>62.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1276.0</v>
+        <v>1286.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>638.0</v>
+        <v>655.0</v>
       </c>
       <c r="D18" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
     </row>
     <row r="19">
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>317.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>357.0</v>
+        <v>376.0</v>
       </c>
       <c r="D21" t="n">
-        <v>509.0</v>
+        <v>517.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="D22" t="n">
-        <v>262.0</v>
+        <v>268.0</v>
       </c>
     </row>
     <row r="23">
@@ -762,10 +762,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="D23" t="n">
-        <v>377.0</v>
+        <v>383.0</v>
       </c>
     </row>
     <row r="24">
@@ -776,10 +776,10 @@
         <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>107.0</v>
+        <v>110.0</v>
       </c>
       <c r="D24" t="n">
-        <v>272.0</v>
+        <v>276.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>25.0</v>
       </c>
       <c r="D25" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="26">
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="D26" t="n">
         <v>12.0</v>
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
       <c r="D28" t="n">
         <v>6.0</v>
@@ -1283,7 +1283,7 @@
         <v>727.0</v>
       </c>
       <c r="D60" t="n">
-        <v>857.0</v>
+        <v>859.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1557.0</v>
+        <v>1560.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12911.0</v>
+        <v>12938.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1425.0</v>
+        <v>1427.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2549.0</v>
+        <v>2553.0</v>
       </c>
     </row>
     <row r="64">
@@ -1353,7 +1353,7 @@
         <v>1557.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1093.0</v>
+        <v>1094.0</v>
       </c>
     </row>
     <row r="66">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>531.0</v>
+        <v>532.0</v>
       </c>
     </row>
     <row r="67">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>455.0</v>
+        <v>459.0</v>
       </c>
       <c r="D87" t="n">
         <v>276.0</v>
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>448.0</v>
+        <v>449.0</v>
       </c>
       <c r="D88" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="89">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>319.0</v>
+        <v>324.0</v>
       </c>
       <c r="D92" t="n">
         <v>52.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1286.0</v>
+        <v>1291.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1829,7 +1829,7 @@
         <v>30.0</v>
       </c>
       <c r="D99" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>211.0</v>
+        <v>212.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>
@@ -1899,7 +1899,7 @@
         <v>120.0</v>
       </c>
       <c r="D104" t="n">
-        <v>314.0</v>
+        <v>316.0</v>
       </c>
     </row>
     <row r="105">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>247.0</v>
+        <v>249.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1560.0</v>
+        <v>1562.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12938.0</v>
+        <v>12952.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2887.0</v>
       </c>
       <c r="D62" t="n">
-        <v>673.0</v>
+        <v>675.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1427.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2553.0</v>
+        <v>2557.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>62.0</v>
       </c>
       <c r="D64" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="65">
@@ -1350,10 +1350,10 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1557.0</v>
+        <v>1558.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1094.0</v>
+        <v>1097.0</v>
       </c>
     </row>
     <row r="66">
@@ -1728,10 +1728,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>324.0</v>
+        <v>326.0</v>
       </c>
       <c r="D92" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="93">
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>100.0</v>
+        <v>102.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>326.0</v>
+        <v>332.0</v>
       </c>
       <c r="D92" t="n">
         <v>53.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1291.0</v>
+        <v>1297.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -499,7 +499,7 @@
         <v>186.0</v>
       </c>
       <c r="D4" t="n">
-        <v>352.0</v>
+        <v>354.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>226.0</v>
+        <v>228.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -1154,10 +1154,10 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>368.0</v>
+        <v>369.0</v>
       </c>
       <c r="D51" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="52">
@@ -1185,7 +1185,7 @@
         <v>106.0</v>
       </c>
       <c r="D53" t="n">
-        <v>170.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="54">
@@ -1199,7 +1199,7 @@
         <v>486.0</v>
       </c>
       <c r="D54" t="n">
-        <v>133.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="55">
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>754.0</v>
+        <v>755.0</v>
       </c>
       <c r="D56" t="n">
-        <v>444.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="57">
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="D57" t="n">
         <v>161.0</v>
@@ -1283,7 +1283,7 @@
         <v>727.0</v>
       </c>
       <c r="D60" t="n">
-        <v>859.0</v>
+        <v>863.0</v>
       </c>
     </row>
     <row r="61">
@@ -1297,7 +1297,7 @@
         <v>1562.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12952.0</v>
+        <v>12982.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1427.0</v>
+        <v>1428.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2557.0</v>
+        <v>2558.0</v>
       </c>
     </row>
     <row r="64">
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>813.0</v>
+        <v>814.0</v>
       </c>
       <c r="D96" t="n">
-        <v>450.0</v>
+        <v>451.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="D97" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>655.0</v>
+        <v>674.0</v>
       </c>
       <c r="D18" t="n">
         <v>252.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>376.0</v>
+        <v>392.0</v>
       </c>
       <c r="D21" t="n">
         <v>517.0</v>
@@ -751,7 +751,7 @@
         <v>34.0</v>
       </c>
       <c r="D22" t="n">
-        <v>268.0</v>
+        <v>271.0</v>
       </c>
     </row>
     <row r="23">
@@ -765,7 +765,7 @@
         <v>76.0</v>
       </c>
       <c r="D23" t="n">
-        <v>383.0</v>
+        <v>384.0</v>
       </c>
     </row>
     <row r="24">
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>836.0</v>
+        <v>886.0</v>
       </c>
       <c r="D30" t="n">
         <v>55.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>292.0</v>
+        <v>310.0</v>
       </c>
       <c r="D31" t="n">
         <v>9.0</v>
@@ -888,10 +888,10 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>308.0</v>
+        <v>319.0</v>
       </c>
       <c r="D32" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="33">
@@ -902,10 +902,10 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>5355.0</v>
+        <v>5502.0</v>
       </c>
       <c r="D33" t="n">
-        <v>209.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="34">
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>861.0</v>
+        <v>901.0</v>
       </c>
       <c r="D34" t="n">
-        <v>85.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="35">
@@ -986,10 +986,10 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="D39" t="n">
-        <v>887.0</v>
+        <v>897.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>177.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2154.0</v>
+        <v>2156.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>432.0</v>
+        <v>434.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1031,7 +1031,7 @@
         <v>132.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3981.0</v>
+        <v>3983.0</v>
       </c>
     </row>
     <row r="43">
@@ -1045,7 +1045,7 @@
         <v>29.0</v>
       </c>
       <c r="D43" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="44">
@@ -1059,7 +1059,7 @@
         <v>53.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24328.0</v>
+        <v>24331.0</v>
       </c>
     </row>
     <row r="45">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1449.0</v>
+        <v>1450.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1084,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>726.0</v>
+        <v>732.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1883.0</v>
+        <v>1884.0</v>
       </c>
     </row>
     <row r="47">
@@ -1112,7 +1112,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1282.0</v>
+        <v>1285.0</v>
       </c>
       <c r="D48" t="n">
         <v>3885.0</v>
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="D49" t="n">
         <v>56.0</v>
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>635.0</v>
+        <v>637.0</v>
       </c>
       <c r="D58" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="59">
@@ -1294,7 +1294,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1562.0</v>
+        <v>1563.0</v>
       </c>
       <c r="D61" t="n">
         <v>12982.0</v>
@@ -1311,7 +1311,7 @@
         <v>2887.0</v>
       </c>
       <c r="D62" t="n">
-        <v>675.0</v>
+        <v>676.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1428.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2558.0</v>
+        <v>2560.0</v>
       </c>
     </row>
     <row r="64">
@@ -1658,7 +1658,7 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>459.0</v>
+        <v>461.0</v>
       </c>
       <c r="D87" t="n">
         <v>276.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>814.0</v>
+        <v>816.0</v>
       </c>
       <c r="D96" t="n">
         <v>451.0</v>
@@ -1801,7 +1801,7 @@
         <v>587.0</v>
       </c>
       <c r="D97" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="98">
@@ -1812,7 +1812,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="D98" t="n">
         <v>42.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -622,10 +622,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>846.0</v>
+        <v>880.0</v>
       </c>
       <c r="D13" t="n">
-        <v>322.0</v>
+        <v>334.0</v>
       </c>
     </row>
     <row r="14">
@@ -636,10 +636,10 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>557.0</v>
+        <v>580.0</v>
       </c>
       <c r="D14" t="n">
-        <v>109.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="15">
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>639.0</v>
+        <v>682.0</v>
       </c>
       <c r="D15" t="n">
-        <v>173.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="16">
@@ -664,7 +664,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="D16" t="n">
         <v>88.0</v>
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9232.0</v>
+        <v>9271.0</v>
       </c>
       <c r="D17" t="n">
-        <v>903.0</v>
+        <v>906.0</v>
       </c>
     </row>
     <row r="18">
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>156.0</v>
+        <v>159.0</v>
       </c>
       <c r="D28" t="n">
         <v>6.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>886.0</v>
+        <v>889.0</v>
       </c>
       <c r="D30" t="n">
         <v>55.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="D31" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>5502.0</v>
+        <v>5507.0</v>
       </c>
       <c r="D33" t="n">
         <v>212.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>901.0</v>
+        <v>905.0</v>
       </c>
       <c r="D34" t="n">
         <v>87.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="D55" t="n">
         <v>145.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>637.0</v>
+        <v>638.0</v>
       </c>
       <c r="D58" t="n">
         <v>136.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>764.0</v>
+        <v>765.0</v>
       </c>
       <c r="D59" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>727.0</v>
       </c>
       <c r="D60" t="n">
-        <v>863.0</v>
+        <v>865.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1563.0</v>
+        <v>1566.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12982.0</v>
+        <v>12996.0</v>
       </c>
     </row>
     <row r="62">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1428.0</v>
+        <v>1430.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2560.0</v>
+        <v>2566.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>532.0</v>
+        <v>534.0</v>
       </c>
     </row>
     <row r="67">
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="D74" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="75">
@@ -1490,10 +1490,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>675.0</v>
+        <v>681.0</v>
       </c>
       <c r="D75" t="n">
-        <v>430.0</v>
+        <v>434.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>462.0</v>
+        <v>472.0</v>
       </c>
       <c r="D76" t="n">
-        <v>439.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>1744.0</v>
+        <v>1773.0</v>
       </c>
       <c r="D77" t="n">
-        <v>528.0</v>
+        <v>538.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,10 +1532,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>323.0</v>
+        <v>328.0</v>
       </c>
       <c r="D78" t="n">
-        <v>492.0</v>
+        <v>499.0</v>
       </c>
     </row>
     <row r="79">
@@ -1658,10 +1658,10 @@
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>461.0</v>
+        <v>463.0</v>
       </c>
       <c r="D87" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
     </row>
     <row r="88">
@@ -1675,7 +1675,7 @@
         <v>449.0</v>
       </c>
       <c r="D88" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>268.0</v>
+        <v>270.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>809.0</v>
+        <v>813.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>332.0</v>
+        <v>333.0</v>
       </c>
       <c r="D92" t="n">
         <v>53.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1297.0</v>
+        <v>1302.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1773,7 +1773,7 @@
         <v>153.0</v>
       </c>
       <c r="D95" t="n">
-        <v>214.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="96">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="D97" t="n">
         <v>145.0</v>
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>127.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="104">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="D105" t="n">
         <v>182.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -667,7 +667,7 @@
         <v>48.0</v>
       </c>
       <c r="D16" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
     </row>
     <row r="17">
@@ -944,7 +944,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="D36" t="n">
         <v>9.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>369.0</v>
+        <v>370.0</v>
       </c>
       <c r="D51" t="n">
         <v>97.0</v>
@@ -1280,10 +1280,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>727.0</v>
+        <v>728.0</v>
       </c>
       <c r="D60" t="n">
-        <v>865.0</v>
+        <v>866.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1566.0</v>
+        <v>1567.0</v>
       </c>
       <c r="D61" t="n">
-        <v>12996.0</v>
+        <v>13028.0</v>
       </c>
     </row>
     <row r="62">
@@ -1325,7 +1325,7 @@
         <v>1430.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2566.0</v>
+        <v>2579.0</v>
       </c>
     </row>
     <row r="64">
@@ -1353,7 +1353,7 @@
         <v>1558.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1097.0</v>
+        <v>1100.0</v>
       </c>
     </row>
     <row r="66">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>449.0</v>
+        <v>450.0</v>
       </c>
       <c r="D88" t="n">
         <v>125.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>270.0</v>
+        <v>271.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>813.0</v>
+        <v>814.0</v>
       </c>
       <c r="D91" t="n">
         <v>20.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>333.0</v>
+        <v>334.0</v>
       </c>
       <c r="D92" t="n">
         <v>53.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1302.0</v>
+        <v>1307.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="D94" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1126.0</v>
+        <v>1133.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2170.0</v>
+        <v>2175.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1080.0</v>
+        <v>1086.0</v>
       </c>
     </row>
     <row r="8">
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>889.0</v>
+        <v>892.0</v>
       </c>
       <c r="D30" t="n">
         <v>55.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
       <c r="D32" t="n">
         <v>50.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>5507.0</v>
+        <v>5509.0</v>
       </c>
       <c r="D33" t="n">
         <v>212.0</v>
@@ -1255,7 +1255,7 @@
         <v>638.0</v>
       </c>
       <c r="D58" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="59">
@@ -1297,7 +1297,7 @@
         <v>1567.0</v>
       </c>
       <c r="D61" t="n">
-        <v>13028.0</v>
+        <v>13041.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2887.0</v>
+        <v>2888.0</v>
       </c>
       <c r="D62" t="n">
         <v>676.0</v>
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1430.0</v>
+        <v>1431.0</v>
       </c>
       <c r="D63" t="n">
         <v>2579.0</v>
@@ -1353,7 +1353,7 @@
         <v>1558.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1100.0</v>
+        <v>1101.0</v>
       </c>
     </row>
     <row r="66">
@@ -1395,7 +1395,7 @@
         <v>214.0</v>
       </c>
       <c r="D68" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="69">
@@ -1406,7 +1406,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>85.0</v>
+        <v>88.0</v>
       </c>
       <c r="D69" t="n">
         <v>107.0</v>
@@ -1462,7 +1462,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
       <c r="D73" t="n">
         <v>42.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1307.0</v>
+        <v>1308.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>334.0</v>
+        <v>344.0</v>
       </c>
       <c r="D92" t="n">
         <v>53.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1308.0</v>
+        <v>1314.0</v>
       </c>
       <c r="D93" t="n">
         <v>43.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>971.0</v>
+        <v>977.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>458.0</v>
+        <v>462.0</v>
       </c>
       <c r="D3" t="n">
         <v>67.0</v>
@@ -499,7 +499,7 @@
         <v>186.0</v>
       </c>
       <c r="D4" t="n">
-        <v>354.0</v>
+        <v>357.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>228.0</v>
+        <v>229.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="D27" t="n">
         <v>151.0</v>
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="D28" t="n">
         <v>6.0</v>
@@ -846,10 +846,10 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="D29" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="30">
@@ -1227,7 +1227,7 @@
         <v>755.0</v>
       </c>
       <c r="D56" t="n">
-        <v>447.0</v>
+        <v>449.0</v>
       </c>
     </row>
     <row r="57">
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="D57" t="n">
         <v>161.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1567.0</v>
+        <v>1568.0</v>
       </c>
       <c r="D61" t="n">
-        <v>13041.0</v>
+        <v>13074.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>2888.0</v>
       </c>
       <c r="D62" t="n">
-        <v>676.0</v>
+        <v>677.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>1431.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2579.0</v>
+        <v>2581.0</v>
       </c>
     </row>
     <row r="64">
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
     </row>
     <row r="67">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>131.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="104">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -989,7 +989,7 @@
         <v>132.0</v>
       </c>
       <c r="D39" t="n">
-        <v>897.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="40">
@@ -1003,7 +1003,7 @@
         <v>177.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2156.0</v>
+        <v>2159.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>434.0</v>
+        <v>437.0</v>
       </c>
       <c r="D41" t="n">
         <v>38.0</v>
@@ -1028,10 +1028,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3983.0</v>
+        <v>3985.0</v>
       </c>
     </row>
     <row r="43">
@@ -1045,7 +1045,7 @@
         <v>29.0</v>
       </c>
       <c r="D43" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>8.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1450.0</v>
+        <v>1453.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>732.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1884.0</v>
+        <v>1885.0</v>
       </c>
     </row>
     <row r="47">
@@ -1112,7 +1112,7 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1285.0</v>
+        <v>1290.0</v>
       </c>
       <c r="D48" t="n">
         <v>3885.0</v>
@@ -1294,7 +1294,7 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1568.0</v>
+        <v>1569.0</v>
       </c>
       <c r="D61" t="n">
         <v>13074.0</v>
@@ -1311,7 +1311,7 @@
         <v>2888.0</v>
       </c>
       <c r="D62" t="n">
-        <v>677.0</v>
+        <v>679.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1431.0</v>
+        <v>1433.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2581.0</v>
+        <v>2584.0</v>
       </c>
     </row>
     <row r="64">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1558.0</v>
+        <v>1559.0</v>
       </c>
       <c r="D65" t="n">
         <v>1101.0</v>
@@ -1367,7 +1367,7 @@
         <v>9.0</v>
       </c>
       <c r="D66" t="n">
-        <v>535.0</v>
+        <v>536.0</v>
       </c>
     </row>
     <row r="67">
@@ -1563,7 +1563,7 @@
         <v>6.0</v>
       </c>
       <c r="D80" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="81">
@@ -1630,7 +1630,7 @@
         <v>108</v>
       </c>
       <c r="C85" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="D85" t="n">
         <v>9.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>271.0</v>
+        <v>272.0</v>
       </c>
       <c r="D89" t="n">
         <v>107.0</v>
@@ -1815,7 +1815,7 @@
         <v>97.0</v>
       </c>
       <c r="D98" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="99">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
   <si>
     <t>Region</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>Parma</t>
+  </si>
+  <si>
+    <t>Piacenza</t>
   </si>
   <si>
     <t>Ravenna</t>
@@ -692,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>674.0</v>
+        <v>680.0</v>
       </c>
       <c r="D18" t="n">
         <v>252.0</v>
@@ -734,10 +737,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>392.0</v>
+        <v>396.0</v>
       </c>
       <c r="D21" t="n">
-        <v>517.0</v>
+        <v>519.0</v>
       </c>
     </row>
     <row r="22">
@@ -751,7 +754,7 @@
         <v>34.0</v>
       </c>
       <c r="D22" t="n">
-        <v>271.0</v>
+        <v>275.0</v>
       </c>
     </row>
     <row r="23">
@@ -762,10 +765,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="n">
-        <v>76.0</v>
+        <v>0.0</v>
       </c>
       <c r="D23" t="n">
-        <v>384.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -776,10 +779,10 @@
         <v>47</v>
       </c>
       <c r="C24" t="n">
-        <v>110.0</v>
+        <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>276.0</v>
+        <v>385.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,24 +793,24 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>25.0</v>
+        <v>110.0</v>
       </c>
       <c r="D25" t="n">
-        <v>82.0</v>
+        <v>281.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>152.0</v>
+        <v>25.0</v>
       </c>
       <c r="D26" t="n">
-        <v>12.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="27">
@@ -818,10 +821,10 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>241.0</v>
+        <v>152.0</v>
       </c>
       <c r="D27" t="n">
-        <v>151.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="28">
@@ -832,10 +835,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>160.0</v>
+        <v>241.0</v>
       </c>
       <c r="D28" t="n">
-        <v>6.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="29">
@@ -846,24 +849,24 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>158.0</v>
+        <v>160.0</v>
       </c>
       <c r="D29" t="n">
-        <v>155.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>892.0</v>
+        <v>158.0</v>
       </c>
       <c r="D30" t="n">
-        <v>55.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="31">
@@ -874,10 +877,10 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>311.0</v>
+        <v>895.0</v>
       </c>
       <c r="D31" t="n">
-        <v>9.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="32">
@@ -888,10 +891,10 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>320.0</v>
+        <v>311.0</v>
       </c>
       <c r="D32" t="n">
-        <v>50.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="33">
@@ -902,10 +905,10 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>5509.0</v>
+        <v>320.0</v>
       </c>
       <c r="D33" t="n">
-        <v>212.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="34">
@@ -916,24 +919,24 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>905.0</v>
+        <v>5519.0</v>
       </c>
       <c r="D34" t="n">
-        <v>87.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>15.0</v>
+        <v>908.0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="36">
@@ -944,10 +947,10 @@
         <v>59</v>
       </c>
       <c r="C36" t="n">
-        <v>250.0</v>
+        <v>15.0</v>
       </c>
       <c r="D36" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -958,10 +961,10 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>4.0</v>
+        <v>250.0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="38">
@@ -972,24 +975,24 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>644.0</v>
+        <v>4.0</v>
       </c>
       <c r="D38" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>132.0</v>
+        <v>644.0</v>
       </c>
       <c r="D39" t="n">
-        <v>904.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="40">
@@ -1000,10 +1003,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>177.0</v>
+        <v>132.0</v>
       </c>
       <c r="D40" t="n">
-        <v>2159.0</v>
+        <v>904.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1017,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>437.0</v>
+        <v>177.0</v>
       </c>
       <c r="D41" t="n">
-        <v>38.0</v>
+        <v>2159.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,10 +1031,10 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>133.0</v>
+        <v>437.0</v>
       </c>
       <c r="D42" t="n">
-        <v>3985.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="43">
@@ -1042,10 +1045,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>29.0</v>
+        <v>133.0</v>
       </c>
       <c r="D43" t="n">
-        <v>35.0</v>
+        <v>3985.0</v>
       </c>
     </row>
     <row r="44">
@@ -1056,10 +1059,10 @@
         <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>53.0</v>
+        <v>29.0</v>
       </c>
       <c r="D44" t="n">
-        <v>24331.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="45">
@@ -1070,10 +1073,10 @@
         <v>68</v>
       </c>
       <c r="C45" t="n">
-        <v>8.0</v>
+        <v>81.0</v>
       </c>
       <c r="D45" t="n">
-        <v>1453.0</v>
+        <v>24858.0</v>
       </c>
     </row>
     <row r="46">
@@ -1084,10 +1087,10 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>732.0</v>
+        <v>8.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1885.0</v>
+        <v>1453.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,10 +1101,10 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>1.0</v>
+        <v>732.0</v>
       </c>
       <c r="D47" t="n">
-        <v>11.0</v>
+        <v>1885.0</v>
       </c>
     </row>
     <row r="48">
@@ -1112,10 +1115,10 @@
         <v>71</v>
       </c>
       <c r="C48" t="n">
-        <v>1290.0</v>
+        <v>1.0</v>
       </c>
       <c r="D48" t="n">
-        <v>3885.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="49">
@@ -1126,10 +1129,10 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>25.0</v>
+        <v>1681.0</v>
       </c>
       <c r="D49" t="n">
-        <v>56.0</v>
+        <v>3902.0</v>
       </c>
     </row>
     <row r="50">
@@ -1140,24 +1143,24 @@
         <v>73</v>
       </c>
       <c r="C50" t="n">
-        <v>747.0</v>
+        <v>25.0</v>
       </c>
       <c r="D50" t="n">
-        <v>75.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>370.0</v>
+        <v>747.0</v>
       </c>
       <c r="D51" t="n">
-        <v>97.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="52">
@@ -1168,10 +1171,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>240.0</v>
+        <v>370.0</v>
       </c>
       <c r="D52" t="n">
-        <v>57.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="53">
@@ -1182,10 +1185,10 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>106.0</v>
+        <v>240.0</v>
       </c>
       <c r="D53" t="n">
-        <v>172.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="54">
@@ -1196,10 +1199,10 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>486.0</v>
+        <v>106.0</v>
       </c>
       <c r="D54" t="n">
-        <v>135.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,24 +1213,24 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>425.0</v>
+        <v>486.0</v>
       </c>
       <c r="D55" t="n">
-        <v>145.0</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>755.0</v>
+        <v>425.0</v>
       </c>
       <c r="D56" t="n">
-        <v>449.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="57">
@@ -1238,24 +1241,24 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>166.0</v>
+        <v>755.0</v>
       </c>
       <c r="D57" t="n">
-        <v>161.0</v>
+        <v>449.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s">
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>638.0</v>
+        <v>166.0</v>
       </c>
       <c r="D58" t="n">
-        <v>137.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>765.0</v>
+        <v>1716.0</v>
       </c>
       <c r="D59" t="n">
-        <v>146.0</v>
+        <v>336.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,10 +1283,10 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>728.0</v>
+        <v>1580.0</v>
       </c>
       <c r="D60" t="n">
-        <v>866.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="61">
@@ -1294,10 +1297,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>1569.0</v>
+        <v>728.0</v>
       </c>
       <c r="D61" t="n">
-        <v>13074.0</v>
+        <v>866.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>2888.0</v>
+        <v>1483.0</v>
       </c>
       <c r="D62" t="n">
-        <v>679.0</v>
+        <v>12926.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1325,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>1433.0</v>
+        <v>2888.0</v>
       </c>
       <c r="D63" t="n">
-        <v>2584.0</v>
+        <v>679.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>62.0</v>
+        <v>1433.0</v>
       </c>
       <c r="D64" t="n">
-        <v>25.0</v>
+        <v>2584.0</v>
       </c>
     </row>
     <row r="65">
@@ -1350,52 +1353,52 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>1559.0</v>
+        <v>62.0</v>
       </c>
       <c r="D65" t="n">
-        <v>1101.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B66" t="s">
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>9.0</v>
+        <v>1559.0</v>
       </c>
       <c r="D66" t="n">
-        <v>536.0</v>
+        <v>1101.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
         <v>90</v>
       </c>
       <c r="C67" t="n">
-        <v>37.0</v>
+        <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>144.0</v>
+        <v>536.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>214.0</v>
+        <v>37.0</v>
       </c>
       <c r="D68" t="n">
-        <v>199.0</v>
+        <v>144.0</v>
       </c>
     </row>
     <row r="69">
@@ -1406,10 +1409,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>88.0</v>
+        <v>214.0</v>
       </c>
       <c r="D69" t="n">
-        <v>107.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="70">
@@ -1420,10 +1423,10 @@
         <v>93</v>
       </c>
       <c r="C70" t="n">
-        <v>3.0</v>
+        <v>88.0</v>
       </c>
       <c r="D70" t="n">
-        <v>24.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="71">
@@ -1434,10 +1437,10 @@
         <v>94</v>
       </c>
       <c r="C71" t="n">
-        <v>154.0</v>
+        <v>3.0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="72">
@@ -1448,10 +1451,10 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>16.0</v>
+        <v>154.0</v>
       </c>
       <c r="D72" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -1462,24 +1465,24 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>298.0</v>
+        <v>16.0</v>
       </c>
       <c r="D73" t="n">
-        <v>42.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>50.0</v>
+        <v>298.0</v>
       </c>
       <c r="D74" t="n">
-        <v>72.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="75">
@@ -1490,10 +1493,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>681.0</v>
+        <v>50.0</v>
       </c>
       <c r="D75" t="n">
-        <v>434.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1507,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>472.0</v>
+        <v>681.0</v>
       </c>
       <c r="D76" t="n">
-        <v>447.0</v>
+        <v>434.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1521,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>1773.0</v>
+        <v>472.0</v>
       </c>
       <c r="D77" t="n">
-        <v>538.0</v>
+        <v>447.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,24 +1535,24 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>328.0</v>
+        <v>1773.0</v>
       </c>
       <c r="D78" t="n">
-        <v>499.0</v>
+        <v>538.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B79" t="s">
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>6.0</v>
+        <v>328.0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0</v>
+        <v>499.0</v>
       </c>
     </row>
     <row r="80">
@@ -1563,7 +1566,7 @@
         <v>6.0</v>
       </c>
       <c r="D80" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -1574,10 +1577,10 @@
         <v>104</v>
       </c>
       <c r="C81" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="D81" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="82">
@@ -1588,10 +1591,10 @@
         <v>105</v>
       </c>
       <c r="C82" t="n">
-        <v>53.0</v>
+        <v>3.0</v>
       </c>
       <c r="D82" t="n">
-        <v>184.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="83">
@@ -1602,10 +1605,10 @@
         <v>106</v>
       </c>
       <c r="C83" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="D83" t="n">
-        <v>3.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="84">
@@ -1616,10 +1619,10 @@
         <v>107</v>
       </c>
       <c r="C84" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="D84" t="n">
         <v>3.0</v>
-      </c>
-      <c r="D84" t="n">
-        <v>18.0</v>
       </c>
     </row>
     <row r="85">
@@ -1630,10 +1633,10 @@
         <v>108</v>
       </c>
       <c r="C85" t="n">
-        <v>42.0</v>
+        <v>3.0</v>
       </c>
       <c r="D85" t="n">
-        <v>9.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="86">
@@ -1644,24 +1647,24 @@
         <v>109</v>
       </c>
       <c r="C86" t="n">
-        <v>12.0</v>
+        <v>42.0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B87" t="s">
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>463.0</v>
+        <v>12.0</v>
       </c>
       <c r="D87" t="n">
-        <v>277.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -1672,10 +1675,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>450.0</v>
+        <v>463.0</v>
       </c>
       <c r="D88" t="n">
-        <v>125.0</v>
+        <v>277.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,10 +1689,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>272.0</v>
+        <v>450.0</v>
       </c>
       <c r="D89" t="n">
-        <v>107.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="90">
@@ -1700,10 +1703,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>167.0</v>
+        <v>276.0</v>
       </c>
       <c r="D90" t="n">
-        <v>62.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="91">
@@ -1714,10 +1717,10 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>814.0</v>
+        <v>167.0</v>
       </c>
       <c r="D91" t="n">
-        <v>20.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="92">
@@ -1728,10 +1731,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>344.0</v>
+        <v>815.0</v>
       </c>
       <c r="D92" t="n">
-        <v>53.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="93">
@@ -1742,10 +1745,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>1314.0</v>
+        <v>344.0</v>
       </c>
       <c r="D93" t="n">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="94">
@@ -1756,10 +1759,10 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>103.0</v>
+        <v>1316.0</v>
       </c>
       <c r="D94" t="n">
-        <v>17.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="95">
@@ -1770,24 +1773,24 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>153.0</v>
+        <v>103.0</v>
       </c>
       <c r="D95" t="n">
-        <v>216.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B96" t="s">
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>816.0</v>
+        <v>153.0</v>
       </c>
       <c r="D96" t="n">
-        <v>451.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,38 +1801,38 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>588.0</v>
+        <v>816.0</v>
       </c>
       <c r="D97" t="n">
-        <v>145.0</v>
+        <v>451.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B98" t="s">
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>97.0</v>
+        <v>588.0</v>
       </c>
       <c r="D98" t="n">
-        <v>43.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B99" t="s">
         <v>122</v>
       </c>
       <c r="C99" t="n">
-        <v>30.0</v>
+        <v>97.0</v>
       </c>
       <c r="D99" t="n">
-        <v>209.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,10 +1843,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>215.0</v>
+        <v>30.0</v>
       </c>
       <c r="D100" t="n">
-        <v>147.0</v>
+        <v>209.0</v>
       </c>
     </row>
     <row r="101">
@@ -1854,10 +1857,10 @@
         <v>124</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0</v>
+        <v>215.0</v>
       </c>
       <c r="D101" t="n">
-        <v>99.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="102">
@@ -1868,10 +1871,10 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>102.0</v>
+        <v>0.0</v>
       </c>
       <c r="D102" t="n">
-        <v>197.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="103">
@@ -1882,10 +1885,10 @@
         <v>126</v>
       </c>
       <c r="C103" t="n">
-        <v>9.0</v>
+        <v>102.0</v>
       </c>
       <c r="D103" t="n">
-        <v>133.0</v>
+        <v>197.0</v>
       </c>
     </row>
     <row r="104">
@@ -1896,10 +1899,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>120.0</v>
+        <v>9.0</v>
       </c>
       <c r="D104" t="n">
-        <v>316.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,9 +1913,23 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>316.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>24</v>
+      </c>
+      <c r="B106" t="s">
+        <v>129</v>
+      </c>
+      <c r="C106" t="n">
         <v>80.0</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D106" t="n">
         <v>182.0</v>
       </c>
     </row>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -555,7 +555,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>541.0</v>
+        <v>549.0</v>
       </c>
       <c r="D8" t="n">
         <v>157.0</v>
@@ -569,10 +569,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>277.0</v>
+        <v>285.0</v>
       </c>
       <c r="D9" t="n">
-        <v>576.0</v>
+        <v>578.0</v>
       </c>
     </row>
     <row r="10">
@@ -597,7 +597,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>2797.0</v>
+        <v>2798.0</v>
       </c>
       <c r="D11" t="n">
         <v>565.0</v>
@@ -611,7 +611,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>222.0</v>
+        <v>228.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -625,7 +625,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>880.0</v>
+        <v>884.0</v>
       </c>
       <c r="D13" t="n">
         <v>334.0</v>
@@ -639,7 +639,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>580.0</v>
+        <v>582.0</v>
       </c>
       <c r="D14" t="n">
         <v>111.0</v>
@@ -653,7 +653,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>682.0</v>
+        <v>686.0</v>
       </c>
       <c r="D15" t="n">
         <v>177.0</v>
@@ -667,7 +667,7 @@
         <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="D16" t="n">
         <v>89.0</v>
@@ -681,7 +681,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9271.0</v>
+        <v>9279.0</v>
       </c>
       <c r="D17" t="n">
         <v>906.0</v>
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>680.0</v>
+        <v>685.0</v>
       </c>
       <c r="D18" t="n">
         <v>252.0</v>
@@ -726,7 +726,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
     </row>
     <row r="21">
@@ -737,7 +737,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>396.0</v>
+        <v>403.0</v>
       </c>
       <c r="D21" t="n">
         <v>519.0</v>
@@ -754,7 +754,7 @@
         <v>34.0</v>
       </c>
       <c r="D22" t="n">
-        <v>275.0</v>
+        <v>276.0</v>
       </c>
     </row>
     <row r="23">
@@ -1272,7 +1272,7 @@
         <v>1716.0</v>
       </c>
       <c r="D59" t="n">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="60">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1483.0</v>
+        <v>1486.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12926.0</v>
+        <v>12971.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1433.0</v>
+        <v>1434.0</v>
       </c>
       <c r="D64" t="n">
         <v>2584.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -877,7 +877,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>895.0</v>
+        <v>896.0</v>
       </c>
       <c r="D31" t="n">
         <v>55.0</v>
@@ -891,7 +891,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>311.0</v>
+        <v>312.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1269,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1716.0</v>
+        <v>1717.0</v>
       </c>
       <c r="D59" t="n">
-        <v>337.0</v>
+        <v>341.0</v>
       </c>
     </row>
     <row r="60">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1486.0</v>
+        <v>1487.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12971.0</v>
+        <v>12984.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1434.0</v>
+        <v>1436.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2584.0</v>
+        <v>2585.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,10 +1367,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1559.0</v>
+        <v>1569.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1101.0</v>
+        <v>1105.0</v>
       </c>
     </row>
     <row r="67">
@@ -1675,7 +1675,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>463.0</v>
+        <v>464.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1689,10 +1689,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>450.0</v>
+        <v>452.0</v>
       </c>
       <c r="D89" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
     </row>
     <row r="90">
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>276.0</v>
+        <v>279.0</v>
       </c>
       <c r="D90" t="n">
         <v>107.0</v>
@@ -1731,7 +1731,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>815.0</v>
+        <v>816.0</v>
       </c>
       <c r="D92" t="n">
         <v>20.0</v>
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>344.0</v>
+        <v>354.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1759,10 +1759,10 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>1316.0</v>
+        <v>1318.0</v>
       </c>
       <c r="D94" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="95">
@@ -1773,7 +1773,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="D95" t="n">
         <v>17.0</v>
@@ -1801,10 +1801,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>816.0</v>
+        <v>815.0</v>
       </c>
       <c r="D97" t="n">
-        <v>451.0</v>
+        <v>452.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>452.0</v>
+        <v>453.0</v>
       </c>
       <c r="D89" t="n">
         <v>126.0</v>
@@ -1731,7 +1731,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>816.0</v>
+        <v>818.0</v>
       </c>
       <c r="D92" t="n">
         <v>20.0</v>
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>354.0</v>
+        <v>356.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>1318.0</v>
+        <v>1322.0</v>
       </c>
       <c r="D94" t="n">
         <v>45.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -471,7 +471,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>977.0</v>
+        <v>981.0</v>
       </c>
       <c r="D2" t="n">
         <v>80.0</v>
@@ -485,10 +485,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>462.0</v>
+        <v>464.0</v>
       </c>
       <c r="D3" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>186.0</v>
       </c>
       <c r="D4" t="n">
-        <v>357.0</v>
+        <v>358.0</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>229.0</v>
+        <v>230.0</v>
       </c>
       <c r="D5" t="n">
         <v>115.0</v>
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>685.0</v>
+        <v>692.0</v>
       </c>
       <c r="D18" t="n">
         <v>252.0</v>
@@ -737,10 +737,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>403.0</v>
+        <v>404.0</v>
       </c>
       <c r="D21" t="n">
-        <v>519.0</v>
+        <v>520.0</v>
       </c>
     </row>
     <row r="22">
@@ -796,7 +796,7 @@
         <v>110.0</v>
       </c>
       <c r="D25" t="n">
-        <v>281.0</v>
+        <v>283.0</v>
       </c>
     </row>
     <row r="26">
@@ -1241,7 +1241,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>755.0</v>
+        <v>756.0</v>
       </c>
       <c r="D57" t="n">
         <v>449.0</v>
@@ -1269,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1717.0</v>
+        <v>1719.0</v>
       </c>
       <c r="D59" t="n">
-        <v>341.0</v>
+        <v>342.0</v>
       </c>
     </row>
     <row r="60">
@@ -1300,7 +1300,7 @@
         <v>728.0</v>
       </c>
       <c r="D61" t="n">
-        <v>866.0</v>
+        <v>868.0</v>
       </c>
     </row>
     <row r="62">
@@ -1314,7 +1314,7 @@
         <v>1487.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12984.0</v>
+        <v>13006.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2888.0</v>
       </c>
       <c r="D63" t="n">
-        <v>679.0</v>
+        <v>683.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1436.0</v>
+        <v>1440.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2585.0</v>
+        <v>2586.0</v>
       </c>
     </row>
     <row r="65">
@@ -1356,7 +1356,7 @@
         <v>62.0</v>
       </c>
       <c r="D65" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="66">
@@ -1370,7 +1370,7 @@
         <v>1569.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1105.0</v>
+        <v>1106.0</v>
       </c>
     </row>
     <row r="67">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -527,7 +527,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1133.0</v>
+        <v>1142.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -544,7 +544,7 @@
         <v>2175.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1086.0</v>
+        <v>1091.0</v>
       </c>
     </row>
     <row r="8">
@@ -821,7 +821,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="D27" t="n">
         <v>12.0</v>
@@ -835,10 +835,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="D28" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="29">
@@ -863,10 +863,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="D30" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="31">
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5519.0</v>
+        <v>5520.0</v>
       </c>
       <c r="D34" t="n">
         <v>212.0</v>
@@ -989,7 +989,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>644.0</v>
+        <v>645.0</v>
       </c>
       <c r="D39" t="n">
         <v>14.0</v>
@@ -1006,7 +1006,7 @@
         <v>132.0</v>
       </c>
       <c r="D40" t="n">
-        <v>904.0</v>
+        <v>906.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,10 +1017,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2159.0</v>
+        <v>2164.0</v>
       </c>
     </row>
     <row r="42">
@@ -1031,7 +1031,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>437.0</v>
+        <v>438.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1048,7 +1048,7 @@
         <v>133.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3985.0</v>
+        <v>3986.0</v>
       </c>
     </row>
     <row r="44">
@@ -1076,7 +1076,7 @@
         <v>81.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24858.0</v>
+        <v>24861.0</v>
       </c>
     </row>
     <row r="46">
@@ -1090,7 +1090,7 @@
         <v>8.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1453.0</v>
+        <v>1455.0</v>
       </c>
     </row>
     <row r="47">
@@ -1104,7 +1104,7 @@
         <v>732.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1885.0</v>
+        <v>1888.0</v>
       </c>
     </row>
     <row r="48">
@@ -1118,7 +1118,7 @@
         <v>1.0</v>
       </c>
       <c r="D48" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="49">
@@ -1129,7 +1129,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1681.0</v>
+        <v>1683.0</v>
       </c>
       <c r="D49" t="n">
         <v>3902.0</v>
@@ -1157,7 +1157,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>747.0</v>
+        <v>748.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1269,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1719.0</v>
+        <v>1720.0</v>
       </c>
       <c r="D59" t="n">
         <v>342.0</v>
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1580.0</v>
+        <v>1581.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1300,7 +1300,7 @@
         <v>728.0</v>
       </c>
       <c r="D61" t="n">
-        <v>868.0</v>
+        <v>871.0</v>
       </c>
     </row>
     <row r="62">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1440.0</v>
+        <v>1441.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2586.0</v>
+        <v>2590.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,10 +1367,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1569.0</v>
+        <v>1570.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1106.0</v>
+        <v>1107.0</v>
       </c>
     </row>
     <row r="67">
@@ -1384,7 +1384,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>536.0</v>
+        <v>538.0</v>
       </c>
     </row>
     <row r="68">
@@ -1409,10 +1409,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
       <c r="D69" t="n">
-        <v>199.0</v>
+        <v>201.0</v>
       </c>
     </row>
     <row r="70">
@@ -1426,7 +1426,7 @@
         <v>88.0</v>
       </c>
       <c r="D70" t="n">
-        <v>107.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="71">
@@ -1451,7 +1451,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="D72" t="n">
         <v>0.0</v>
@@ -1465,7 +1465,7 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D73" t="n">
         <v>16.0</v>
@@ -1482,7 +1482,7 @@
         <v>298.0</v>
       </c>
       <c r="D74" t="n">
-        <v>42.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="75">
@@ -1675,7 +1675,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>464.0</v>
+        <v>467.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1717,7 +1717,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="D91" t="n">
         <v>62.0</v>
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>356.0</v>
+        <v>359.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1888,7 +1888,7 @@
         <v>102.0</v>
       </c>
       <c r="D103" t="n">
-        <v>197.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="104">
@@ -1913,10 +1913,10 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>120.0</v>
+        <v>122.0</v>
       </c>
       <c r="D105" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
     </row>
     <row r="106">
@@ -1930,7 +1930,7 @@
         <v>80.0</v>
       </c>
       <c r="D106" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>692.0</v>
+        <v>699.0</v>
       </c>
       <c r="D18" t="n">
         <v>252.0</v>
@@ -737,10 +737,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>404.0</v>
+        <v>409.0</v>
       </c>
       <c r="D21" t="n">
-        <v>520.0</v>
+        <v>522.0</v>
       </c>
     </row>
     <row r="22">
@@ -754,7 +754,7 @@
         <v>34.0</v>
       </c>
       <c r="D22" t="n">
-        <v>276.0</v>
+        <v>277.0</v>
       </c>
     </row>
     <row r="23">
@@ -793,10 +793,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>110.0</v>
+        <v>112.0</v>
       </c>
       <c r="D25" t="n">
-        <v>283.0</v>
+        <v>285.0</v>
       </c>
     </row>
     <row r="26">
@@ -877,7 +877,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>896.0</v>
+        <v>898.0</v>
       </c>
       <c r="D31" t="n">
         <v>55.0</v>
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5520.0</v>
+        <v>5528.0</v>
       </c>
       <c r="D34" t="n">
         <v>212.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1487.0</v>
+        <v>1489.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13006.0</v>
+        <v>13025.0</v>
       </c>
     </row>
     <row r="63">
@@ -1342,7 +1342,7 @@
         <v>1441.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2590.0</v>
+        <v>2592.0</v>
       </c>
     </row>
     <row r="65">
@@ -1675,7 +1675,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>467.0</v>
+        <v>468.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>453.0</v>
+        <v>454.0</v>
       </c>
       <c r="D89" t="n">
         <v>126.0</v>
@@ -1731,7 +1731,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>818.0</v>
+        <v>820.0</v>
       </c>
       <c r="D92" t="n">
         <v>20.0</v>
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>359.0</v>
+        <v>361.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1773,7 +1773,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="D95" t="n">
         <v>17.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -838,7 +838,7 @@
         <v>242.0</v>
       </c>
       <c r="D28" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="29">
@@ -863,10 +863,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="D30" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="31">
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>251.0</v>
+        <v>250.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1269,7 +1269,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1720.0</v>
+        <v>1721.0</v>
       </c>
       <c r="D59" t="n">
         <v>342.0</v>
@@ -1300,7 +1300,7 @@
         <v>728.0</v>
       </c>
       <c r="D61" t="n">
-        <v>871.0</v>
+        <v>873.0</v>
       </c>
     </row>
     <row r="62">
@@ -1314,7 +1314,7 @@
         <v>1489.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13025.0</v>
+        <v>13042.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2888.0</v>
       </c>
       <c r="D63" t="n">
-        <v>683.0</v>
+        <v>684.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1441.0</v>
+        <v>1444.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2592.0</v>
+        <v>2598.0</v>
       </c>
     </row>
     <row r="65">
@@ -1370,7 +1370,7 @@
         <v>1570.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1107.0</v>
+        <v>1115.0</v>
       </c>
     </row>
     <row r="67">
@@ -1384,7 +1384,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>538.0</v>
+        <v>539.0</v>
       </c>
     </row>
     <row r="68">
@@ -1675,7 +1675,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>468.0</v>
+        <v>469.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1689,10 +1689,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>454.0</v>
+        <v>456.0</v>
       </c>
       <c r="D89" t="n">
-        <v>126.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="90">
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>361.0</v>
+        <v>366.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>1322.0</v>
+        <v>1331.0</v>
       </c>
       <c r="D94" t="n">
         <v>45.0</v>
@@ -1843,10 +1843,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="D100" t="n">
-        <v>209.0</v>
+        <v>211.0</v>
       </c>
     </row>
     <row r="101">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -695,7 +695,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>699.0</v>
+        <v>708.0</v>
       </c>
       <c r="D18" t="n">
         <v>252.0</v>
@@ -796,7 +796,7 @@
         <v>112.0</v>
       </c>
       <c r="D25" t="n">
-        <v>285.0</v>
+        <v>286.0</v>
       </c>
     </row>
     <row r="26">
@@ -1003,7 +1003,7 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="D40" t="n">
         <v>906.0</v>
@@ -1017,7 +1017,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="D41" t="n">
         <v>2164.0</v>
@@ -1031,7 +1031,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1076,7 +1076,7 @@
         <v>81.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24861.0</v>
+        <v>24862.0</v>
       </c>
     </row>
     <row r="46">
@@ -1090,7 +1090,7 @@
         <v>8.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1455.0</v>
+        <v>1457.0</v>
       </c>
     </row>
     <row r="47">
@@ -1157,7 +1157,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>748.0</v>
+        <v>749.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1489.0</v>
+        <v>1493.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13042.0</v>
+        <v>13061.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2888.0</v>
       </c>
       <c r="D63" t="n">
-        <v>684.0</v>
+        <v>685.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1444.0</v>
+        <v>1445.0</v>
       </c>
       <c r="D64" t="n">
         <v>2598.0</v>
@@ -1370,7 +1370,7 @@
         <v>1570.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1115.0</v>
+        <v>1116.0</v>
       </c>
     </row>
     <row r="67">
@@ -1496,7 +1496,7 @@
         <v>50.0</v>
       </c>
       <c r="D75" t="n">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="76">
@@ -1507,10 +1507,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>681.0</v>
+        <v>686.0</v>
       </c>
       <c r="D76" t="n">
-        <v>434.0</v>
+        <v>436.0</v>
       </c>
     </row>
     <row r="77">
@@ -1521,10 +1521,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>472.0</v>
+        <v>484.0</v>
       </c>
       <c r="D77" t="n">
-        <v>447.0</v>
+        <v>456.0</v>
       </c>
     </row>
     <row r="78">
@@ -1535,10 +1535,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1773.0</v>
+        <v>1796.0</v>
       </c>
       <c r="D78" t="n">
-        <v>538.0</v>
+        <v>541.0</v>
       </c>
     </row>
     <row r="79">
@@ -1549,10 +1549,10 @@
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>328.0</v>
+        <v>332.0</v>
       </c>
       <c r="D79" t="n">
-        <v>499.0</v>
+        <v>503.0</v>
       </c>
     </row>
     <row r="80">
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>456.0</v>
+        <v>457.0</v>
       </c>
       <c r="D89" t="n">
         <v>129.0</v>
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>279.0</v>
+        <v>281.0</v>
       </c>
       <c r="D90" t="n">
         <v>107.0</v>
@@ -1790,7 +1790,7 @@
         <v>153.0</v>
       </c>
       <c r="D96" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -474,7 +474,7 @@
         <v>981.0</v>
       </c>
       <c r="D2" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>464.0</v>
+        <v>465.0</v>
       </c>
       <c r="D3" t="n">
         <v>68.0</v>
@@ -499,10 +499,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="D4" t="n">
-        <v>358.0</v>
+        <v>359.0</v>
       </c>
     </row>
     <row r="5">
@@ -513,10 +513,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="D5" t="n">
-        <v>115.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="6">
@@ -1241,10 +1241,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>756.0</v>
+        <v>760.0</v>
       </c>
       <c r="D57" t="n">
-        <v>449.0</v>
+        <v>452.0</v>
       </c>
     </row>
     <row r="58">
@@ -1255,7 +1255,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="D58" t="n">
         <v>161.0</v>
@@ -1269,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1721.0</v>
+        <v>1722.0</v>
       </c>
       <c r="D59" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1581.0</v>
+        <v>1582.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1297,10 +1297,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>728.0</v>
+        <v>729.0</v>
       </c>
       <c r="D61" t="n">
-        <v>873.0</v>
+        <v>874.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1493.0</v>
+        <v>1494.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13061.0</v>
+        <v>13084.0</v>
       </c>
     </row>
     <row r="63">
@@ -1328,7 +1328,7 @@
         <v>2888.0</v>
       </c>
       <c r="D63" t="n">
-        <v>685.0</v>
+        <v>687.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1445.0</v>
+        <v>1446.0</v>
       </c>
       <c r="D64" t="n">
         <v>2598.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -625,10 +625,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>884.0</v>
+        <v>891.0</v>
       </c>
       <c r="D13" t="n">
-        <v>334.0</v>
+        <v>337.0</v>
       </c>
     </row>
     <row r="14">
@@ -639,7 +639,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>582.0</v>
+        <v>589.0</v>
       </c>
       <c r="D14" t="n">
         <v>111.0</v>
@@ -653,7 +653,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>686.0</v>
+        <v>690.0</v>
       </c>
       <c r="D15" t="n">
         <v>177.0</v>
@@ -681,7 +681,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9279.0</v>
+        <v>9287.0</v>
       </c>
       <c r="D17" t="n">
         <v>906.0</v>
@@ -877,10 +877,10 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>898.0</v>
+        <v>902.0</v>
       </c>
       <c r="D31" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="32">
@@ -919,10 +919,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5528.0</v>
+        <v>5533.0</v>
       </c>
       <c r="D34" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="35">
@@ -933,7 +933,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>908.0</v>
+        <v>912.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1003,10 +1003,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="D40" t="n">
-        <v>906.0</v>
+        <v>910.0</v>
       </c>
     </row>
     <row r="41">
@@ -1020,7 +1020,7 @@
         <v>179.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2164.0</v>
+        <v>2166.0</v>
       </c>
     </row>
     <row r="42">
@@ -1031,7 +1031,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1045,10 +1045,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3986.0</v>
+        <v>3987.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,10 +1073,10 @@
         <v>68</v>
       </c>
       <c r="C45" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24862.0</v>
+        <v>24863.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>69</v>
       </c>
       <c r="C46" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D46" t="n">
         <v>1457.0</v>
@@ -1101,10 +1101,10 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>732.0</v>
+        <v>733.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1888.0</v>
+        <v>1889.0</v>
       </c>
     </row>
     <row r="48">
@@ -1129,7 +1129,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1683.0</v>
+        <v>1684.0</v>
       </c>
       <c r="D49" t="n">
         <v>3902.0</v>
@@ -1171,10 +1171,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>370.0</v>
+        <v>373.0</v>
       </c>
       <c r="D52" t="n">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="53">
@@ -1216,7 +1216,7 @@
         <v>486.0</v>
       </c>
       <c r="D55" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="56">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1494.0</v>
+        <v>1496.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13084.0</v>
+        <v>13100.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1446.0</v>
+        <v>1447.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2598.0</v>
+        <v>2599.0</v>
       </c>
     </row>
     <row r="65">
@@ -1507,10 +1507,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>686.0</v>
+        <v>688.0</v>
       </c>
       <c r="D76" t="n">
-        <v>436.0</v>
+        <v>438.0</v>
       </c>
     </row>
     <row r="77">
@@ -1535,7 +1535,7 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1796.0</v>
+        <v>1797.0</v>
       </c>
       <c r="D78" t="n">
         <v>541.0</v>
@@ -1552,7 +1552,7 @@
         <v>332.0</v>
       </c>
       <c r="D79" t="n">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
     </row>
     <row r="80">
@@ -1675,7 +1675,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>469.0</v>
+        <v>471.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>457.0</v>
+        <v>459.0</v>
       </c>
       <c r="D89" t="n">
         <v>129.0</v>
@@ -1703,7 +1703,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>281.0</v>
+        <v>283.0</v>
       </c>
       <c r="D90" t="n">
         <v>107.0</v>
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>366.0</v>
+        <v>370.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>1331.0</v>
+        <v>1333.0</v>
       </c>
       <c r="D94" t="n">
         <v>45.0</v>
@@ -1801,10 +1801,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>815.0</v>
+        <v>820.0</v>
       </c>
       <c r="D97" t="n">
-        <v>452.0</v>
+        <v>456.0</v>
       </c>
     </row>
     <row r="98">
@@ -1815,10 +1815,10 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>588.0</v>
+        <v>592.0</v>
       </c>
       <c r="D98" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="99">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -527,7 +527,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1142.0</v>
+        <v>1145.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -541,7 +541,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2175.0</v>
+        <v>2177.0</v>
       </c>
       <c r="D7" t="n">
         <v>1091.0</v>
@@ -695,10 +695,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>708.0</v>
+        <v>724.0</v>
       </c>
       <c r="D18" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
     </row>
     <row r="19">
@@ -740,7 +740,7 @@
         <v>409.0</v>
       </c>
       <c r="D21" t="n">
-        <v>522.0</v>
+        <v>524.0</v>
       </c>
     </row>
     <row r="22">
@@ -849,7 +849,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -863,7 +863,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="D30" t="n">
         <v>157.0</v>
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1017,7 +1017,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="D41" t="n">
         <v>2166.0</v>
@@ -1157,7 +1157,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>749.0</v>
+        <v>750.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1227,7 +1227,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>425.0</v>
+        <v>429.0</v>
       </c>
       <c r="D56" t="n">
         <v>145.0</v>
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1582.0</v>
+        <v>1583.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1496.0</v>
+        <v>1504.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13100.0</v>
+        <v>13102.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1447.0</v>
+        <v>1448.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2599.0</v>
+        <v>2602.0</v>
       </c>
     </row>
     <row r="65">
@@ -1384,7 +1384,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>539.0</v>
+        <v>543.0</v>
       </c>
     </row>
     <row r="68">
@@ -1409,7 +1409,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
       <c r="D69" t="n">
         <v>201.0</v>
@@ -1482,7 +1482,7 @@
         <v>298.0</v>
       </c>
       <c r="D74" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="75">
@@ -1857,7 +1857,7 @@
         <v>124</v>
       </c>
       <c r="C101" t="n">
-        <v>215.0</v>
+        <v>218.0</v>
       </c>
       <c r="D101" t="n">
         <v>147.0</v>
@@ -1874,7 +1874,7 @@
         <v>0.0</v>
       </c>
       <c r="D102" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="103">
@@ -1916,7 +1916,7 @@
         <v>122.0</v>
       </c>
       <c r="D105" t="n">
-        <v>317.0</v>
+        <v>319.0</v>
       </c>
     </row>
     <row r="106">
@@ -1927,7 +1927,7 @@
         <v>129</v>
       </c>
       <c r="C106" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="D106" t="n">
         <v>183.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -726,7 +726,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>312.0</v>
+        <v>313.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -919,7 +919,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5533.0</v>
+        <v>5538.0</v>
       </c>
       <c r="D34" t="n">
         <v>213.0</v>
@@ -961,7 +961,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>251.0</v>
+        <v>252.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1185,7 +1185,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="D53" t="n">
         <v>57.0</v>
@@ -1227,7 +1227,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>429.0</v>
+        <v>430.0</v>
       </c>
       <c r="D56" t="n">
         <v>145.0</v>
@@ -1269,10 +1269,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1722.0</v>
+        <v>1723.0</v>
       </c>
       <c r="D59" t="n">
-        <v>343.0</v>
+        <v>346.0</v>
       </c>
     </row>
     <row r="60">
@@ -1283,7 +1283,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1583.0</v>
+        <v>1585.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1300,7 +1300,7 @@
         <v>729.0</v>
       </c>
       <c r="D61" t="n">
-        <v>874.0</v>
+        <v>878.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,10 +1311,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1504.0</v>
+        <v>1505.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13102.0</v>
+        <v>13138.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,10 +1325,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2888.0</v>
+        <v>2889.0</v>
       </c>
       <c r="D63" t="n">
-        <v>687.0</v>
+        <v>688.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,10 +1339,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1448.0</v>
+        <v>1449.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2602.0</v>
+        <v>2604.0</v>
       </c>
     </row>
     <row r="65">
@@ -1370,7 +1370,7 @@
         <v>1570.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1116.0</v>
+        <v>1119.0</v>
       </c>
     </row>
     <row r="67">
@@ -1552,7 +1552,7 @@
         <v>332.0</v>
       </c>
       <c r="D79" t="n">
-        <v>504.0</v>
+        <v>505.0</v>
       </c>
     </row>
     <row r="80">
@@ -1689,7 +1689,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>459.0</v>
+        <v>460.0</v>
       </c>
       <c r="D89" t="n">
         <v>129.0</v>
@@ -1731,7 +1731,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>820.0</v>
+        <v>821.0</v>
       </c>
       <c r="D92" t="n">
         <v>20.0</v>
@@ -1745,7 +1745,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>370.0</v>
+        <v>375.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1759,7 +1759,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>1333.0</v>
+        <v>1336.0</v>
       </c>
       <c r="D94" t="n">
         <v>45.0</v>
@@ -1773,7 +1773,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="D95" t="n">
         <v>17.0</v>
@@ -1801,7 +1801,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>820.0</v>
+        <v>823.0</v>
       </c>
       <c r="D97" t="n">
         <v>456.0</v>
@@ -1815,7 +1815,7 @@
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>592.0</v>
+        <v>593.0</v>
       </c>
       <c r="D98" t="n">
         <v>147.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="129">
   <si>
     <t>Region</t>
   </si>
@@ -363,9 +363,6 @@
   </si>
   <si>
     <t>Pisa</t>
-  </si>
-  <si>
-    <t>Pistoia</t>
   </si>
   <si>
     <t>Prato</t>
@@ -695,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>724.0</v>
+        <v>557.0</v>
       </c>
       <c r="D18" t="n">
-        <v>253.0</v>
+        <v>231.0</v>
       </c>
     </row>
     <row r="19">
@@ -737,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>409.0</v>
+        <v>340.0</v>
       </c>
       <c r="D21" t="n">
-        <v>524.0</v>
+        <v>522.0</v>
       </c>
     </row>
     <row r="22">
@@ -989,10 +986,10 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>645.0</v>
+        <v>582.0</v>
       </c>
       <c r="D39" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="40">
@@ -1171,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>373.0</v>
+        <v>374.0</v>
       </c>
       <c r="D52" t="n">
         <v>99.0</v>
@@ -1311,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1505.0</v>
+        <v>1155.0</v>
       </c>
       <c r="D62" t="n">
-        <v>13138.0</v>
+        <v>12383.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1449.0</v>
+        <v>1452.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2604.0</v>
+        <v>2607.0</v>
       </c>
     </row>
     <row r="65">
@@ -1675,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>471.0</v>
+        <v>472.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1689,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
       <c r="D89" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="90">
@@ -1717,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="D91" t="n">
         <v>62.0</v>
@@ -1731,10 +1728,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>821.0</v>
+        <v>83.0</v>
       </c>
       <c r="D92" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="93">
@@ -1745,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>375.0</v>
+        <v>391.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1759,10 +1756,10 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>1336.0</v>
+        <v>12.0</v>
       </c>
       <c r="D94" t="n">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="95">
@@ -1773,24 +1770,24 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>106.0</v>
+        <v>153.0</v>
       </c>
       <c r="D95" t="n">
-        <v>17.0</v>
+        <v>218.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B96" t="s">
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>153.0</v>
+        <v>823.0</v>
       </c>
       <c r="D96" t="n">
-        <v>217.0</v>
+        <v>456.0</v>
       </c>
     </row>
     <row r="97">
@@ -1801,38 +1798,38 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>823.0</v>
+        <v>597.0</v>
       </c>
       <c r="D97" t="n">
-        <v>456.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B98" t="s">
         <v>121</v>
       </c>
       <c r="C98" t="n">
-        <v>593.0</v>
+        <v>97.0</v>
       </c>
       <c r="D98" t="n">
-        <v>147.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B99" t="s">
         <v>122</v>
       </c>
       <c r="C99" t="n">
-        <v>97.0</v>
+        <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>43.0</v>
+        <v>211.0</v>
       </c>
     </row>
     <row r="100">
@@ -1843,10 +1840,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>32.0</v>
+        <v>218.0</v>
       </c>
       <c r="D100" t="n">
-        <v>211.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="101">
@@ -1857,10 +1854,10 @@
         <v>124</v>
       </c>
       <c r="C101" t="n">
-        <v>218.0</v>
+        <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>147.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="102">
@@ -1871,10 +1868,10 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0</v>
+        <v>102.0</v>
       </c>
       <c r="D102" t="n">
-        <v>100.0</v>
+        <v>198.0</v>
       </c>
     </row>
     <row r="103">
@@ -1885,10 +1882,10 @@
         <v>126</v>
       </c>
       <c r="C103" t="n">
-        <v>102.0</v>
+        <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>198.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="104">
@@ -1899,10 +1896,10 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>9.0</v>
+        <v>122.0</v>
       </c>
       <c r="D104" t="n">
-        <v>133.0</v>
+        <v>319.0</v>
       </c>
     </row>
     <row r="105">
@@ -1913,23 +1910,9 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>122.0</v>
+        <v>81.0</v>
       </c>
       <c r="D105" t="n">
-        <v>319.0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>24</v>
-      </c>
-      <c r="B106" t="s">
-        <v>129</v>
-      </c>
-      <c r="C106" t="n">
-        <v>81.0</v>
-      </c>
-      <c r="D106" t="n">
         <v>183.0</v>
       </c>
     </row>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>242.0</v>
+        <v>245.0</v>
       </c>
       <c r="D28" t="n">
         <v>154.0</v>
@@ -863,7 +863,7 @@
         <v>161.0</v>
       </c>
       <c r="D30" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
     </row>
     <row r="31">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>902.0</v>
+        <v>908.0</v>
       </c>
       <c r="D31" t="n">
         <v>56.0</v>
@@ -919,7 +919,7 @@
         <v>5538.0</v>
       </c>
       <c r="D34" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="35">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>543.0</v>
+        <v>544.0</v>
       </c>
     </row>
     <row r="68">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>472.0</v>
+        <v>473.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>391.0</v>
+        <v>392.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1773,7 +1773,7 @@
         <v>153.0</v>
       </c>
       <c r="D95" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
     </row>
     <row r="96">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>
@@ -1857,7 +1857,7 @@
         <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="102">
@@ -1868,7 +1868,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>102.0</v>
+        <v>105.0</v>
       </c>
       <c r="D102" t="n">
         <v>198.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,10 +468,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>981.0</v>
+        <v>984.0</v>
       </c>
       <c r="D2" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>465.0</v>
+        <v>466.0</v>
       </c>
       <c r="D3" t="n">
         <v>68.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="D4" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         <v>231.0</v>
       </c>
       <c r="D5" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="6">
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>549.0</v>
+        <v>564.0</v>
       </c>
       <c r="D8" t="n">
         <v>157.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>285.0</v>
+        <v>299.0</v>
       </c>
       <c r="D9" t="n">
-        <v>578.0</v>
+        <v>585.0</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>228.0</v>
+        <v>231.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>557.0</v>
+        <v>583.0</v>
       </c>
       <c r="D18" t="n">
         <v>231.0</v>
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>340.0</v>
+        <v>342.0</v>
       </c>
       <c r="D21" t="n">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
     </row>
     <row r="22">
@@ -804,7 +804,7 @@
         <v>49</v>
       </c>
       <c r="C26" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="D26" t="n">
         <v>84.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>582.0</v>
+        <v>583.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1238,7 +1238,7 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>760.0</v>
+        <v>762.0</v>
       </c>
       <c r="D57" t="n">
         <v>452.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1155.0</v>
+        <v>1157.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12383.0</v>
+        <v>12402.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2889.0</v>
       </c>
       <c r="D63" t="n">
-        <v>688.0</v>
+        <v>691.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1452.0</v>
+        <v>1453.0</v>
       </c>
       <c r="D64" t="n">
         <v>2607.0</v>
@@ -1367,7 +1367,7 @@
         <v>1570.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1119.0</v>
+        <v>1126.0</v>
       </c>
     </row>
     <row r="67">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="D40" t="n">
-        <v>910.0</v>
+        <v>912.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>180.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2166.0</v>
+        <v>2170.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>441.0</v>
+        <v>442.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>134.0</v>
+        <v>136.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3987.0</v>
+        <v>3990.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>82.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24863.0</v>
+        <v>24867.0</v>
       </c>
     </row>
     <row r="46">
@@ -1098,10 +1098,10 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>733.0</v>
+        <v>734.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1889.0</v>
+        <v>1890.0</v>
       </c>
     </row>
     <row r="48">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>750.0</v>
+        <v>752.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1182,7 +1182,7 @@
         <v>76</v>
       </c>
       <c r="C53" t="n">
-        <v>241.0</v>
+        <v>243.0</v>
       </c>
       <c r="D53" t="n">
         <v>57.0</v>
@@ -1213,7 +1213,7 @@
         <v>486.0</v>
       </c>
       <c r="D55" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="56">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1723.0</v>
+        <v>1725.0</v>
       </c>
       <c r="D59" t="n">
         <v>346.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1585.0</v>
+        <v>1586.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1311,7 +1311,7 @@
         <v>1157.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12402.0</v>
+        <v>12423.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2889.0</v>
       </c>
       <c r="D63" t="n">
-        <v>691.0</v>
+        <v>693.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1453.0</v>
+        <v>1455.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2607.0</v>
+        <v>2609.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1570.0</v>
+        <v>1571.0</v>
       </c>
       <c r="D66" t="n">
         <v>1126.0</v>
@@ -1504,7 +1504,7 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>688.0</v>
+        <v>689.0</v>
       </c>
       <c r="D76" t="n">
         <v>438.0</v>
@@ -1549,7 +1549,7 @@
         <v>332.0</v>
       </c>
       <c r="D79" t="n">
-        <v>505.0</v>
+        <v>509.0</v>
       </c>
     </row>
     <row r="80">
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>823.0</v>
+        <v>825.0</v>
       </c>
       <c r="D96" t="n">
         <v>456.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>597.0</v>
+        <v>598.0</v>
       </c>
       <c r="D97" t="n">
         <v>147.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1145.0</v>
+        <v>1155.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,7 +538,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2177.0</v>
+        <v>2183.0</v>
       </c>
       <c r="D7" t="n">
         <v>1091.0</v>
@@ -622,7 +622,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>891.0</v>
+        <v>897.0</v>
       </c>
       <c r="D13" t="n">
         <v>337.0</v>
@@ -636,10 +636,10 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>589.0</v>
+        <v>594.0</v>
       </c>
       <c r="D14" t="n">
-        <v>111.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="15">
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>690.0</v>
+        <v>707.0</v>
       </c>
       <c r="D15" t="n">
-        <v>177.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="16">
@@ -678,10 +678,10 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9287.0</v>
+        <v>9293.0</v>
       </c>
       <c r="D17" t="n">
-        <v>906.0</v>
+        <v>907.0</v>
       </c>
     </row>
     <row r="18">
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>583.0</v>
+        <v>584.0</v>
       </c>
       <c r="D18" t="n">
         <v>231.0</v>
@@ -751,7 +751,7 @@
         <v>34.0</v>
       </c>
       <c r="D22" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
     </row>
     <row r="23">
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D30" t="n">
         <v>158.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>313.0</v>
+        <v>314.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5538.0</v>
+        <v>5543.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1725.0</v>
+        <v>1728.0</v>
       </c>
       <c r="D59" t="n">
         <v>346.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1586.0</v>
+        <v>1591.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1157.0</v>
+        <v>1159.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12423.0</v>
+        <v>12442.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1455.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2609.0</v>
+        <v>2610.0</v>
       </c>
     </row>
     <row r="65">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>544.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="68">
@@ -1409,7 +1409,7 @@
         <v>216.0</v>
       </c>
       <c r="D69" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="70">
@@ -1420,10 +1420,10 @@
         <v>93</v>
       </c>
       <c r="C70" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="D70" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="71">
@@ -1476,7 +1476,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>298.0</v>
+        <v>299.0</v>
       </c>
       <c r="D74" t="n">
         <v>47.0</v>
@@ -1521,7 +1521,7 @@
         <v>484.0</v>
       </c>
       <c r="D77" t="n">
-        <v>456.0</v>
+        <v>458.0</v>
       </c>
     </row>
     <row r="78">
@@ -1546,7 +1546,7 @@
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>332.0</v>
+        <v>335.0</v>
       </c>
       <c r="D79" t="n">
         <v>509.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>473.0</v>
+        <v>475.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
       <c r="D90" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
     </row>
     <row r="91">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="D92" t="n">
         <v>4.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>392.0</v>
+        <v>393.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1798,10 +1798,10 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>598.0</v>
+        <v>599.0</v>
       </c>
       <c r="D97" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="98">
@@ -1857,7 +1857,7 @@
         <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>101.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="102">
@@ -1885,7 +1885,7 @@
         <v>9.0</v>
       </c>
       <c r="D103" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="104">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>584.0</v>
+        <v>586.0</v>
       </c>
       <c r="D18" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>322.0</v>
+        <v>324.0</v>
       </c>
     </row>
     <row r="21">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>385.0</v>
+        <v>386.0</v>
       </c>
     </row>
     <row r="25">
@@ -807,7 +807,7 @@
         <v>26.0</v>
       </c>
       <c r="D26" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="27">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1728.0</v>
+        <v>1730.0</v>
       </c>
       <c r="D59" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
     </row>
     <row r="60">
@@ -1297,7 +1297,7 @@
         <v>729.0</v>
       </c>
       <c r="D61" t="n">
-        <v>878.0</v>
+        <v>881.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>1159.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12442.0</v>
+        <v>12451.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2889.0</v>
+        <v>2890.0</v>
       </c>
       <c r="D63" t="n">
-        <v>693.0</v>
+        <v>694.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1455.0</v>
+        <v>1457.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2610.0</v>
+        <v>2611.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1571.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1126.0</v>
+        <v>1130.0</v>
       </c>
     </row>
     <row r="67">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>462.0</v>
+        <v>464.0</v>
       </c>
       <c r="D89" t="n">
         <v>131.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>825.0</v>
+        <v>826.0</v>
       </c>
       <c r="D96" t="n">
         <v>456.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>599.0</v>
+        <v>600.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1003,7 +1003,7 @@
         <v>135.0</v>
       </c>
       <c r="D40" t="n">
-        <v>912.0</v>
+        <v>916.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2170.0</v>
+        <v>2172.0</v>
       </c>
     </row>
     <row r="42">
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>136.0</v>
+        <v>139.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3990.0</v>
+        <v>3991.0</v>
       </c>
     </row>
     <row r="44">
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>374.0</v>
+        <v>375.0</v>
       </c>
       <c r="D52" t="n">
         <v>99.0</v>
@@ -1269,7 +1269,7 @@
         <v>1730.0</v>
       </c>
       <c r="D59" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
     </row>
     <row r="60">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1159.0</v>
+        <v>1160.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12451.0</v>
+        <v>12469.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2890.0</v>
       </c>
       <c r="D63" t="n">
-        <v>694.0</v>
+        <v>695.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1457.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2611.0</v>
+        <v>2612.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1571.0</v>
+        <v>1572.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1130.0</v>
+        <v>1134.0</v>
       </c>
     </row>
     <row r="67">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>464.0</v>
+        <v>466.0</v>
       </c>
       <c r="D89" t="n">
         <v>131.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>284.0</v>
+        <v>286.0</v>
       </c>
       <c r="D90" t="n">
         <v>108.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="D92" t="n">
         <v>4.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>393.0</v>
+        <v>398.0</v>
       </c>
       <c r="D93" t="n">
         <v>53.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>826.0</v>
+        <v>827.0</v>
       </c>
       <c r="D96" t="n">
         <v>456.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>600.0</v>
+        <v>603.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>908.0</v>
+        <v>910.0</v>
       </c>
       <c r="D31" t="n">
         <v>56.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5543.0</v>
+        <v>5548.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>475.0</v>
+        <v>476.0</v>
       </c>
       <c r="D88" t="n">
         <v>277.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>466.0</v>
+        <v>468.0</v>
       </c>
       <c r="D89" t="n">
         <v>131.0</v>
@@ -1745,7 +1745,7 @@
         <v>398.0</v>
       </c>
       <c r="D93" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="94">
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="D95" t="n">
         <v>219.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>984.0</v>
+        <v>986.0</v>
       </c>
       <c r="D2" t="n">
         <v>83.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>466.0</v>
+        <v>467.0</v>
       </c>
       <c r="D3" t="n">
         <v>68.0</v>
@@ -499,7 +499,7 @@
         <v>188.0</v>
       </c>
       <c r="D4" t="n">
-        <v>360.0</v>
+        <v>363.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,10 +510,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>231.0</v>
+        <v>232.0</v>
       </c>
       <c r="D5" t="n">
-        <v>117.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="6">
@@ -1238,10 +1238,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>762.0</v>
+        <v>765.0</v>
       </c>
       <c r="D57" t="n">
-        <v>452.0</v>
+        <v>453.0</v>
       </c>
     </row>
     <row r="58">
@@ -1255,7 +1255,7 @@
         <v>167.0</v>
       </c>
       <c r="D58" t="n">
-        <v>161.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="59">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1591.0</v>
+        <v>1592.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1297,7 +1297,7 @@
         <v>729.0</v>
       </c>
       <c r="D61" t="n">
-        <v>881.0</v>
+        <v>884.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1160.0</v>
+        <v>1162.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12469.0</v>
+        <v>12481.0</v>
       </c>
     </row>
     <row r="63">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1572.0</v>
+        <v>1575.0</v>
       </c>
       <c r="D66" t="n">
         <v>1134.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>603.0</v>
+        <v>604.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1730.0</v>
+        <v>1731.0</v>
       </c>
       <c r="D59" t="n">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
     </row>
     <row r="60">
@@ -1311,7 +1311,7 @@
         <v>1162.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12481.0</v>
+        <v>12505.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1457.0</v>
+        <v>1459.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2612.0</v>
+        <v>2617.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1575.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1134.0</v>
+        <v>1141.0</v>
       </c>
     </row>
     <row r="67">
@@ -1616,7 +1616,7 @@
         <v>107</v>
       </c>
       <c r="C84" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="D84" t="n">
         <v>3.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>342.0</v>
+        <v>364.0</v>
       </c>
       <c r="D21" t="n">
-        <v>523.0</v>
+        <v>524.0</v>
       </c>
     </row>
     <row r="22">
@@ -807,7 +807,7 @@
         <v>26.0</v>
       </c>
       <c r="D26" t="n">
-        <v>86.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="27">
@@ -835,7 +835,7 @@
         <v>245.0</v>
       </c>
       <c r="D28" t="n">
-        <v>154.0</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="29">
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="D30" t="n">
         <v>158.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>314.0</v>
+        <v>315.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>321.0</v>
+        <v>322.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5548.0</v>
+        <v>5550.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>912.0</v>
+        <v>915.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>375.0</v>
+        <v>376.0</v>
       </c>
       <c r="D52" t="n">
         <v>99.0</v>
@@ -1199,7 +1199,7 @@
         <v>106.0</v>
       </c>
       <c r="D54" t="n">
-        <v>172.0</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="55">
@@ -1227,7 +1227,7 @@
         <v>430.0</v>
       </c>
       <c r="D56" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="57">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1731.0</v>
+        <v>1732.0</v>
       </c>
       <c r="D59" t="n">
         <v>349.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1162.0</v>
+        <v>1165.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12505.0</v>
+        <v>12524.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2890.0</v>
       </c>
       <c r="D63" t="n">
-        <v>695.0</v>
+        <v>697.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1459.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2617.0</v>
+        <v>2620.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1575.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1141.0</v>
+        <v>1142.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>550.0</v>
+        <v>553.0</v>
       </c>
     </row>
     <row r="68">
@@ -1395,7 +1395,7 @@
         <v>37.0</v>
       </c>
       <c r="D68" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="69">
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>476.0</v>
+        <v>477.0</v>
       </c>
       <c r="D88" t="n">
-        <v>277.0</v>
+        <v>278.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>468.0</v>
+        <v>470.0</v>
       </c>
       <c r="D89" t="n">
         <v>131.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
       <c r="D90" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="91">
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D91" t="n">
         <v>62.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="D93" t="n">
         <v>54.0</v>
@@ -1773,7 +1773,7 @@
         <v>154.0</v>
       </c>
       <c r="D95" t="n">
-        <v>219.0</v>
+        <v>221.0</v>
       </c>
     </row>
     <row r="96">
@@ -1787,7 +1787,7 @@
         <v>827.0</v>
       </c>
       <c r="D96" t="n">
-        <v>456.0</v>
+        <v>462.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>604.0</v>
+        <v>605.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>211.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="100">
@@ -1857,7 +1857,7 @@
         <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>103.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="102">
@@ -1899,7 +1899,7 @@
         <v>122.0</v>
       </c>
       <c r="D104" t="n">
-        <v>319.0</v>
+        <v>320.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>81.0</v>
+        <v>84.0</v>
       </c>
       <c r="D105" t="n">
         <v>183.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1155.0</v>
+        <v>1156.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,7 +538,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2183.0</v>
+        <v>2191.0</v>
       </c>
       <c r="D7" t="n">
         <v>1091.0</v>
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="D18" t="n">
         <v>233.0</v>
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>324.0</v>
+        <v>325.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>364.0</v>
+        <v>365.0</v>
       </c>
       <c r="D21" t="n">
-        <v>524.0</v>
+        <v>525.0</v>
       </c>
     </row>
     <row r="22">
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5550.0</v>
+        <v>5551.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1592.0</v>
+        <v>1598.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1297,7 +1297,7 @@
         <v>729.0</v>
       </c>
       <c r="D61" t="n">
-        <v>884.0</v>
+        <v>886.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1165.0</v>
+        <v>1168.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12524.0</v>
+        <v>12541.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1459.0</v>
+        <v>1460.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2620.0</v>
+        <v>2621.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1575.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1142.0</v>
+        <v>1143.0</v>
       </c>
     </row>
     <row r="67">
@@ -1406,7 +1406,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
       <c r="D69" t="n">
         <v>202.0</v>
@@ -1448,7 +1448,7 @@
         <v>95</v>
       </c>
       <c r="C72" t="n">
-        <v>155.0</v>
+        <v>158.0</v>
       </c>
       <c r="D72" t="n">
         <v>0.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>477.0</v>
+        <v>479.0</v>
       </c>
       <c r="D88" t="n">
         <v>278.0</v>
@@ -1689,7 +1689,7 @@
         <v>470.0</v>
       </c>
       <c r="D89" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="90">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>910.0</v>
+        <v>911.0</v>
       </c>
       <c r="D31" t="n">
         <v>56.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>315.0</v>
+        <v>318.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5551.0</v>
+        <v>5560.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="D52" t="n">
         <v>99.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
       <c r="D56" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="57">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1598.0</v>
+        <v>1602.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1308,7 +1308,7 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1168.0</v>
+        <v>1171.0</v>
       </c>
       <c r="D62" t="n">
         <v>12541.0</v>
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2890.0</v>
+        <v>2892.0</v>
       </c>
       <c r="D63" t="n">
-        <v>697.0</v>
+        <v>698.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1460.0</v>
+        <v>1461.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2621.0</v>
+        <v>2622.0</v>
       </c>
     </row>
     <row r="65">
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>479.0</v>
+        <v>481.0</v>
       </c>
       <c r="D88" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
     </row>
     <row r="89">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>85.0</v>
+        <v>89.0</v>
       </c>
       <c r="D92" t="n">
         <v>4.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>399.0</v>
+        <v>408.0</v>
       </c>
       <c r="D93" t="n">
         <v>54.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>827.0</v>
+        <v>829.0</v>
       </c>
       <c r="D96" t="n">
         <v>462.0</v>
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>605.0</v>
+        <v>606.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5560.0</v>
+        <v>5561.0</v>
       </c>
       <c r="D34" t="n">
-        <v>214.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="35">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>470.0</v>
+        <v>473.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="D95" t="n">
         <v>221.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -482,10 +482,10 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>467.0</v>
+        <v>469.0</v>
       </c>
       <c r="D3" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="4">
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>188.0</v>
+        <v>189.0</v>
       </c>
       <c r="D4" t="n">
-        <v>363.0</v>
+        <v>368.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>232.0</v>
+        <v>233.0</v>
       </c>
       <c r="D5" t="n">
         <v>119.0</v>
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>564.0</v>
+        <v>569.0</v>
       </c>
       <c r="D8" t="n">
         <v>157.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>299.0</v>
+        <v>302.0</v>
       </c>
       <c r="D9" t="n">
-        <v>585.0</v>
+        <v>587.0</v>
       </c>
     </row>
     <row r="10">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="D22" t="n">
         <v>278.0</v>
@@ -793,7 +793,7 @@
         <v>112.0</v>
       </c>
       <c r="D25" t="n">
-        <v>286.0</v>
+        <v>288.0</v>
       </c>
     </row>
     <row r="26">
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>583.0</v>
+        <v>584.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1252,7 +1252,7 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="D58" t="n">
         <v>164.0</v>
@@ -1269,7 +1269,7 @@
         <v>1732.0</v>
       </c>
       <c r="D59" t="n">
-        <v>349.0</v>
+        <v>351.0</v>
       </c>
     </row>
     <row r="60">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1171.0</v>
+        <v>1173.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12541.0</v>
+        <v>12563.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1461.0</v>
+        <v>1463.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2622.0</v>
+        <v>2623.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1575.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1143.0</v>
+        <v>1145.0</v>
       </c>
     </row>
     <row r="67">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="D30" t="n">
         <v>158.0</v>
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>442.0</v>
+        <v>443.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1171,7 +1171,7 @@
         <v>377.0</v>
       </c>
       <c r="D52" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="53">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="D55" t="n">
         <v>138.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1732.0</v>
+        <v>1734.0</v>
       </c>
       <c r="D59" t="n">
         <v>351.0</v>
@@ -1311,7 +1311,7 @@
         <v>1173.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12563.0</v>
+        <v>12580.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1463.0</v>
+        <v>1464.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2623.0</v>
+        <v>2626.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1575.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1145.0</v>
+        <v>1146.0</v>
       </c>
     </row>
     <row r="67">
@@ -1647,7 +1647,7 @@
         <v>42.0</v>
       </c>
       <c r="D86" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="87">
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>408.0</v>
+        <v>411.0</v>
       </c>
       <c r="D93" t="n">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="94">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>606.0</v>
+        <v>607.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>213.0</v>
+        <v>215.0</v>
       </c>
     </row>
     <row r="100">
@@ -1857,7 +1857,7 @@
         <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>107.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="102">
@@ -1913,7 +1913,7 @@
         <v>84.0</v>
       </c>
       <c r="D105" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="D18" t="n">
         <v>233.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>911.0</v>
+        <v>914.0</v>
       </c>
       <c r="D31" t="n">
         <v>56.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5561.0</v>
+        <v>5570.0</v>
       </c>
       <c r="D34" t="n">
         <v>213.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>915.0</v>
+        <v>919.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1098,7 +1098,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>734.0</v>
+        <v>739.0</v>
       </c>
       <c r="D47" t="n">
         <v>1890.0</v>
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1684.0</v>
+        <v>1685.0</v>
       </c>
       <c r="D49" t="n">
         <v>3902.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1602.0</v>
+        <v>1610.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1173.0</v>
+        <v>1175.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12580.0</v>
+        <v>12597.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2892.0</v>
+        <v>2895.0</v>
       </c>
       <c r="D63" t="n">
-        <v>698.0</v>
+        <v>699.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1464.0</v>
+        <v>1465.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2626.0</v>
+        <v>2628.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1575.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1146.0</v>
+        <v>1147.0</v>
       </c>
     </row>
     <row r="67">
@@ -1675,7 +1675,7 @@
         <v>481.0</v>
       </c>
       <c r="D88" t="n">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
     </row>
     <row r="89">
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>411.0</v>
+        <v>413.0</v>
       </c>
       <c r="D93" t="n">
         <v>55.0</v>
@@ -1773,7 +1773,7 @@
         <v>155.0</v>
       </c>
       <c r="D95" t="n">
-        <v>221.0</v>
+        <v>224.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1734.0</v>
+        <v>1736.0</v>
       </c>
       <c r="D59" t="n">
-        <v>351.0</v>
+        <v>353.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1610.0</v>
+        <v>1617.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>729.0</v>
+        <v>730.0</v>
       </c>
       <c r="D61" t="n">
-        <v>886.0</v>
+        <v>889.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1175.0</v>
+        <v>1179.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12597.0</v>
+        <v>12608.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2895.0</v>
       </c>
       <c r="D63" t="n">
-        <v>699.0</v>
+        <v>700.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1465.0</v>
+        <v>1467.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2628.0</v>
+        <v>2631.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1575.0</v>
+        <v>1576.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1147.0</v>
+        <v>1151.0</v>
       </c>
     </row>
     <row r="67">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>473.0</v>
+        <v>479.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -622,10 +622,10 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>897.0</v>
+        <v>905.0</v>
       </c>
       <c r="D13" t="n">
-        <v>337.0</v>
+        <v>339.0</v>
       </c>
     </row>
     <row r="14">
@@ -636,10 +636,10 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>594.0</v>
+        <v>609.0</v>
       </c>
       <c r="D14" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
     </row>
     <row r="15">
@@ -650,10 +650,10 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>707.0</v>
+        <v>712.0</v>
       </c>
       <c r="D15" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
     </row>
     <row r="16">
@@ -678,7 +678,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9293.0</v>
+        <v>9307.0</v>
       </c>
       <c r="D17" t="n">
         <v>907.0</v>
@@ -846,7 +846,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="D29" t="n">
         <v>6.0</v>
@@ -860,10 +860,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>164.0</v>
+        <v>165.0</v>
       </c>
       <c r="D30" t="n">
-        <v>158.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="31">
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>377.0</v>
+        <v>378.0</v>
       </c>
       <c r="D52" t="n">
         <v>100.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>487.0</v>
+        <v>488.0</v>
       </c>
       <c r="D55" t="n">
         <v>138.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>432.0</v>
+        <v>433.0</v>
       </c>
       <c r="D56" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="57">
@@ -1311,7 +1311,7 @@
         <v>1179.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12608.0</v>
+        <v>12624.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2895.0</v>
       </c>
       <c r="D63" t="n">
-        <v>700.0</v>
+        <v>701.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1467.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2631.0</v>
+        <v>2632.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1576.0</v>
+        <v>1578.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1151.0</v>
+        <v>1153.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>553.0</v>
+        <v>554.0</v>
       </c>
     </row>
     <row r="68">
@@ -1392,7 +1392,7 @@
         <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="D68" t="n">
         <v>145.0</v>
@@ -1675,7 +1675,7 @@
         <v>481.0</v>
       </c>
       <c r="D88" t="n">
-        <v>280.0</v>
+        <v>281.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>479.0</v>
+        <v>480.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>413.0</v>
+        <v>424.0</v>
       </c>
       <c r="D93" t="n">
         <v>55.0</v>
@@ -1773,7 +1773,7 @@
         <v>155.0</v>
       </c>
       <c r="D95" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
     </row>
     <row r="96">
@@ -1787,7 +1787,7 @@
         <v>829.0</v>
       </c>
       <c r="D96" t="n">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>607.0</v>
+        <v>608.0</v>
       </c>
       <c r="D97" t="n">
         <v>148.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,7 +1840,7 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>219.0</v>
+        <v>220.0</v>
       </c>
       <c r="D100" t="n">
         <v>147.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>588.0</v>
+        <v>595.0</v>
       </c>
       <c r="D18" t="n">
         <v>233.0</v>
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="20">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>365.0</v>
+        <v>384.0</v>
       </c>
       <c r="D21" t="n">
-        <v>525.0</v>
+        <v>526.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="D22" t="n">
-        <v>278.0</v>
+        <v>279.0</v>
       </c>
     </row>
     <row r="23">
@@ -874,10 +874,10 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>914.0</v>
+        <v>916.0</v>
       </c>
       <c r="D31" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="32">
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>318.0</v>
+        <v>321.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5570.0</v>
+        <v>5572.0</v>
       </c>
       <c r="D34" t="n">
         <v>213.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>919.0</v>
+        <v>920.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>481.0</v>
+        <v>483.0</v>
       </c>
       <c r="D88" t="n">
-        <v>281.0</v>
+        <v>283.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>480.0</v>
+        <v>481.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1156.0</v>
+        <v>1162.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2191.0</v>
+        <v>2196.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1091.0</v>
+        <v>1092.0</v>
       </c>
     </row>
     <row r="8">
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>595.0</v>
+        <v>617.0</v>
       </c>
       <c r="D18" t="n">
         <v>233.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>384.0</v>
+        <v>385.0</v>
       </c>
       <c r="D21" t="n">
         <v>526.0</v>
@@ -790,7 +790,7 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="D25" t="n">
         <v>288.0</v>
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1736.0</v>
+        <v>1739.0</v>
       </c>
       <c r="D59" t="n">
-        <v>353.0</v>
+        <v>355.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1617.0</v>
+        <v>1619.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1297,7 +1297,7 @@
         <v>730.0</v>
       </c>
       <c r="D61" t="n">
-        <v>889.0</v>
+        <v>893.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1179.0</v>
+        <v>1180.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12624.0</v>
+        <v>12647.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1467.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2632.0</v>
+        <v>2633.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1578.0</v>
+        <v>1581.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1153.0</v>
+        <v>1154.0</v>
       </c>
     </row>
     <row r="67">
@@ -1409,7 +1409,7 @@
         <v>217.0</v>
       </c>
       <c r="D69" t="n">
-        <v>202.0</v>
+        <v>203.0</v>
       </c>
     </row>
     <row r="70">
@@ -1476,10 +1476,10 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>299.0</v>
+        <v>302.0</v>
       </c>
       <c r="D74" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="75">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5572.0</v>
+        <v>5575.0</v>
       </c>
       <c r="D34" t="n">
         <v>213.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>920.0</v>
+        <v>929.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1003,7 +1003,7 @@
         <v>135.0</v>
       </c>
       <c r="D40" t="n">
-        <v>916.0</v>
+        <v>924.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2172.0</v>
+        <v>2180.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>443.0</v>
+        <v>446.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="D43" t="n">
-        <v>3991.0</v>
+        <v>4000.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>82.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24867.0</v>
+        <v>24871.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1457.0</v>
+        <v>1461.0</v>
       </c>
     </row>
     <row r="47">
@@ -1101,7 +1101,7 @@
         <v>739.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1890.0</v>
+        <v>1894.0</v>
       </c>
     </row>
     <row r="48">
@@ -1115,7 +1115,7 @@
         <v>1.0</v>
       </c>
       <c r="D48" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="49">
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1685.0</v>
+        <v>1686.0</v>
       </c>
       <c r="D49" t="n">
         <v>3902.0</v>
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>752.0</v>
+        <v>753.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>488.0</v>
+        <v>494.0</v>
       </c>
       <c r="D55" t="n">
         <v>138.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>424.0</v>
+        <v>425.0</v>
       </c>
       <c r="D93" t="n">
         <v>55.0</v>
@@ -1770,10 +1770,10 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
       <c r="D95" t="n">
-        <v>225.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="96">
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>829.0</v>
+        <v>830.0</v>
       </c>
       <c r="D96" t="n">
-        <v>463.0</v>
+        <v>465.0</v>
       </c>
     </row>
     <row r="97">
@@ -1801,7 +1801,7 @@
         <v>608.0</v>
       </c>
       <c r="D97" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>617.0</v>
+        <v>619.0</v>
       </c>
       <c r="D18" t="n">
         <v>233.0</v>
@@ -737,7 +737,7 @@
         <v>385.0</v>
       </c>
       <c r="D21" t="n">
-        <v>526.0</v>
+        <v>527.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,7 +748,7 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>36.0</v>
+        <v>39.0</v>
       </c>
       <c r="D22" t="n">
         <v>279.0</v>
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>386.0</v>
+        <v>389.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,10 +790,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="D25" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
     </row>
     <row r="26">
@@ -807,7 +807,7 @@
         <v>26.0</v>
       </c>
       <c r="D26" t="n">
-        <v>87.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="27">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>482.0</v>
+        <v>483.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -650,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>712.0</v>
+        <v>713.0</v>
       </c>
       <c r="D15" t="n">
         <v>180.0</v>
@@ -1014,7 +1014,7 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>182.0</v>
+        <v>184.0</v>
       </c>
       <c r="D41" t="n">
         <v>2180.0</v>
@@ -1675,7 +1675,7 @@
         <v>483.0</v>
       </c>
       <c r="D88" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>483.0</v>
+        <v>484.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,10 +552,10 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>569.0</v>
+        <v>571.0</v>
       </c>
       <c r="D8" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>302.0</v>
+        <v>307.0</v>
       </c>
       <c r="D9" t="n">
         <v>587.0</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>233.0</v>
+        <v>237.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5575.0</v>
+        <v>5580.0</v>
       </c>
       <c r="D34" t="n">
         <v>213.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>257.0</v>
+        <v>259.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1168,10 +1168,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>378.0</v>
+        <v>379.0</v>
       </c>
       <c r="D52" t="n">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="53">
@@ -1185,7 +1185,7 @@
         <v>243.0</v>
       </c>
       <c r="D53" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="54">
@@ -1196,7 +1196,7 @@
         <v>77</v>
       </c>
       <c r="C54" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="D54" t="n">
         <v>175.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>494.0</v>
+        <v>496.0</v>
       </c>
       <c r="D55" t="n">
         <v>138.0</v>
@@ -1224,10 +1224,10 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>433.0</v>
+        <v>435.0</v>
       </c>
       <c r="D56" t="n">
-        <v>148.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="57">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1739.0</v>
+        <v>1743.0</v>
       </c>
       <c r="D59" t="n">
         <v>355.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1619.0</v>
+        <v>1620.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>730.0</v>
+        <v>732.0</v>
       </c>
       <c r="D61" t="n">
-        <v>893.0</v>
+        <v>894.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1180.0</v>
+        <v>1185.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12647.0</v>
+        <v>12707.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2895.0</v>
       </c>
       <c r="D63" t="n">
-        <v>701.0</v>
+        <v>703.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1467.0</v>
+        <v>1469.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2633.0</v>
+        <v>2639.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1581.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1154.0</v>
+        <v>1156.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>483.0</v>
+        <v>486.0</v>
       </c>
       <c r="D88" t="n">
         <v>284.0</v>
@@ -1745,7 +1745,7 @@
         <v>425.0</v>
       </c>
       <c r="D93" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="94">
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="D95" t="n">
         <v>232.0</v>
@@ -1801,7 +1801,7 @@
         <v>608.0</v>
       </c>
       <c r="D97" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="98">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>619.0</v>
+        <v>622.0</v>
       </c>
       <c r="D18" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="19">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>385.0</v>
+        <v>386.0</v>
       </c>
       <c r="D21" t="n">
-        <v>527.0</v>
+        <v>530.0</v>
       </c>
     </row>
     <row r="22">
@@ -986,7 +986,7 @@
         <v>62</v>
       </c>
       <c r="C39" t="n">
-        <v>584.0</v>
+        <v>585.0</v>
       </c>
       <c r="D39" t="n">
         <v>13.0</v>
@@ -1297,7 +1297,7 @@
         <v>732.0</v>
       </c>
       <c r="D61" t="n">
-        <v>894.0</v>
+        <v>896.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>1185.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12707.0</v>
+        <v>12722.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2895.0</v>
+        <v>2896.0</v>
       </c>
       <c r="D63" t="n">
         <v>703.0</v>
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1469.0</v>
+        <v>1470.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2639.0</v>
+        <v>2641.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1581.0</v>
+        <v>1582.0</v>
       </c>
       <c r="D66" t="n">
         <v>1156.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="D88" t="n">
         <v>284.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>484.0</v>
+        <v>486.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
       <c r="D90" t="n">
         <v>109.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="D91" t="n">
         <v>62.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1000,10 +1000,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="D40" t="n">
-        <v>924.0</v>
+        <v>927.0</v>
       </c>
     </row>
     <row r="41">
@@ -1014,10 +1014,10 @@
         <v>64</v>
       </c>
       <c r="C41" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2180.0</v>
+        <v>2182.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>446.0</v>
+        <v>448.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4000.0</v>
+        <v>4002.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>82.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24871.0</v>
+        <v>24873.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1461.0</v>
+        <v>1463.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,7 +1098,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>739.0</v>
+        <v>743.0</v>
       </c>
       <c r="D47" t="n">
         <v>1894.0</v>
@@ -1126,10 +1126,10 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1686.0</v>
+        <v>1688.0</v>
       </c>
       <c r="D49" t="n">
-        <v>3902.0</v>
+        <v>3903.0</v>
       </c>
     </row>
     <row r="50">
@@ -1143,7 +1143,7 @@
         <v>25.0</v>
       </c>
       <c r="D50" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="51">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>753.0</v>
+        <v>754.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>379.0</v>
+        <v>380.0</v>
       </c>
       <c r="D52" t="n">
         <v>103.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="D55" t="n">
         <v>138.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1185.0</v>
+        <v>1186.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12722.0</v>
+        <v>12730.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1470.0</v>
+        <v>1472.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2641.0</v>
+        <v>2648.0</v>
       </c>
     </row>
     <row r="65">
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>830.0</v>
+        <v>832.0</v>
       </c>
       <c r="D96" t="n">
-        <v>465.0</v>
+        <v>473.0</v>
       </c>
     </row>
     <row r="97">
@@ -1798,7 +1798,7 @@
         <v>120</v>
       </c>
       <c r="C97" t="n">
-        <v>608.0</v>
+        <v>609.0</v>
       </c>
       <c r="D97" t="n">
         <v>150.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="D27" t="n">
         <v>12.0</v>
@@ -832,10 +832,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>245.0</v>
+        <v>249.0</v>
       </c>
       <c r="D28" t="n">
-        <v>157.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="29">
@@ -860,10 +860,10 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>165.0</v>
+        <v>167.0</v>
       </c>
       <c r="D30" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
     </row>
     <row r="31">
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>916.0</v>
+        <v>920.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>321.0</v>
+        <v>324.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>323.0</v>
+        <v>324.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5580.0</v>
+        <v>5583.0</v>
       </c>
       <c r="D34" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="35">
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>929.0</v>
+        <v>940.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>554.0</v>
+        <v>567.0</v>
       </c>
     </row>
     <row r="68">
@@ -1395,7 +1395,7 @@
         <v>39.0</v>
       </c>
       <c r="D68" t="n">
-        <v>145.0</v>
+        <v>146.0</v>
       </c>
     </row>
     <row r="69">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>487.0</v>
+        <v>490.0</v>
       </c>
       <c r="D88" t="n">
         <v>284.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>486.0</v>
+        <v>487.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="D91" t="n">
         <v>62.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="D92" t="n">
         <v>4.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="D95" t="n">
         <v>232.0</v>
@@ -1840,10 +1840,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>220.0</v>
+        <v>222.0</v>
       </c>
       <c r="D100" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
     </row>
     <row r="101">
@@ -1857,7 +1857,7 @@
         <v>0.0</v>
       </c>
       <c r="D101" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="102">
@@ -1868,10 +1868,10 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>105.0</v>
+        <v>107.0</v>
       </c>
       <c r="D102" t="n">
-        <v>198.0</v>
+        <v>199.0</v>
       </c>
     </row>
     <row r="103">
@@ -1896,7 +1896,7 @@
         <v>127</v>
       </c>
       <c r="C104" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="D104" t="n">
         <v>320.0</v>
@@ -1910,10 +1910,10 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="D105" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,7 +524,7 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1162.0</v>
+        <v>1180.0</v>
       </c>
       <c r="D6" t="n">
         <v>342.0</v>
@@ -538,10 +538,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2196.0</v>
+        <v>2207.0</v>
       </c>
       <c r="D7" t="n">
-        <v>1092.0</v>
+        <v>1096.0</v>
       </c>
     </row>
     <row r="8">
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>380.0</v>
+        <v>382.0</v>
       </c>
       <c r="D52" t="n">
         <v>103.0</v>
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>498.0</v>
+        <v>499.0</v>
       </c>
       <c r="D55" t="n">
         <v>138.0</v>
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>435.0</v>
+        <v>436.0</v>
       </c>
       <c r="D56" t="n">
         <v>150.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1743.0</v>
+        <v>1744.0</v>
       </c>
       <c r="D59" t="n">
         <v>355.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1620.0</v>
+        <v>1624.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1297,7 +1297,7 @@
         <v>732.0</v>
       </c>
       <c r="D61" t="n">
-        <v>896.0</v>
+        <v>898.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1186.0</v>
+        <v>1196.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12730.0</v>
+        <v>12765.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2896.0</v>
       </c>
       <c r="D63" t="n">
-        <v>703.0</v>
+        <v>706.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1472.0</v>
+        <v>1483.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2648.0</v>
+        <v>2652.0</v>
       </c>
     </row>
     <row r="65">
@@ -1350,7 +1350,7 @@
         <v>88</v>
       </c>
       <c r="C65" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="D65" t="n">
         <v>26.0</v>
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1582.0</v>
+        <v>1586.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1156.0</v>
+        <v>1166.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>567.0</v>
+        <v>570.0</v>
       </c>
     </row>
     <row r="68">
@@ -1406,10 +1406,10 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="D69" t="n">
-        <v>203.0</v>
+        <v>205.0</v>
       </c>
     </row>
     <row r="70">
@@ -1476,7 +1476,7 @@
         <v>97</v>
       </c>
       <c r="C74" t="n">
-        <v>302.0</v>
+        <v>303.0</v>
       </c>
       <c r="D74" t="n">
         <v>48.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>490.0</v>
+        <v>491.0</v>
       </c>
       <c r="D88" t="n">
         <v>284.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>487.0</v>
+        <v>489.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>425.0</v>
+        <v>426.0</v>
       </c>
       <c r="D93" t="n">
         <v>56.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>832.0</v>
+        <v>833.0</v>
       </c>
       <c r="D96" t="n">
         <v>473.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>216.0</v>
+        <v>217.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,10 +1840,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>222.0</v>
+        <v>224.0</v>
       </c>
       <c r="D100" t="n">
-        <v>149.0</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="101">
@@ -1868,7 +1868,7 @@
         <v>125</v>
       </c>
       <c r="C102" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="D102" t="n">
         <v>199.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -653,7 +653,7 @@
         <v>713.0</v>
       </c>
       <c r="D15" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="16">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1744.0</v>
+        <v>1747.0</v>
       </c>
       <c r="D59" t="n">
-        <v>355.0</v>
+        <v>357.0</v>
       </c>
     </row>
     <row r="60">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1196.0</v>
+        <v>1197.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12765.0</v>
+        <v>12769.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2896.0</v>
       </c>
       <c r="D63" t="n">
-        <v>706.0</v>
+        <v>707.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1483.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2652.0</v>
+        <v>2654.0</v>
       </c>
     </row>
     <row r="65">
@@ -1367,7 +1367,7 @@
         <v>1586.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1166.0</v>
+        <v>1167.0</v>
       </c>
     </row>
     <row r="67">
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>491.0</v>
+        <v>493.0</v>
       </c>
       <c r="D88" t="n">
-        <v>284.0</v>
+        <v>286.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>489.0</v>
+        <v>491.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>288.0</v>
+        <v>289.0</v>
       </c>
       <c r="D90" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="91">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -622,7 +622,7 @@
         <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>905.0</v>
+        <v>912.0</v>
       </c>
       <c r="D13" t="n">
         <v>339.0</v>
@@ -636,7 +636,7 @@
         <v>37</v>
       </c>
       <c r="C14" t="n">
-        <v>609.0</v>
+        <v>616.0</v>
       </c>
       <c r="D14" t="n">
         <v>119.0</v>
@@ -650,7 +650,7 @@
         <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>713.0</v>
+        <v>720.0</v>
       </c>
       <c r="D15" t="n">
         <v>181.0</v>
@@ -678,7 +678,7 @@
         <v>40</v>
       </c>
       <c r="C17" t="n">
-        <v>9307.0</v>
+        <v>9317.0</v>
       </c>
       <c r="D17" t="n">
         <v>907.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>920.0</v>
+        <v>923.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>324.0</v>
+        <v>326.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5583.0</v>
+        <v>5598.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>426.0</v>
+        <v>427.0</v>
       </c>
       <c r="D93" t="n">
         <v>56.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,10 +468,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>986.0</v>
+        <v>990.0</v>
       </c>
       <c r="D2" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>469.0</v>
+        <v>473.0</v>
       </c>
       <c r="D3" t="n">
         <v>70.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="D4" t="n">
-        <v>368.0</v>
+        <v>369.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,10 +510,10 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>233.0</v>
+        <v>237.0</v>
       </c>
       <c r="D5" t="n">
-        <v>119.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="6">
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>622.0</v>
+        <v>627.0</v>
       </c>
       <c r="D18" t="n">
-        <v>234.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>325.0</v>
+        <v>328.0</v>
       </c>
     </row>
     <row r="21">
@@ -734,10 +734,10 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>386.0</v>
+        <v>389.0</v>
       </c>
       <c r="D21" t="n">
-        <v>530.0</v>
+        <v>534.0</v>
       </c>
     </row>
     <row r="22">
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="D22" t="n">
-        <v>279.0</v>
+        <v>283.0</v>
       </c>
     </row>
     <row r="23">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>114.0</v>
       </c>
       <c r="D25" t="n">
-        <v>289.0</v>
+        <v>290.0</v>
       </c>
     </row>
     <row r="26">
@@ -818,7 +818,7 @@
         <v>50</v>
       </c>
       <c r="C27" t="n">
-        <v>155.0</v>
+        <v>156.0</v>
       </c>
       <c r="D27" t="n">
         <v>12.0</v>
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="D28" t="n">
         <v>160.0</v>
@@ -972,7 +972,7 @@
         <v>61</v>
       </c>
       <c r="C38" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D38" t="n">
         <v>0.0</v>
@@ -1238,10 +1238,10 @@
         <v>80</v>
       </c>
       <c r="C57" t="n">
-        <v>765.0</v>
+        <v>769.0</v>
       </c>
       <c r="D57" t="n">
-        <v>453.0</v>
+        <v>459.0</v>
       </c>
     </row>
     <row r="58">
@@ -1255,7 +1255,7 @@
         <v>169.0</v>
       </c>
       <c r="D58" t="n">
-        <v>164.0</v>
+        <v>172.0</v>
       </c>
     </row>
     <row r="59">
@@ -1297,7 +1297,7 @@
         <v>732.0</v>
       </c>
       <c r="D61" t="n">
-        <v>898.0</v>
+        <v>899.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1197.0</v>
+        <v>1200.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12769.0</v>
+        <v>12783.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1483.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2654.0</v>
+        <v>2656.0</v>
       </c>
     </row>
     <row r="65">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>570.0</v>
+        <v>571.0</v>
       </c>
     </row>
     <row r="68">
@@ -1490,10 +1490,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="D75" t="n">
-        <v>75.0</v>
+        <v>79.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>689.0</v>
+        <v>701.0</v>
       </c>
       <c r="D76" t="n">
-        <v>438.0</v>
+        <v>443.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>484.0</v>
+        <v>496.0</v>
       </c>
       <c r="D77" t="n">
-        <v>458.0</v>
+        <v>465.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,10 +1532,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1797.0</v>
+        <v>1840.0</v>
       </c>
       <c r="D78" t="n">
-        <v>541.0</v>
+        <v>548.0</v>
       </c>
     </row>
     <row r="79">
@@ -1546,10 +1546,10 @@
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>335.0</v>
+        <v>339.0</v>
       </c>
       <c r="D79" t="n">
-        <v>509.0</v>
+        <v>517.0</v>
       </c>
     </row>
     <row r="80">
@@ -1899,7 +1899,7 @@
         <v>123.0</v>
       </c>
       <c r="D104" t="n">
-        <v>320.0</v>
+        <v>321.0</v>
       </c>
     </row>
     <row r="105">
@@ -1910,7 +1910,7 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="D105" t="n">
         <v>185.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -468,7 +468,7 @@
         <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>990.0</v>
+        <v>993.0</v>
       </c>
       <c r="D2" t="n">
         <v>84.0</v>
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>473.0</v>
+        <v>476.0</v>
       </c>
       <c r="D3" t="n">
         <v>70.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>190.0</v>
+        <v>191.0</v>
       </c>
       <c r="D4" t="n">
-        <v>369.0</v>
+        <v>377.0</v>
       </c>
     </row>
     <row r="5">
@@ -510,7 +510,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
       <c r="D5" t="n">
         <v>122.0</v>
@@ -692,7 +692,7 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>627.0</v>
+        <v>631.0</v>
       </c>
       <c r="D18" t="n">
         <v>237.0</v>
@@ -734,7 +734,7 @@
         <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>389.0</v>
+        <v>392.0</v>
       </c>
       <c r="D21" t="n">
         <v>534.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5598.0</v>
+        <v>5599.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -1003,7 +1003,7 @@
         <v>136.0</v>
       </c>
       <c r="D40" t="n">
-        <v>927.0</v>
+        <v>931.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>185.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2182.0</v>
+        <v>2190.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>448.0</v>
+        <v>452.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,10 +1042,10 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4002.0</v>
+        <v>4005.0</v>
       </c>
     </row>
     <row r="44">
@@ -1073,7 +1073,7 @@
         <v>82.0</v>
       </c>
       <c r="D45" t="n">
-        <v>24873.0</v>
+        <v>24875.0</v>
       </c>
     </row>
     <row r="46">
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1463.0</v>
+        <v>1464.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,10 +1098,10 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>743.0</v>
+        <v>746.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1894.0</v>
+        <v>1895.0</v>
       </c>
     </row>
     <row r="48">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>754.0</v>
+        <v>755.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1241,7 +1241,7 @@
         <v>769.0</v>
       </c>
       <c r="D57" t="n">
-        <v>459.0</v>
+        <v>460.0</v>
       </c>
     </row>
     <row r="58">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1747.0</v>
+        <v>1748.0</v>
       </c>
       <c r="D59" t="n">
         <v>357.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1624.0</v>
+        <v>1625.0</v>
       </c>
       <c r="D60" t="n">
         <v>150.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1200.0</v>
+        <v>1203.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12783.0</v>
+        <v>12800.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2896.0</v>
       </c>
       <c r="D63" t="n">
-        <v>707.0</v>
+        <v>709.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1483.0</v>
+        <v>1485.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2656.0</v>
+        <v>2685.0</v>
       </c>
     </row>
     <row r="65">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1168,10 +1168,10 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>382.0</v>
+        <v>383.0</v>
       </c>
       <c r="D52" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="53">
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>176.0</v>
+        <v>177.0</v>
       </c>
     </row>
     <row r="55">
@@ -1210,10 +1210,10 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>499.0</v>
+        <v>500.0</v>
       </c>
       <c r="D55" t="n">
-        <v>138.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="56">
@@ -1224,7 +1224,7 @@
         <v>79</v>
       </c>
       <c r="C56" t="n">
-        <v>436.0</v>
+        <v>438.0</v>
       </c>
       <c r="D56" t="n">
         <v>150.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1748.0</v>
+        <v>1750.0</v>
       </c>
       <c r="D59" t="n">
         <v>357.0</v>
@@ -1311,7 +1311,7 @@
         <v>1203.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12800.0</v>
+        <v>12822.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1485.0</v>
+        <v>1488.0</v>
       </c>
       <c r="D64" t="n">
         <v>2685.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>493.0</v>
+        <v>495.0</v>
       </c>
       <c r="D88" t="n">
         <v>286.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>491.0</v>
+        <v>492.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="D92" t="n">
         <v>4.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>427.0</v>
+        <v>429.0</v>
       </c>
       <c r="D93" t="n">
         <v>56.0</v>
@@ -1787,7 +1787,7 @@
         <v>833.0</v>
       </c>
       <c r="D96" t="n">
-        <v>473.0</v>
+        <v>474.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>923.0</v>
+        <v>924.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>326.0</v>
+        <v>327.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5599.0</v>
+        <v>5608.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>940.0</v>
+        <v>945.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1283,7 +1283,7 @@
         <v>1625.0</v>
       </c>
       <c r="D60" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="61">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1203.0</v>
+        <v>1206.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12822.0</v>
+        <v>12838.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2896.0</v>
+        <v>2897.0</v>
       </c>
       <c r="D63" t="n">
-        <v>709.0</v>
+        <v>712.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1488.0</v>
+        <v>1489.0</v>
       </c>
       <c r="D64" t="n">
         <v>2685.0</v>
@@ -1619,7 +1619,7 @@
         <v>53.0</v>
       </c>
       <c r="D84" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="85">
@@ -1633,7 +1633,7 @@
         <v>3.0</v>
       </c>
       <c r="D85" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="86">
@@ -1644,7 +1644,7 @@
         <v>109</v>
       </c>
       <c r="C86" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="D86" t="n">
         <v>10.0</v>
@@ -1675,7 +1675,7 @@
         <v>495.0</v>
       </c>
       <c r="D88" t="n">
-        <v>286.0</v>
+        <v>287.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1199,7 +1199,7 @@
         <v>107.0</v>
       </c>
       <c r="D54" t="n">
-        <v>177.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="55">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1750.0</v>
+        <v>1751.0</v>
       </c>
       <c r="D59" t="n">
         <v>357.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1206.0</v>
+        <v>1208.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12838.0</v>
+        <v>12845.0</v>
       </c>
     </row>
     <row r="63">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1586.0</v>
+        <v>1588.0</v>
       </c>
       <c r="D66" t="n">
         <v>1167.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>493.0</v>
+        <v>495.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="D95" t="n">
         <v>232.0</v>
@@ -1784,10 +1784,10 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>833.0</v>
+        <v>836.0</v>
       </c>
       <c r="D96" t="n">
-        <v>474.0</v>
+        <v>475.0</v>
       </c>
     </row>
     <row r="97">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>495.0</v>
+        <v>496.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1703,7 +1703,7 @@
         <v>289.0</v>
       </c>
       <c r="D90" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="91">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -524,10 +524,10 @@
         <v>29</v>
       </c>
       <c r="C6" t="n">
-        <v>1180.0</v>
+        <v>1186.0</v>
       </c>
       <c r="D6" t="n">
-        <v>342.0</v>
+        <v>343.0</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +538,7 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>2207.0</v>
+        <v>2219.0</v>
       </c>
       <c r="D7" t="n">
         <v>1096.0</v>
@@ -692,10 +692,10 @@
         <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>631.0</v>
+        <v>636.0</v>
       </c>
       <c r="D18" t="n">
-        <v>237.0</v>
+        <v>239.0</v>
       </c>
     </row>
     <row r="19">
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="20">
@@ -723,7 +723,7 @@
         <v>79.0</v>
       </c>
       <c r="D20" t="n">
-        <v>328.0</v>
+        <v>329.0</v>
       </c>
     </row>
     <row r="21">
@@ -748,10 +748,10 @@
         <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="D22" t="n">
-        <v>283.0</v>
+        <v>284.0</v>
       </c>
     </row>
     <row r="23">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>390.0</v>
+        <v>391.0</v>
       </c>
     </row>
     <row r="25">
@@ -790,10 +790,10 @@
         <v>48</v>
       </c>
       <c r="C25" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="D25" t="n">
-        <v>290.0</v>
+        <v>293.0</v>
       </c>
     </row>
     <row r="26">
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>250.0</v>
+        <v>251.0</v>
       </c>
       <c r="D28" t="n">
         <v>160.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>167.0</v>
+        <v>171.0</v>
       </c>
       <c r="D30" t="n">
         <v>161.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1210,7 +1210,7 @@
         <v>78</v>
       </c>
       <c r="C55" t="n">
-        <v>500.0</v>
+        <v>501.0</v>
       </c>
       <c r="D55" t="n">
         <v>140.0</v>
@@ -1283,7 +1283,7 @@
         <v>1625.0</v>
       </c>
       <c r="D60" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="61">
@@ -1297,7 +1297,7 @@
         <v>732.0</v>
       </c>
       <c r="D61" t="n">
-        <v>899.0</v>
+        <v>900.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>1208.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12845.0</v>
+        <v>12859.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2897.0</v>
       </c>
       <c r="D63" t="n">
-        <v>712.0</v>
+        <v>715.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1489.0</v>
+        <v>1492.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2685.0</v>
+        <v>2686.0</v>
       </c>
     </row>
     <row r="65">
@@ -1406,7 +1406,7 @@
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
       <c r="D69" t="n">
         <v>205.0</v>
@@ -1479,7 +1479,7 @@
         <v>303.0</v>
       </c>
       <c r="D74" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="75">
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>836.0</v>
+        <v>837.0</v>
       </c>
       <c r="D96" t="n">
         <v>475.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>217.0</v>
+        <v>219.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,10 +1840,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="D100" t="n">
-        <v>151.0</v>
+        <v>154.0</v>
       </c>
     </row>
     <row r="101">
@@ -1871,7 +1871,7 @@
         <v>108.0</v>
       </c>
       <c r="D102" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="103">
@@ -1882,7 +1882,7 @@
         <v>126</v>
       </c>
       <c r="C103" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D103" t="n">
         <v>134.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1003,7 +1003,7 @@
         <v>136.0</v>
       </c>
       <c r="D40" t="n">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>185.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2190.0</v>
+        <v>2194.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>452.0</v>
+        <v>454.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1045,7 +1045,7 @@
         <v>144.0</v>
       </c>
       <c r="D43" t="n">
-        <v>4005.0</v>
+        <v>4006.0</v>
       </c>
     </row>
     <row r="44">
@@ -1056,7 +1056,7 @@
         <v>67</v>
       </c>
       <c r="C44" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="D44" t="n">
         <v>35.0</v>
@@ -1070,7 +1070,7 @@
         <v>68</v>
       </c>
       <c r="C45" t="n">
-        <v>82.0</v>
+        <v>85.0</v>
       </c>
       <c r="D45" t="n">
         <v>24875.0</v>
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1464.0</v>
+        <v>1467.0</v>
       </c>
     </row>
     <row r="47">
@@ -1101,7 +1101,7 @@
         <v>746.0</v>
       </c>
       <c r="D47" t="n">
-        <v>1895.0</v>
+        <v>1898.0</v>
       </c>
     </row>
     <row r="48">
@@ -1129,7 +1129,7 @@
         <v>1688.0</v>
       </c>
       <c r="D49" t="n">
-        <v>3903.0</v>
+        <v>3904.0</v>
       </c>
     </row>
     <row r="50">
@@ -1154,7 +1154,7 @@
         <v>74</v>
       </c>
       <c r="C51" t="n">
-        <v>755.0</v>
+        <v>757.0</v>
       </c>
       <c r="D51" t="n">
         <v>75.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1751.0</v>
+        <v>1752.0</v>
       </c>
       <c r="D59" t="n">
         <v>357.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1625.0</v>
+        <v>1626.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1311,7 +1311,7 @@
         <v>1208.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12859.0</v>
+        <v>12880.0</v>
       </c>
     </row>
     <row r="63">
@@ -1339,7 +1339,7 @@
         <v>1492.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2686.0</v>
+        <v>2688.0</v>
       </c>
     </row>
     <row r="65">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>495.0</v>
+        <v>496.0</v>
       </c>
       <c r="D88" t="n">
         <v>287.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>289.0</v>
+        <v>291.0</v>
       </c>
       <c r="D90" t="n">
         <v>111.0</v>
@@ -1745,7 +1745,7 @@
         <v>429.0</v>
       </c>
       <c r="D93" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
     </row>
     <row r="94">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="D30" t="n">
         <v>161.0</v>
@@ -1168,7 +1168,7 @@
         <v>75</v>
       </c>
       <c r="C52" t="n">
-        <v>383.0</v>
+        <v>385.0</v>
       </c>
       <c r="D52" t="n">
         <v>104.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1752.0</v>
+        <v>1756.0</v>
       </c>
       <c r="D59" t="n">
         <v>357.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1626.0</v>
+        <v>1629.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1208.0</v>
+        <v>1213.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12880.0</v>
+        <v>12892.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2897.0</v>
       </c>
       <c r="D63" t="n">
-        <v>715.0</v>
+        <v>716.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1492.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2688.0</v>
+        <v>2690.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1588.0</v>
+        <v>1592.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1167.0</v>
+        <v>1168.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>571.0</v>
+        <v>572.0</v>
       </c>
     </row>
     <row r="68">
@@ -1395,7 +1395,7 @@
         <v>39.0</v>
       </c>
       <c r="D68" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="69">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>496.0</v>
+        <v>506.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1700,10 +1700,10 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>291.0</v>
+        <v>292.0</v>
       </c>
       <c r="D90" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="91">
@@ -1728,7 +1728,7 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="D92" t="n">
         <v>4.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>429.0</v>
+        <v>430.0</v>
       </c>
       <c r="D93" t="n">
         <v>57.0</v>
@@ -1784,7 +1784,7 @@
         <v>119</v>
       </c>
       <c r="C96" t="n">
-        <v>837.0</v>
+        <v>840.0</v>
       </c>
       <c r="D96" t="n">
         <v>475.0</v>
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>219.0</v>
+        <v>221.0</v>
       </c>
     </row>
     <row r="100">
@@ -1843,7 +1843,7 @@
         <v>225.0</v>
       </c>
       <c r="D100" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="101">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,7 +552,7 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>571.0</v>
+        <v>585.0</v>
       </c>
       <c r="D8" t="n">
         <v>158.0</v>
@@ -566,10 +566,10 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>307.0</v>
+        <v>312.0</v>
       </c>
       <c r="D9" t="n">
-        <v>587.0</v>
+        <v>591.0</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +594,7 @@
         <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>2798.0</v>
+        <v>2799.0</v>
       </c>
       <c r="D11" t="n">
         <v>565.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>924.0</v>
+        <v>928.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>327.0</v>
+        <v>329.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5608.0</v>
+        <v>5622.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>945.0</v>
+        <v>950.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1756.0</v>
+        <v>1757.0</v>
       </c>
       <c r="D59" t="n">
         <v>357.0</v>
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1629.0</v>
+        <v>1630.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1297,7 +1297,7 @@
         <v>732.0</v>
       </c>
       <c r="D61" t="n">
-        <v>900.0</v>
+        <v>903.0</v>
       </c>
     </row>
     <row r="62">
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1213.0</v>
+        <v>1215.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12892.0</v>
+        <v>12905.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1492.0</v>
+        <v>1493.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2690.0</v>
+        <v>2692.0</v>
       </c>
     </row>
     <row r="65">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>496.0</v>
+        <v>498.0</v>
       </c>
       <c r="D88" t="n">
         <v>287.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>506.0</v>
+        <v>507.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="D90" t="n">
         <v>112.0</v>
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="D95" t="n">
         <v>232.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -1311,7 +1311,7 @@
         <v>1215.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12905.0</v>
+        <v>12907.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2897.0</v>
       </c>
       <c r="D63" t="n">
-        <v>716.0</v>
+        <v>720.0</v>
       </c>
     </row>
     <row r="64">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1493.0</v>
+        <v>1494.0</v>
       </c>
       <c r="D64" t="n">
         <v>2692.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>498.0</v>
+        <v>501.0</v>
       </c>
       <c r="D88" t="n">
         <v>287.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>507.0</v>
+        <v>508.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1773,7 +1773,7 @@
         <v>160.0</v>
       </c>
       <c r="D95" t="n">
-        <v>232.0</v>
+        <v>234.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>928.0</v>
+        <v>932.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>329.0</v>
+        <v>333.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5622.0</v>
+        <v>5634.0</v>
       </c>
       <c r="D34" t="n">
         <v>214.0</v>
@@ -1672,10 +1672,10 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>501.0</v>
+        <v>502.0</v>
       </c>
       <c r="D88" t="n">
-        <v>287.0</v>
+        <v>288.0</v>
       </c>
     </row>
     <row r="89">
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>293.0</v>
+        <v>294.0</v>
       </c>
       <c r="D90" t="n">
         <v>112.0</v>
@@ -1717,7 +1717,7 @@
         <v>172.0</v>
       </c>
       <c r="D91" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="92">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -471,7 +471,7 @@
         <v>993.0</v>
       </c>
       <c r="D2" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="3">
@@ -482,7 +482,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>476.0</v>
+        <v>478.0</v>
       </c>
       <c r="D3" t="n">
         <v>70.0</v>
@@ -496,10 +496,10 @@
         <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="D4" t="n">
-        <v>377.0</v>
+        <v>381.0</v>
       </c>
     </row>
     <row r="5">
@@ -832,7 +832,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>251.0</v>
+        <v>253.0</v>
       </c>
       <c r="D28" t="n">
         <v>160.0</v>
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>172.0</v>
+        <v>174.0</v>
       </c>
       <c r="D30" t="n">
         <v>161.0</v>
@@ -1241,7 +1241,7 @@
         <v>769.0</v>
       </c>
       <c r="D57" t="n">
-        <v>460.0</v>
+        <v>462.0</v>
       </c>
     </row>
     <row r="58">
@@ -1252,10 +1252,10 @@
         <v>81</v>
       </c>
       <c r="C58" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="D58" t="n">
-        <v>172.0</v>
+        <v>176.0</v>
       </c>
     </row>
     <row r="59">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1757.0</v>
+        <v>1758.0</v>
       </c>
       <c r="D59" t="n">
-        <v>357.0</v>
+        <v>359.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1630.0</v>
+        <v>1632.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1215.0</v>
+        <v>1218.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12907.0</v>
+        <v>12923.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,10 +1322,10 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2897.0</v>
+        <v>2898.0</v>
       </c>
       <c r="D63" t="n">
-        <v>720.0</v>
+        <v>722.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1494.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2692.0</v>
+        <v>2693.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1592.0</v>
+        <v>1593.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1168.0</v>
+        <v>1170.0</v>
       </c>
     </row>
     <row r="67">
@@ -1381,7 +1381,7 @@
         <v>9.0</v>
       </c>
       <c r="D67" t="n">
-        <v>572.0</v>
+        <v>577.0</v>
       </c>
     </row>
     <row r="68">
@@ -1395,7 +1395,7 @@
         <v>39.0</v>
       </c>
       <c r="D68" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="69">
@@ -1829,7 +1829,7 @@
         <v>32.0</v>
       </c>
       <c r="D99" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
     </row>
     <row r="100">
@@ -1840,10 +1840,10 @@
         <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="D100" t="n">
-        <v>156.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="101">
@@ -1871,7 +1871,7 @@
         <v>108.0</v>
       </c>
       <c r="D102" t="n">
-        <v>200.0</v>
+        <v>201.0</v>
       </c>
     </row>
     <row r="103">
@@ -1910,10 +1910,10 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>86.0</v>
+        <v>89.0</v>
       </c>
       <c r="D105" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>932.0</v>
+        <v>933.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>333.0</v>
+        <v>336.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>324.0</v>
+        <v>325.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5634.0</v>
+        <v>5644.0</v>
       </c>
       <c r="D34" t="n">
-        <v>214.0</v>
+        <v>215.0</v>
       </c>
     </row>
     <row r="35">
@@ -930,7 +930,7 @@
         <v>58</v>
       </c>
       <c r="C35" t="n">
-        <v>950.0</v>
+        <v>954.0</v>
       </c>
       <c r="D35" t="n">
         <v>87.0</v>
@@ -1003,7 +1003,7 @@
         <v>136.0</v>
       </c>
       <c r="D40" t="n">
-        <v>933.0</v>
+        <v>935.0</v>
       </c>
     </row>
     <row r="41">
@@ -1017,7 +1017,7 @@
         <v>185.0</v>
       </c>
       <c r="D41" t="n">
-        <v>2194.0</v>
+        <v>2195.0</v>
       </c>
     </row>
     <row r="42">
@@ -1028,7 +1028,7 @@
         <v>65</v>
       </c>
       <c r="C42" t="n">
-        <v>454.0</v>
+        <v>457.0</v>
       </c>
       <c r="D42" t="n">
         <v>38.0</v>
@@ -1042,7 +1042,7 @@
         <v>66</v>
       </c>
       <c r="C43" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="D43" t="n">
         <v>4006.0</v>
@@ -1087,7 +1087,7 @@
         <v>9.0</v>
       </c>
       <c r="D46" t="n">
-        <v>1467.0</v>
+        <v>1468.0</v>
       </c>
     </row>
     <row r="47">
@@ -1098,7 +1098,7 @@
         <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>746.0</v>
+        <v>747.0</v>
       </c>
       <c r="D47" t="n">
         <v>1898.0</v>
@@ -1126,7 +1126,7 @@
         <v>72</v>
       </c>
       <c r="C49" t="n">
-        <v>1688.0</v>
+        <v>1689.0</v>
       </c>
       <c r="D49" t="n">
         <v>3904.0</v>
@@ -1157,7 +1157,7 @@
         <v>757.0</v>
       </c>
       <c r="D51" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1758.0</v>
+        <v>1762.0</v>
       </c>
       <c r="D59" t="n">
         <v>359.0</v>
@@ -1311,7 +1311,7 @@
         <v>1218.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12923.0</v>
+        <v>12940.0</v>
       </c>
     </row>
     <row r="63">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1593.0</v>
+        <v>1595.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1170.0</v>
+        <v>1172.0</v>
       </c>
     </row>
     <row r="67">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -860,7 +860,7 @@
         <v>53</v>
       </c>
       <c r="C30" t="n">
-        <v>174.0</v>
+        <v>176.0</v>
       </c>
       <c r="D30" t="n">
         <v>161.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>933.0</v>
+        <v>934.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -916,7 +916,7 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5644.0</v>
+        <v>5646.0</v>
       </c>
       <c r="D34" t="n">
         <v>215.0</v>
@@ -958,7 +958,7 @@
         <v>60</v>
       </c>
       <c r="C37" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="D37" t="n">
         <v>9.0</v>
@@ -1269,7 +1269,7 @@
         <v>1762.0</v>
       </c>
       <c r="D59" t="n">
-        <v>359.0</v>
+        <v>360.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1632.0</v>
+        <v>1636.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1218.0</v>
+        <v>1220.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12940.0</v>
+        <v>12958.0</v>
       </c>
     </row>
     <row r="63">
@@ -1325,7 +1325,7 @@
         <v>2898.0</v>
       </c>
       <c r="D63" t="n">
-        <v>722.0</v>
+        <v>723.0</v>
       </c>
     </row>
     <row r="64">
@@ -1339,7 +1339,7 @@
         <v>1494.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2693.0</v>
+        <v>2696.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,7 +1364,7 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1595.0</v>
+        <v>1596.0</v>
       </c>
       <c r="D66" t="n">
         <v>1172.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>509.0</v>
+        <v>510.0</v>
       </c>
       <c r="D89" t="n">
         <v>132.0</v>
@@ -1700,7 +1700,7 @@
         <v>113</v>
       </c>
       <c r="C90" t="n">
-        <v>294.0</v>
+        <v>295.0</v>
       </c>
       <c r="D90" t="n">
         <v>112.0</v>
@@ -1714,7 +1714,7 @@
         <v>114</v>
       </c>
       <c r="C91" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="D91" t="n">
         <v>63.0</v>
@@ -1742,7 +1742,7 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>430.0</v>
+        <v>432.0</v>
       </c>
       <c r="D93" t="n">
         <v>57.0</v>
@@ -1756,7 +1756,7 @@
         <v>117</v>
       </c>
       <c r="C94" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="D94" t="n">
         <v>0.0</v>
@@ -1773,7 +1773,7 @@
         <v>160.0</v>
       </c>
       <c r="D95" t="n">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
     </row>
     <row r="96">

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -709,7 +709,7 @@
         <v>7.0</v>
       </c>
       <c r="D19" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>41.0</v>
       </c>
       <c r="D22" t="n">
-        <v>284.0</v>
+        <v>291.0</v>
       </c>
     </row>
     <row r="23">
@@ -779,7 +779,7 @@
         <v>76.0</v>
       </c>
       <c r="D24" t="n">
-        <v>391.0</v>
+        <v>392.0</v>
       </c>
     </row>
     <row r="25">
@@ -793,7 +793,7 @@
         <v>115.0</v>
       </c>
       <c r="D25" t="n">
-        <v>293.0</v>
+        <v>295.0</v>
       </c>
     </row>
     <row r="26">
@@ -902,7 +902,7 @@
         <v>56</v>
       </c>
       <c r="C33" t="n">
-        <v>325.0</v>
+        <v>329.0</v>
       </c>
       <c r="D33" t="n">
         <v>50.0</v>
@@ -919,7 +919,7 @@
         <v>5646.0</v>
       </c>
       <c r="D34" t="n">
-        <v>215.0</v>
+        <v>216.0</v>
       </c>
     </row>
     <row r="35">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1636.0</v>
+        <v>1638.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1294,10 +1294,10 @@
         <v>84</v>
       </c>
       <c r="C61" t="n">
-        <v>732.0</v>
+        <v>734.0</v>
       </c>
       <c r="D61" t="n">
-        <v>903.0</v>
+        <v>907.0</v>
       </c>
     </row>
     <row r="62">
@@ -1311,7 +1311,7 @@
         <v>1220.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12958.0</v>
+        <v>12962.0</v>
       </c>
     </row>
     <row r="63">
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
       <c r="C63" t="n">
-        <v>2898.0</v>
+        <v>2899.0</v>
       </c>
       <c r="D63" t="n">
         <v>723.0</v>
@@ -1336,10 +1336,10 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1494.0</v>
+        <v>1496.0</v>
       </c>
       <c r="D64" t="n">
-        <v>2696.0</v>
+        <v>2697.0</v>
       </c>
     </row>
     <row r="65">
@@ -1364,10 +1364,10 @@
         <v>89</v>
       </c>
       <c r="C66" t="n">
-        <v>1596.0</v>
+        <v>1597.0</v>
       </c>
       <c r="D66" t="n">
-        <v>1172.0</v>
+        <v>1173.0</v>
       </c>
     </row>
     <row r="67">
@@ -1490,10 +1490,10 @@
         <v>98</v>
       </c>
       <c r="C75" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="D75" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="76">
@@ -1504,10 +1504,10 @@
         <v>99</v>
       </c>
       <c r="C76" t="n">
-        <v>701.0</v>
+        <v>711.0</v>
       </c>
       <c r="D76" t="n">
-        <v>443.0</v>
+        <v>448.0</v>
       </c>
     </row>
     <row r="77">
@@ -1518,10 +1518,10 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>496.0</v>
+        <v>512.0</v>
       </c>
       <c r="D77" t="n">
-        <v>465.0</v>
+        <v>473.0</v>
       </c>
     </row>
     <row r="78">
@@ -1532,10 +1532,10 @@
         <v>101</v>
       </c>
       <c r="C78" t="n">
-        <v>1840.0</v>
+        <v>1855.0</v>
       </c>
       <c r="D78" t="n">
-        <v>548.0</v>
+        <v>551.0</v>
       </c>
     </row>
     <row r="79">
@@ -1546,10 +1546,10 @@
         <v>102</v>
       </c>
       <c r="C79" t="n">
-        <v>339.0</v>
+        <v>342.0</v>
       </c>
       <c r="D79" t="n">
-        <v>517.0</v>
+        <v>524.0</v>
       </c>
     </row>
     <row r="80">
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>502.0</v>
+        <v>503.0</v>
       </c>
       <c r="D88" t="n">
         <v>288.0</v>
@@ -1686,10 +1686,10 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>510.0</v>
+        <v>514.0</v>
       </c>
       <c r="D89" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="90">
@@ -1770,7 +1770,7 @@
         <v>118</v>
       </c>
       <c r="C95" t="n">
-        <v>160.0</v>
+        <v>161.0</v>
       </c>
       <c r="D95" t="n">
         <v>236.0</v>

--- a/Download/unrestricted_areas.xlsx
+++ b/Download/unrestricted_areas.xlsx
@@ -552,10 +552,10 @@
         <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>585.0</v>
+        <v>589.0</v>
       </c>
       <c r="D8" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>312.0</v>
+        <v>314.0</v>
       </c>
       <c r="D9" t="n">
         <v>591.0</v>
@@ -597,7 +597,7 @@
         <v>2799.0</v>
       </c>
       <c r="D11" t="n">
-        <v>565.0</v>
+        <v>568.0</v>
       </c>
     </row>
     <row r="12">
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="C12" t="n">
-        <v>237.0</v>
+        <v>245.0</v>
       </c>
       <c r="D12" t="n">
         <v>7.0</v>
@@ -874,7 +874,7 @@
         <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>934.0</v>
+        <v>936.0</v>
       </c>
       <c r="D31" t="n">
         <v>57.0</v>
@@ -888,7 +888,7 @@
         <v>55</v>
       </c>
       <c r="C32" t="n">
-        <v>336.0</v>
+        <v>337.0</v>
       </c>
       <c r="D32" t="n">
         <v>9.0</v>
@@ -916,10 +916,10 @@
         <v>57</v>
       </c>
       <c r="C34" t="n">
-        <v>5646.0</v>
+        <v>3969.0</v>
       </c>
       <c r="D34" t="n">
-        <v>216.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="35">
@@ -1266,10 +1266,10 @@
         <v>82</v>
       </c>
       <c r="C59" t="n">
-        <v>1762.0</v>
+        <v>1764.0</v>
       </c>
       <c r="D59" t="n">
-        <v>360.0</v>
+        <v>363.0</v>
       </c>
     </row>
     <row r="60">
@@ -1280,7 +1280,7 @@
         <v>83</v>
       </c>
       <c r="C60" t="n">
-        <v>1638.0</v>
+        <v>1640.0</v>
       </c>
       <c r="D60" t="n">
         <v>153.0</v>
@@ -1308,10 +1308,10 @@
         <v>85</v>
       </c>
       <c r="C62" t="n">
-        <v>1220.0</v>
+        <v>1226.0</v>
       </c>
       <c r="D62" t="n">
-        <v>12962.0</v>
+        <v>12983.0</v>
       </c>
     </row>
     <row r="63">
@@ -1336,7 +1336,7 @@
         <v>87</v>
       </c>
       <c r="C64" t="n">
-        <v>1496.0</v>
+        <v>1497.0</v>
       </c>
       <c r="D64" t="n">
         <v>2697.0</v>
@@ -1672,7 +1672,7 @@
         <v>111</v>
       </c>
       <c r="C88" t="n">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
       <c r="D88" t="n">
         <v>288.0</v>
@@ -1686,7 +1686,7 @@
         <v>112</v>
       </c>
       <c r="C89" t="n">
-        <v>514.0</v>
+        <v>506.0</v>
       </c>
       <c r="D89" t="n">
         <v>133.0</v>
@@ -1717,7 +1717,7 @@
         <v>173.0</v>
       </c>
       <c r="D91" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="92">
@@ -1728,10 +1728,10 @@
         <v>115</v>
       </c>
       <c r="C92" t="n">
-        <v>94.0</v>
+        <v>5.0</v>
       </c>
       <c r="D92" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="93">
@@ -1742,10 +1742,10 @@
         <v>116</v>
       </c>
       <c r="C93" t="n">
-        <v>432.0</v>
+        <v>210.0</v>
       </c>
       <c r="D93" t="n">
-        <v>57.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="94">
